--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Cheque Automation\Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Dropbox\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49605855-2644-4AAA-ABF1-1C095A08BFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE8A013-B18B-47BC-859E-B04A362136E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12654" uniqueCount="2799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12655" uniqueCount="2798">
   <si>
     <t>USE</t>
   </si>
@@ -8416,10 +8416,7 @@
     <t>Cheque No.</t>
   </si>
   <si>
-    <t>use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security </t>
+    <t>ASIF</t>
   </si>
 </sst>
 </file>
@@ -9048,9 +9045,13 @@
       <c r="D9" s="13" t="s">
         <v>2411</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>2797</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -9083,14 +9084,12 @@
         <v>466472</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>2797</v>
+        <v>0</v>
       </c>
       <c r="F11" s="7">
         <v>46153</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>2798</v>
-      </c>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Dropbox\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE8A013-B18B-47BC-859E-B04A362136E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BBD5A3-DEAB-488C-A223-19ED5D04F4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12655" uniqueCount="2798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12657" uniqueCount="2798">
   <si>
     <t>USE</t>
   </si>
@@ -8416,7 +8416,7 @@
     <t>Cheque No.</t>
   </si>
   <si>
-    <t>ASIF</t>
+    <t>use</t>
   </si>
 </sst>
 </file>
@@ -9048,10 +9048,10 @@
       <c r="E9" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>2797</v>
-      </c>
+      <c r="F9" s="7">
+        <v>46153</v>
+      </c>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -9392,8 +9392,12 @@
       <c r="D28" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="E28" s="5" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F28" s="7">
+        <v>46153</v>
+      </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -9409,8 +9413,12 @@
       <c r="D29" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F29" s="7">
+        <v>46153</v>
+      </c>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -9426,8 +9434,12 @@
       <c r="D30" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F30" s="7">
+        <v>46153</v>
+      </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD334C25-F0C4-4767-B1B6-229E36911322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC41848-345D-45BC-BD7A-5001E3848051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$2654</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$2737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9777" uniqueCount="2209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10134" uniqueCount="2244">
   <si>
     <t>USE</t>
   </si>
@@ -5839,12 +5839,6 @@
     <t>000478</t>
   </si>
   <si>
-    <t>049189</t>
-  </si>
-  <si>
-    <t>049188</t>
-  </si>
-  <si>
     <t>UNIVERSAL MEDICAL AGENCY</t>
   </si>
   <si>
@@ -6415,9 +6409,6 @@
     <t>048631</t>
   </si>
   <si>
-    <t>SAYYOG ENTERPRISES</t>
-  </si>
-  <si>
     <t>036662</t>
   </si>
   <si>
@@ -6641,6 +6632,120 @@
   </si>
   <si>
     <t>AMISHA MEDICAL STORE</t>
+  </si>
+  <si>
+    <t>049187</t>
+  </si>
+  <si>
+    <t>049190</t>
+  </si>
+  <si>
+    <t>ANIL DRUG DISTRIBUTORS</t>
+  </si>
+  <si>
+    <t>KLRL PHARMA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>000496</t>
+  </si>
+  <si>
+    <t>000497</t>
+  </si>
+  <si>
+    <t>PK MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>004027</t>
+  </si>
+  <si>
+    <t>004028</t>
+  </si>
+  <si>
+    <t>004029</t>
+  </si>
+  <si>
+    <t>004030</t>
+  </si>
+  <si>
+    <t>004031</t>
+  </si>
+  <si>
+    <t>004032</t>
+  </si>
+  <si>
+    <t>PAWAN MEDICAL AGENCY</t>
+  </si>
+  <si>
+    <t>000498</t>
+  </si>
+  <si>
+    <t>000342</t>
+  </si>
+  <si>
+    <t>000341</t>
+  </si>
+  <si>
+    <t>MARS MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>002111</t>
+  </si>
+  <si>
+    <t>002110</t>
+  </si>
+  <si>
+    <t>002109</t>
+  </si>
+  <si>
+    <t>002108</t>
+  </si>
+  <si>
+    <t>SANYOG ENTERPRISES</t>
+  </si>
+  <si>
+    <t>TARUN MEDICOSE</t>
+  </si>
+  <si>
+    <t>QUALITY MEDICINE CO</t>
+  </si>
+  <si>
+    <t>008481</t>
+  </si>
+  <si>
+    <t>008480</t>
+  </si>
+  <si>
+    <t>008482</t>
+  </si>
+  <si>
+    <t>008483</t>
+  </si>
+  <si>
+    <t>008484</t>
+  </si>
+  <si>
+    <t>032882</t>
+  </si>
+  <si>
+    <t>TANU MEDICOSE</t>
+  </si>
+  <si>
+    <t>002701</t>
+  </si>
+  <si>
+    <t>SHANTI MEDICINE COMPANY</t>
+  </si>
+  <si>
+    <t>003411</t>
+  </si>
+  <si>
+    <t>8563/-</t>
+  </si>
+  <si>
+    <t>5596/-</t>
+  </si>
+  <si>
+    <t>006220</t>
   </si>
   <si>
     <t>Party Name</t>
@@ -6656,7 +6761,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6694,12 +6799,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Berlin Sans FB Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -6769,7 +6868,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -6818,7 +6917,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="40% - Accent1" xfId="2" builtinId="31"/>
@@ -7145,14 +7243,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1048575"/>
+  <dimension ref="A1:O1048573"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.5703125" style="1" customWidth="1"/>
@@ -7164,7 +7262,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>2206</v>
+        <v>2241</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>370</v>
@@ -7173,10 +7271,10 @@
         <v>701</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>2207</v>
+        <v>2242</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>2208</v>
+        <v>2243</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>396</v>
@@ -7583,7 +7681,7 @@
         <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8666,7 +8764,12 @@
       <c r="E87" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="G87" s="7"/>
+      <c r="F87" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
@@ -9332,7 +9435,12 @@
       <c r="E125" s="1">
         <v>868740</v>
       </c>
-      <c r="G125" s="7"/>
+      <c r="F125" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G125" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
@@ -9654,7 +9762,7 @@
         <v>195642</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="7">
         <v>46052</v>
       </c>
@@ -9671,7 +9779,7 @@
         <v>195641</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="7">
         <v>46052</v>
       </c>
@@ -9688,7 +9796,7 @@
         <v>195640</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="7">
         <v>46052</v>
       </c>
@@ -9705,7 +9813,7 @@
         <v>195639</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="7">
         <v>46052</v>
       </c>
@@ -9722,7 +9830,7 @@
         <v>195638</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="7">
         <v>46052</v>
       </c>
@@ -9739,7 +9847,7 @@
         <v>195637</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="7">
         <v>46134</v>
       </c>
@@ -9755,8 +9863,14 @@
       <c r="E150" s="1">
         <v>334555</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F150" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G150" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7">
         <v>46134</v>
       </c>
@@ -9773,7 +9887,7 @@
         <v>334556</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7">
         <v>46137</v>
       </c>
@@ -9789,8 +9903,14 @@
       <c r="E152" s="2" t="s">
         <v>1645</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F152" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G152" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7">
         <v>46137</v>
       </c>
@@ -9807,7 +9927,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7">
         <v>46137</v>
       </c>
@@ -9824,7 +9944,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="7">
         <v>46137</v>
       </c>
@@ -9841,7 +9961,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7">
         <v>46137</v>
       </c>
@@ -9858,7 +9978,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7">
         <v>46137</v>
       </c>
@@ -9875,7 +9995,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
         <v>46137</v>
       </c>
@@ -9892,7 +10012,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
         <v>45800</v>
       </c>
@@ -9909,7 +10029,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7">
         <v>45800</v>
       </c>
@@ -9926,7 +10046,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="7">
         <v>46139</v>
       </c>
@@ -9943,7 +10063,7 @@
         <v>995749</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>46139</v>
       </c>
@@ -9960,7 +10080,7 @@
         <v>995748</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7">
         <v>46139</v>
       </c>
@@ -9976,8 +10096,14 @@
       <c r="E163" s="1">
         <v>995747</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F163" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G163" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
         <v>46139</v>
       </c>
@@ -9993,8 +10119,14 @@
       <c r="E164" s="1">
         <v>995746</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F164" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G164" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B165" s="3" t="s">
         <v>66</v>
       </c>
@@ -10008,7 +10140,7 @@
         <v>713136</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B166" s="3" t="s">
         <v>66</v>
       </c>
@@ -10022,7 +10154,7 @@
         <v>713134</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7">
         <v>46053</v>
       </c>
@@ -10039,7 +10171,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7">
         <v>46053</v>
       </c>
@@ -10056,7 +10188,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="7">
         <v>46036</v>
       </c>
@@ -10073,7 +10205,7 @@
         <v>578096</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7">
         <v>46036</v>
       </c>
@@ -10090,7 +10222,7 @@
         <v>578097</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7">
         <v>46036</v>
       </c>
@@ -10107,7 +10239,7 @@
         <v>578098</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7">
         <v>46036</v>
       </c>
@@ -10124,7 +10256,7 @@
         <v>578099</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7">
         <v>46147</v>
       </c>
@@ -10141,7 +10273,7 @@
         <v>578186</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7">
         <v>46147</v>
       </c>
@@ -10158,7 +10290,7 @@
         <v>578187</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7">
         <v>46147</v>
       </c>
@@ -10175,7 +10307,7 @@
         <v>578188</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7">
         <v>46147</v>
       </c>
@@ -11213,31 +11345,36 @@
         <v>46157</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="E236" s="1">
         <v>123009</v>
       </c>
-      <c r="G236" s="7"/>
+      <c r="F236" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G236" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="237" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="7">
         <v>46157</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="E237" s="1">
         <v>123008</v>
@@ -13467,7 +13604,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="7">
         <v>46135</v>
       </c>
@@ -13484,7 +13621,7 @@
         <v>958417</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="7">
         <v>46135</v>
       </c>
@@ -13501,7 +13638,7 @@
         <v>958418</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="7">
         <v>46135</v>
       </c>
@@ -13518,7 +13655,7 @@
         <v>958419</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="7">
         <v>46149</v>
       </c>
@@ -13534,8 +13671,14 @@
       <c r="E372" s="2" t="s">
         <v>1843</v>
       </c>
-    </row>
-    <row r="373" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F372" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G372" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="7">
         <v>46149</v>
       </c>
@@ -13551,8 +13694,9 @@
       <c r="E373" s="2" t="s">
         <v>1844</v>
       </c>
-    </row>
-    <row r="374" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G373" s="7"/>
+    </row>
+    <row r="374" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="7">
         <v>46149</v>
       </c>
@@ -13569,7 +13713,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="7">
         <v>46149</v>
       </c>
@@ -13586,7 +13730,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="7">
         <v>46149</v>
       </c>
@@ -13603,7 +13747,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="7">
         <v>46149</v>
       </c>
@@ -13620,7 +13764,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="7">
         <v>46149</v>
       </c>
@@ -13637,7 +13781,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="7">
         <v>46149</v>
       </c>
@@ -13654,7 +13798,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="7">
         <v>46139</v>
       </c>
@@ -13671,7 +13815,7 @@
         <v>472150</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="7">
         <v>46139</v>
       </c>
@@ -13688,7 +13832,7 @@
         <v>472151</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="7">
         <v>46139</v>
       </c>
@@ -13705,7 +13849,7 @@
         <v>472152</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="7">
         <v>46139</v>
       </c>
@@ -13722,7 +13866,7 @@
         <v>472153</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="7">
         <v>46139</v>
       </c>
@@ -14024,6 +14168,12 @@
       <c r="E401" s="2" t="s">
         <v>1550</v>
       </c>
+      <c r="F401" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G401" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="402" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="7">
@@ -14217,6 +14367,12 @@
       <c r="E412" s="1">
         <v>388403</v>
       </c>
+      <c r="F412" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G412" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="413" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="7">
@@ -14234,6 +14390,12 @@
       <c r="E413" s="1">
         <v>388404</v>
       </c>
+      <c r="F413" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G413" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="414" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="7">
@@ -15316,6 +15478,12 @@
       <c r="E477" s="2" t="s">
         <v>1151</v>
       </c>
+      <c r="F477" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G477" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="478" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="7">
@@ -15809,6 +15977,12 @@
       <c r="E506" s="1">
         <v>476135</v>
       </c>
+      <c r="F506" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G506" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="507" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="7">
@@ -16304,7 +16478,7 @@
         <v>4</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="535" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16321,7 +16495,7 @@
         <v>4</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="536" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16774,7 +16948,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="7">
         <v>46129</v>
       </c>
@@ -16791,7 +16965,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="7">
         <v>45868</v>
       </c>
@@ -16808,7 +16982,7 @@
         <v>639551</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="7">
         <v>45868</v>
       </c>
@@ -16825,7 +16999,7 @@
         <v>639552</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="7">
         <v>46106</v>
       </c>
@@ -16841,8 +17015,14 @@
       <c r="E564" s="1">
         <v>693050</v>
       </c>
-    </row>
-    <row r="565" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F564" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G564" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="7">
         <v>46147</v>
       </c>
@@ -16859,7 +17039,7 @@
         <v>677900</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="7">
         <v>46147</v>
       </c>
@@ -16876,7 +17056,7 @@
         <v>677899</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="7">
         <v>46147</v>
       </c>
@@ -16893,7 +17073,7 @@
         <v>677898</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="7">
         <v>46147</v>
       </c>
@@ -16910,7 +17090,7 @@
         <v>677897</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="7">
         <v>46147</v>
       </c>
@@ -16927,7 +17107,7 @@
         <v>677896</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="7">
         <v>46147</v>
       </c>
@@ -16944,7 +17124,7 @@
         <v>677895</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="7">
         <v>46147</v>
       </c>
@@ -16961,7 +17141,7 @@
         <v>677894</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="7">
         <v>46147</v>
       </c>
@@ -16978,7 +17158,7 @@
         <v>677893</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="7">
         <v>46147</v>
       </c>
@@ -16995,7 +17175,7 @@
         <v>677892</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="7">
         <v>46147</v>
       </c>
@@ -17012,7 +17192,7 @@
         <v>677891</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="7">
         <v>46148</v>
       </c>
@@ -17029,7 +17209,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="7">
         <v>46148</v>
       </c>
@@ -17230,7 +17410,7 @@
         <v>15</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="588" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17247,7 +17427,7 @@
         <v>15</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="589" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17264,7 +17444,7 @@
         <v>15</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="590" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17281,7 +17461,7 @@
         <v>15</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="591" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17298,7 +17478,7 @@
         <v>15</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17315,7 +17495,7 @@
         <v>15</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="593" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17332,7 +17512,7 @@
         <v>15</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17349,7 +17529,7 @@
         <v>15</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17366,7 +17546,7 @@
         <v>15</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="596" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17383,7 +17563,7 @@
         <v>15</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="597" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18180,7 +18360,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="7">
         <v>46142</v>
       </c>
@@ -18197,7 +18377,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="7">
         <v>46142</v>
       </c>
@@ -18214,7 +18394,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="7">
         <v>46142</v>
       </c>
@@ -18231,7 +18411,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="7">
         <v>46142</v>
       </c>
@@ -18248,7 +18428,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="7">
         <v>46142</v>
       </c>
@@ -18265,7 +18445,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="7">
         <v>46157</v>
       </c>
@@ -18281,8 +18461,14 @@
       <c r="E646" s="1">
         <v>449782</v>
       </c>
-    </row>
-    <row r="647" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F646" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G646" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="7">
         <v>46157</v>
       </c>
@@ -18298,8 +18484,14 @@
       <c r="E647" s="1">
         <v>449783</v>
       </c>
-    </row>
-    <row r="648" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F647" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G647" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="7">
         <v>46157</v>
       </c>
@@ -18316,7 +18508,7 @@
         <v>449784</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="7">
         <v>46157</v>
       </c>
@@ -18333,7 +18525,7 @@
         <v>449785</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="7">
         <v>46157</v>
       </c>
@@ -18350,7 +18542,7 @@
         <v>449786</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="7">
         <v>46157</v>
       </c>
@@ -18367,7 +18559,7 @@
         <v>449787</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="7">
         <v>46157</v>
       </c>
@@ -18384,7 +18576,7 @@
         <v>449788</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="7">
         <v>46157</v>
       </c>
@@ -18401,7 +18593,7 @@
         <v>449789</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="7">
         <v>46157</v>
       </c>
@@ -18418,7 +18610,7 @@
         <v>449790</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="7">
         <v>46065</v>
       </c>
@@ -18435,7 +18627,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="7">
         <v>46065</v>
       </c>
@@ -20885,6 +21077,12 @@
       <c r="E798" s="2" t="s">
         <v>1022</v>
       </c>
+      <c r="F798" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G798" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="799" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="7">
@@ -20920,7 +21118,7 @@
         <v>311086</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="7">
         <v>46105</v>
       </c>
@@ -20937,7 +21135,7 @@
         <v>311087</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="7">
         <v>46107</v>
       </c>
@@ -20953,8 +21151,14 @@
       <c r="E802" s="2" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="803" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F802" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G802" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="803" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="7">
         <v>46107</v>
       </c>
@@ -20970,8 +21174,14 @@
       <c r="E803" s="2" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="804" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F803" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G803" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="804" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="7">
         <v>46107</v>
       </c>
@@ -20988,7 +21198,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="7">
         <v>46107</v>
       </c>
@@ -21005,7 +21215,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="7">
         <v>46107</v>
       </c>
@@ -21022,7 +21232,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="7">
         <v>46107</v>
       </c>
@@ -21039,7 +21249,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="7">
         <v>46107</v>
       </c>
@@ -21056,7 +21266,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="7">
         <v>46107</v>
       </c>
@@ -21073,7 +21283,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="7">
         <v>46107</v>
       </c>
@@ -21090,7 +21300,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="7">
         <v>46010</v>
       </c>
@@ -21107,7 +21317,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="7">
         <v>46010</v>
       </c>
@@ -21124,7 +21334,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="7">
         <v>46010</v>
       </c>
@@ -21141,7 +21351,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="7">
         <v>46080</v>
       </c>
@@ -21158,7 +21368,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="7">
         <v>46080</v>
       </c>
@@ -21175,7 +21385,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="7">
         <v>46080</v>
       </c>
@@ -21533,6 +21743,12 @@
       <c r="E836" s="1">
         <v>503789</v>
       </c>
+      <c r="F836" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G836" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="837" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="7">
@@ -21550,6 +21766,7 @@
       <c r="E837" s="1">
         <v>503790</v>
       </c>
+      <c r="G837" s="7"/>
     </row>
     <row r="838" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="7">
@@ -21567,6 +21784,7 @@
       <c r="E838" s="1">
         <v>503791</v>
       </c>
+      <c r="G838" s="7"/>
     </row>
     <row r="839" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="7">
@@ -22429,10 +22647,10 @@
         <v>44</v>
       </c>
       <c r="D889" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E889" s="2" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="G889" s="7"/>
     </row>
@@ -22447,10 +22665,10 @@
         <v>44</v>
       </c>
       <c r="D890" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E890" s="2" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="891" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22464,10 +22682,10 @@
         <v>44</v>
       </c>
       <c r="D891" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E891" s="2" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="892" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22481,10 +22699,10 @@
         <v>44</v>
       </c>
       <c r="D892" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E892" s="2" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="893" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22498,10 +22716,10 @@
         <v>44</v>
       </c>
       <c r="D893" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E893" s="2" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="894" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22515,10 +22733,10 @@
         <v>44</v>
       </c>
       <c r="D894" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E894" s="2" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="895" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22532,10 +22750,10 @@
         <v>44</v>
       </c>
       <c r="D895" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E895" s="2" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="896" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22549,10 +22767,10 @@
         <v>44</v>
       </c>
       <c r="D896" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E896" s="2" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="897" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22566,10 +22784,10 @@
         <v>44</v>
       </c>
       <c r="D897" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="898" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22583,10 +22801,10 @@
         <v>44</v>
       </c>
       <c r="D898" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E898" s="2" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22600,10 +22818,10 @@
         <v>44</v>
       </c>
       <c r="D899" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E899" s="2" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22617,10 +22835,10 @@
         <v>44</v>
       </c>
       <c r="D900" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E900" s="2" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22634,10 +22852,10 @@
         <v>44</v>
       </c>
       <c r="D901" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E901" s="2" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22651,10 +22869,10 @@
         <v>44</v>
       </c>
       <c r="D902" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E902" s="2" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22668,10 +22886,10 @@
         <v>44</v>
       </c>
       <c r="D903" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E903" s="2" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="904" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22685,10 +22903,10 @@
         <v>44</v>
       </c>
       <c r="D904" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E904" s="2" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="905" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22702,10 +22920,10 @@
         <v>44</v>
       </c>
       <c r="D905" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E905" s="2" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="906" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22719,10 +22937,10 @@
         <v>44</v>
       </c>
       <c r="D906" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E906" s="2" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="907" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22736,10 +22954,10 @@
         <v>44</v>
       </c>
       <c r="D907" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E907" s="2" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="908" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22753,10 +22971,10 @@
         <v>44</v>
       </c>
       <c r="D908" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E908" s="2" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="909" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22770,10 +22988,10 @@
         <v>44</v>
       </c>
       <c r="D909" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E909" s="2" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="910" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22787,10 +23005,10 @@
         <v>44</v>
       </c>
       <c r="D910" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E910" s="2" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="911" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22804,10 +23022,10 @@
         <v>44</v>
       </c>
       <c r="D911" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E911" s="2" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="912" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22821,10 +23039,10 @@
         <v>44</v>
       </c>
       <c r="D912" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E912" s="2" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="913" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22838,10 +23056,10 @@
         <v>44</v>
       </c>
       <c r="D913" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E913" s="2" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="F913" s="1" t="s">
         <v>0</v>
@@ -22861,10 +23079,10 @@
         <v>44</v>
       </c>
       <c r="D914" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E914" s="2" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="F914" s="1" t="s">
         <v>0</v>
@@ -22884,10 +23102,10 @@
         <v>44</v>
       </c>
       <c r="D915" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E915" s="2" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="F915" s="1" t="s">
         <v>0</v>
@@ -23134,6 +23352,12 @@
       <c r="E929" s="2" t="s">
         <v>1821</v>
       </c>
+      <c r="F929" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G929" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="930" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="7">
@@ -23151,6 +23375,12 @@
       <c r="E930" s="2" t="s">
         <v>1822</v>
       </c>
+      <c r="F930" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G930" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="931" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="7">
@@ -23168,6 +23398,12 @@
       <c r="E931" s="2" t="s">
         <v>1823</v>
       </c>
+      <c r="F931" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G931" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="932" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="7">
@@ -23348,8 +23584,9 @@
         <v>15</v>
       </c>
       <c r="E942" s="2" t="s">
-        <v>1938</v>
-      </c>
+        <v>2203</v>
+      </c>
+      <c r="G942" s="7"/>
     </row>
     <row r="943" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="7">
@@ -23365,7 +23602,7 @@
         <v>15</v>
       </c>
       <c r="E943" s="2" t="s">
-        <v>1939</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="944" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23530,7 +23767,13 @@
         <v>24</v>
       </c>
       <c r="E952" s="2" t="s">
-        <v>1997</v>
+        <v>1995</v>
+      </c>
+      <c r="F952" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G952" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="953" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23547,7 +23790,7 @@
         <v>24</v>
       </c>
       <c r="E953" s="2" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="954" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23564,7 +23807,7 @@
         <v>24</v>
       </c>
       <c r="E954" s="2" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="955" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23581,7 +23824,7 @@
         <v>24</v>
       </c>
       <c r="E955" s="2" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="956" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23598,7 +23841,7 @@
         <v>24</v>
       </c>
       <c r="E956" s="2" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="957" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23854,7 +24097,7 @@
         <v>4</v>
       </c>
       <c r="E971" s="2" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="972" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23871,7 +24114,7 @@
         <v>4</v>
       </c>
       <c r="E972" s="2" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="973" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23888,7 +24131,7 @@
         <v>4</v>
       </c>
       <c r="E973" s="2" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="974" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23905,7 +24148,7 @@
         <v>4</v>
       </c>
       <c r="E974" s="2" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="975" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23922,7 +24165,7 @@
         <v>4</v>
       </c>
       <c r="E975" s="2" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="976" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23939,7 +24182,7 @@
         <v>4</v>
       </c>
       <c r="E976" s="2" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="977" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23956,7 +24199,7 @@
         <v>4</v>
       </c>
       <c r="E977" s="2" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="978" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23973,7 +24216,7 @@
         <v>4</v>
       </c>
       <c r="E978" s="2" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="979" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23990,7 +24233,7 @@
         <v>4</v>
       </c>
       <c r="E979" s="2" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="980" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24007,7 +24250,7 @@
         <v>4</v>
       </c>
       <c r="E980" s="2" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="981" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24024,7 +24267,7 @@
         <v>4</v>
       </c>
       <c r="E981" s="2" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="982" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24041,7 +24284,7 @@
         <v>4</v>
       </c>
       <c r="E982" s="2" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="983" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24058,7 +24301,7 @@
         <v>4</v>
       </c>
       <c r="E983" s="2" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="984" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24075,7 +24318,7 @@
         <v>4</v>
       </c>
       <c r="E984" s="2" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="985" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24092,7 +24335,7 @@
         <v>4</v>
       </c>
       <c r="E985" s="2" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="986" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24109,7 +24352,7 @@
         <v>4</v>
       </c>
       <c r="E986" s="2" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="987" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24126,7 +24369,7 @@
         <v>4</v>
       </c>
       <c r="E987" s="2" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="988" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24728,7 +24971,7 @@
         <v>49</v>
       </c>
       <c r="E1022" s="2" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1023" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24973,7 +25216,7 @@
         <v>247</v>
       </c>
       <c r="E1036" s="2" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1037" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25809,6 +26052,7 @@
       <c r="E1084" s="1">
         <v>305805</v>
       </c>
+      <c r="G1084" s="7"/>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1085" s="7">
@@ -27009,7 +27253,7 @@
         <v>15</v>
       </c>
       <c r="E1151" s="2" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.25">
@@ -27540,7 +27784,13 @@
         <v>24</v>
       </c>
       <c r="E1181" s="2" t="s">
-        <v>2079</v>
+        <v>2077</v>
+      </c>
+      <c r="F1181" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1181" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="1182" spans="1:7" x14ac:dyDescent="0.25">
@@ -27557,7 +27807,7 @@
         <v>24</v>
       </c>
       <c r="E1182" s="2" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1183" spans="1:7" x14ac:dyDescent="0.25">
@@ -27574,7 +27824,7 @@
         <v>24</v>
       </c>
       <c r="E1183" s="2" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1184" spans="1:7" x14ac:dyDescent="0.25">
@@ -27591,7 +27841,7 @@
         <v>24</v>
       </c>
       <c r="E1184" s="2" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1185" spans="1:7" x14ac:dyDescent="0.25">
@@ -27700,7 +27950,7 @@
         <v>4</v>
       </c>
       <c r="E1190" s="2" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1191" spans="1:7" x14ac:dyDescent="0.25">
@@ -27717,7 +27967,7 @@
         <v>4</v>
       </c>
       <c r="E1191" s="2" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1192" spans="1:7" x14ac:dyDescent="0.25">
@@ -27734,7 +27984,7 @@
         <v>4</v>
       </c>
       <c r="E1192" s="2" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.25">
@@ -27751,7 +28001,7 @@
         <v>4</v>
       </c>
       <c r="E1193" s="2" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1194" spans="1:7" x14ac:dyDescent="0.25">
@@ -27768,7 +28018,7 @@
         <v>4</v>
       </c>
       <c r="E1194" s="2" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
@@ -27785,7 +28035,7 @@
         <v>4</v>
       </c>
       <c r="E1195" s="2" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
@@ -27802,7 +28052,7 @@
         <v>4</v>
       </c>
       <c r="E1196" s="2" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1197" spans="1:7" x14ac:dyDescent="0.25">
@@ -29285,6 +29535,12 @@
       <c r="E1281" s="2" t="s">
         <v>1626</v>
       </c>
+      <c r="F1281" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1281" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1282" s="7">
@@ -30408,7 +30664,7 @@
         <v>168</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
@@ -30425,7 +30681,7 @@
         <v>168</v>
       </c>
       <c r="E1346" s="2" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
@@ -30442,7 +30698,7 @@
         <v>168</v>
       </c>
       <c r="E1347" s="2" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
@@ -30459,7 +30715,7 @@
         <v>168</v>
       </c>
       <c r="E1348" s="2" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
@@ -30476,7 +30732,7 @@
         <v>168</v>
       </c>
       <c r="E1349" s="2" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
@@ -31304,7 +31560,7 @@
         <v>46155</v>
       </c>
       <c r="B1397" s="3" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C1397" s="1" t="s">
         <v>120</v>
@@ -31313,7 +31569,7 @@
         <v>1386</v>
       </c>
       <c r="E1397" s="2" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1398" spans="1:7" x14ac:dyDescent="0.25">
@@ -31321,7 +31577,7 @@
         <v>46155</v>
       </c>
       <c r="B1398" s="3" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C1398" s="1" t="s">
         <v>120</v>
@@ -31330,7 +31586,7 @@
         <v>1386</v>
       </c>
       <c r="E1398" s="2" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1399" spans="1:7" x14ac:dyDescent="0.25">
@@ -31338,7 +31594,7 @@
         <v>46155</v>
       </c>
       <c r="B1399" s="3" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C1399" s="1" t="s">
         <v>120</v>
@@ -31347,7 +31603,7 @@
         <v>1386</v>
       </c>
       <c r="E1399" s="2" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.25">
@@ -31355,7 +31611,7 @@
         <v>46155</v>
       </c>
       <c r="B1400" s="3" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C1400" s="1" t="s">
         <v>120</v>
@@ -31364,7 +31620,7 @@
         <v>1386</v>
       </c>
       <c r="E1400" s="2" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.25">
@@ -31372,7 +31628,7 @@
         <v>46155</v>
       </c>
       <c r="B1401" s="3" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C1401" s="1" t="s">
         <v>120</v>
@@ -31381,7 +31637,7 @@
         <v>1386</v>
       </c>
       <c r="E1401" s="2" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.25">
@@ -31611,7 +31867,7 @@
         <v>46157</v>
       </c>
       <c r="B1415" s="3" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C1415" s="1" t="s">
         <v>120</v>
@@ -31620,7 +31876,7 @@
         <v>26</v>
       </c>
       <c r="E1415" s="2" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="1416" spans="1:7" x14ac:dyDescent="0.25">
@@ -31628,7 +31884,7 @@
         <v>46157</v>
       </c>
       <c r="B1416" s="3" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C1416" s="1" t="s">
         <v>120</v>
@@ -31637,7 +31893,7 @@
         <v>26</v>
       </c>
       <c r="E1416" s="2" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1417" spans="1:7" x14ac:dyDescent="0.25">
@@ -33126,9 +33382,14 @@
         <v>4</v>
       </c>
       <c r="E1503" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="G1503" s="7"/>
+        <v>696</v>
+      </c>
+      <c r="F1503" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1503" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1504" s="7">
@@ -33146,8 +33407,14 @@
       <c r="E1504" s="2" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="1505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1504" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1504" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1505" s="7">
         <v>46038</v>
       </c>
@@ -33161,10 +33428,11 @@
         <v>4</v>
       </c>
       <c r="E1505" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="1506" spans="1:5" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+      <c r="G1505" s="7"/>
+    </row>
+    <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1506" s="7">
         <v>46106</v>
       </c>
@@ -33181,7 +33449,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="1507" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1507" s="7">
         <v>46106</v>
       </c>
@@ -33198,7 +33466,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="1508" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1508" s="7">
         <v>46106</v>
       </c>
@@ -33215,7 +33483,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="1509" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1509" s="7">
         <v>46106</v>
       </c>
@@ -33232,7 +33500,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="1510" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1510" s="7">
         <v>46106</v>
       </c>
@@ -33249,7 +33517,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="1511" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1511" s="7">
         <v>46106</v>
       </c>
@@ -33266,7 +33534,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="1512" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1512" s="7">
         <v>46140</v>
       </c>
@@ -33283,7 +33551,7 @@
         <v>600632</v>
       </c>
     </row>
-    <row r="1513" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1513" s="7">
         <v>46140</v>
       </c>
@@ -33300,7 +33568,7 @@
         <v>600634</v>
       </c>
     </row>
-    <row r="1514" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1514" s="7">
         <v>46140</v>
       </c>
@@ -33317,7 +33585,7 @@
         <v>600635</v>
       </c>
     </row>
-    <row r="1515" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1515" s="7">
         <v>46140</v>
       </c>
@@ -33334,7 +33602,7 @@
         <v>600636</v>
       </c>
     </row>
-    <row r="1516" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1516" s="7">
         <v>46139</v>
       </c>
@@ -33351,7 +33619,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="1517" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1517" s="7">
         <v>46139</v>
       </c>
@@ -33368,7 +33636,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="1518" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1518" s="7">
         <v>46139</v>
       </c>
@@ -33385,7 +33653,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="1519" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1519" s="7">
         <v>46139</v>
       </c>
@@ -33402,7 +33670,7 @@
         <v>679010</v>
       </c>
     </row>
-    <row r="1520" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1520" s="7">
         <v>46139</v>
       </c>
@@ -33419,7 +33687,7 @@
         <v>679011</v>
       </c>
     </row>
-    <row r="1521" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1521" s="7">
         <v>46139</v>
       </c>
@@ -33436,7 +33704,7 @@
         <v>679012</v>
       </c>
     </row>
-    <row r="1522" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1522" s="7">
         <v>46139</v>
       </c>
@@ -33453,7 +33721,7 @@
         <v>679013</v>
       </c>
     </row>
-    <row r="1523" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1523" s="7">
         <v>46139</v>
       </c>
@@ -33470,7 +33738,7 @@
         <v>679014</v>
       </c>
     </row>
-    <row r="1524" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1524" s="7">
         <v>46139</v>
       </c>
@@ -33487,7 +33755,7 @@
         <v>679015</v>
       </c>
     </row>
-    <row r="1525" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1525" s="7">
         <v>46137</v>
       </c>
@@ -33504,7 +33772,7 @@
         <v>308554</v>
       </c>
     </row>
-    <row r="1526" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1526" s="7">
         <v>46137</v>
       </c>
@@ -33521,7 +33789,7 @@
         <v>308553</v>
       </c>
     </row>
-    <row r="1527" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1527" s="7">
         <v>46137</v>
       </c>
@@ -33538,7 +33806,7 @@
         <v>308552</v>
       </c>
     </row>
-    <row r="1528" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1528" s="7">
         <v>46128</v>
       </c>
@@ -33554,8 +33822,14 @@
       <c r="E1528" s="1">
         <v>822145</v>
       </c>
-    </row>
-    <row r="1529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1528" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1528" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1529" s="7">
         <v>46146</v>
       </c>
@@ -33572,7 +33846,7 @@
         <v>822171</v>
       </c>
     </row>
-    <row r="1530" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1530" s="7">
         <v>46146</v>
       </c>
@@ -33589,7 +33863,7 @@
         <v>822172</v>
       </c>
     </row>
-    <row r="1531" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1531" s="7">
         <v>46146</v>
       </c>
@@ -33606,7 +33880,7 @@
         <v>822173</v>
       </c>
     </row>
-    <row r="1532" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1532" s="7">
         <v>46146</v>
       </c>
@@ -33623,7 +33897,7 @@
         <v>822174</v>
       </c>
     </row>
-    <row r="1533" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1533" s="7">
         <v>46146</v>
       </c>
@@ -33640,7 +33914,7 @@
         <v>822175</v>
       </c>
     </row>
-    <row r="1534" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1534" s="7">
         <v>46146</v>
       </c>
@@ -33657,7 +33931,7 @@
         <v>822176</v>
       </c>
     </row>
-    <row r="1535" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1535" s="7">
         <v>46091</v>
       </c>
@@ -33674,7 +33948,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="1536" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1536" s="7">
         <v>46091</v>
       </c>
@@ -33876,7 +34150,7 @@
         <v>4</v>
       </c>
       <c r="E1547" s="2" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1548" spans="1:7" x14ac:dyDescent="0.25">
@@ -34535,7 +34809,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="1585" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1585" s="7">
         <v>46139</v>
       </c>
@@ -34552,7 +34826,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="1586" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1586" s="7">
         <v>46139</v>
       </c>
@@ -34569,7 +34843,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="1587" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1587" s="7">
         <v>46139</v>
       </c>
@@ -34586,7 +34860,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="1588" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1588" s="7">
         <v>46139</v>
       </c>
@@ -34603,7 +34877,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="1589" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1589" s="7">
         <v>46139</v>
       </c>
@@ -34620,7 +34894,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="1590" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1590" s="7">
         <v>46151</v>
       </c>
@@ -34637,7 +34911,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="1591" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1591" s="7">
         <v>46151</v>
       </c>
@@ -34654,7 +34928,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="1592" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1592" s="7">
         <v>46151</v>
       </c>
@@ -34671,7 +34945,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="1593" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1593" s="7">
         <v>46151</v>
       </c>
@@ -34688,7 +34962,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="1594" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1594" s="7">
         <v>46151</v>
       </c>
@@ -34705,7 +34979,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="1595" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1595" s="7">
         <v>46109</v>
       </c>
@@ -34721,8 +34995,14 @@
       <c r="E1595" s="2" t="s">
         <v>1111</v>
       </c>
-    </row>
-    <row r="1596" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1595" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1595" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1596" s="7">
         <v>46109</v>
       </c>
@@ -34739,7 +35019,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="1597" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1597" s="7">
         <v>46109</v>
       </c>
@@ -34756,7 +35036,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="1598" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1598" s="7">
         <v>46130</v>
       </c>
@@ -34773,7 +35053,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="1599" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1599" s="7">
         <v>46130</v>
       </c>
@@ -34790,7 +35070,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="1600" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1600" s="7">
         <v>46130</v>
       </c>
@@ -34807,7 +35087,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="1601" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1601" s="7">
         <v>46130</v>
       </c>
@@ -34824,7 +35104,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="1602" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1602" s="7">
         <v>46130</v>
       </c>
@@ -34841,7 +35121,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="1603" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1603" s="7">
         <v>46130</v>
       </c>
@@ -34858,7 +35138,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="1604" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1604" s="7">
         <v>46130</v>
       </c>
@@ -34875,7 +35155,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="1605" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1605" s="7">
         <v>46130</v>
       </c>
@@ -34892,7 +35172,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="1606" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1606" s="7">
         <v>46130</v>
       </c>
@@ -34909,7 +35189,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="1607" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1607" s="7">
         <v>46130</v>
       </c>
@@ -34926,7 +35206,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="1608" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1608" s="7">
         <v>46154</v>
       </c>
@@ -34940,10 +35220,16 @@
         <v>26</v>
       </c>
       <c r="E1608" s="2" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="1609" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1952</v>
+      </c>
+      <c r="F1608" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1608" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1609" s="7">
         <v>46154</v>
       </c>
@@ -34957,10 +35243,16 @@
         <v>26</v>
       </c>
       <c r="E1609" s="2" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="1610" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1953</v>
+      </c>
+      <c r="F1609" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1609" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1610" s="7">
         <v>46154</v>
       </c>
@@ -34974,10 +35266,16 @@
         <v>26</v>
       </c>
       <c r="E1610" s="2" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="1611" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1954</v>
+      </c>
+      <c r="F1610" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1610" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1611" s="7">
         <v>46154</v>
       </c>
@@ -34994,7 +35292,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="1612" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1612" s="7">
         <v>46154</v>
       </c>
@@ -35011,7 +35309,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="1613" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1613" s="7">
         <v>46154</v>
       </c>
@@ -35025,10 +35323,10 @@
         <v>26</v>
       </c>
       <c r="E1613" s="2" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="1614" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1614" s="7">
         <v>46154</v>
       </c>
@@ -35042,10 +35340,10 @@
         <v>26</v>
       </c>
       <c r="E1614" s="2" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="1615" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1615" s="7">
         <v>46154</v>
       </c>
@@ -35059,10 +35357,10 @@
         <v>26</v>
       </c>
       <c r="E1615" s="2" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="1616" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1616" s="7">
         <v>46154</v>
       </c>
@@ -35076,7 +35374,7 @@
         <v>26</v>
       </c>
       <c r="E1616" s="2" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1617" spans="1:5" x14ac:dyDescent="0.25">
@@ -35093,7 +35391,7 @@
         <v>26</v>
       </c>
       <c r="E1617" s="2" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1618" spans="1:5" x14ac:dyDescent="0.25">
@@ -35110,7 +35408,7 @@
         <v>26</v>
       </c>
       <c r="E1618" s="2" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1619" spans="1:5" x14ac:dyDescent="0.25">
@@ -35127,7 +35425,7 @@
         <v>26</v>
       </c>
       <c r="E1619" s="2" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1620" spans="1:5" x14ac:dyDescent="0.25">
@@ -35144,7 +35442,7 @@
         <v>26</v>
       </c>
       <c r="E1620" s="2" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1621" spans="1:5" x14ac:dyDescent="0.25">
@@ -35161,7 +35459,7 @@
         <v>26</v>
       </c>
       <c r="E1621" s="2" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1622" spans="1:5" x14ac:dyDescent="0.25">
@@ -35229,7 +35527,7 @@
         <v>26</v>
       </c>
       <c r="E1625" s="2" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1626" spans="1:5" x14ac:dyDescent="0.25">
@@ -35305,7 +35603,7 @@
         <v>46154</v>
       </c>
       <c r="B1630" s="3" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C1630" s="1" t="s">
         <v>17</v>
@@ -35314,7 +35612,7 @@
         <v>58</v>
       </c>
       <c r="E1630" s="2" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1631" spans="1:5" x14ac:dyDescent="0.25">
@@ -35322,7 +35620,7 @@
         <v>46154</v>
       </c>
       <c r="B1631" s="3" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C1631" s="1" t="s">
         <v>17</v>
@@ -35331,7 +35629,7 @@
         <v>58</v>
       </c>
       <c r="E1631" s="2" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1632" spans="1:5" x14ac:dyDescent="0.25">
@@ -35339,7 +35637,7 @@
         <v>46154</v>
       </c>
       <c r="B1632" s="3" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C1632" s="1" t="s">
         <v>17</v>
@@ -35348,7 +35646,7 @@
         <v>58</v>
       </c>
       <c r="E1632" s="2" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1633" spans="1:7" x14ac:dyDescent="0.25">
@@ -35356,7 +35654,7 @@
         <v>46154</v>
       </c>
       <c r="B1633" s="3" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C1633" s="1" t="s">
         <v>17</v>
@@ -35365,7 +35663,7 @@
         <v>58</v>
       </c>
       <c r="E1633" s="2" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1634" spans="1:7" x14ac:dyDescent="0.25">
@@ -35373,7 +35671,7 @@
         <v>46154</v>
       </c>
       <c r="B1634" s="3" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C1634" s="1" t="s">
         <v>17</v>
@@ -35382,7 +35680,7 @@
         <v>58</v>
       </c>
       <c r="E1634" s="2" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1635" spans="1:7" x14ac:dyDescent="0.25">
@@ -35629,7 +35927,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="1649" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1649" s="7">
         <v>46134</v>
       </c>
@@ -35646,7 +35944,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="1650" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1650" s="7">
         <v>46134</v>
       </c>
@@ -35663,7 +35961,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="1651" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1651" s="7">
         <v>46134</v>
       </c>
@@ -35680,7 +35978,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="1652" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1652" s="7">
         <v>45987</v>
       </c>
@@ -35697,7 +35995,7 @@
         <v>658455</v>
       </c>
     </row>
-    <row r="1653" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1653" s="7">
         <v>46041</v>
       </c>
@@ -35714,7 +36012,7 @@
         <v>509443</v>
       </c>
     </row>
-    <row r="1654" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1654" s="7">
         <v>46041</v>
       </c>
@@ -35731,7 +36029,7 @@
         <v>509444</v>
       </c>
     </row>
-    <row r="1655" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1655" s="7">
         <v>46041</v>
       </c>
@@ -35748,7 +36046,7 @@
         <v>509445</v>
       </c>
     </row>
-    <row r="1656" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1656" s="7">
         <v>46157</v>
       </c>
@@ -35762,10 +36060,10 @@
         <v>10</v>
       </c>
       <c r="E1656" s="2" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="1657" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1657" s="7">
         <v>46157</v>
       </c>
@@ -35779,10 +36077,10 @@
         <v>10</v>
       </c>
       <c r="E1657" s="2" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="1658" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1658" s="7">
         <v>46157</v>
       </c>
@@ -35796,10 +36094,10 @@
         <v>10</v>
       </c>
       <c r="E1658" s="2" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="1659" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1659" s="7">
         <v>46157</v>
       </c>
@@ -35813,10 +36111,10 @@
         <v>10</v>
       </c>
       <c r="E1659" s="2" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="1660" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1660" s="7">
         <v>46157</v>
       </c>
@@ -35830,10 +36128,10 @@
         <v>10</v>
       </c>
       <c r="E1660" s="2" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="1661" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1661" s="7">
         <v>46095</v>
       </c>
@@ -35849,8 +36147,14 @@
       <c r="E1661" s="1">
         <v>564881</v>
       </c>
-    </row>
-    <row r="1662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1661" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1661" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1662" s="7">
         <v>46154</v>
       </c>
@@ -35864,10 +36168,10 @@
         <v>15</v>
       </c>
       <c r="E1662" s="2" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="1663" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1663" s="7">
         <v>46154</v>
       </c>
@@ -35881,10 +36185,10 @@
         <v>15</v>
       </c>
       <c r="E1663" s="2" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="1664" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1664" s="7">
         <v>46154</v>
       </c>
@@ -35898,10 +36202,10 @@
         <v>15</v>
       </c>
       <c r="E1664" s="2" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="1665" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1665" s="7">
         <v>46154</v>
       </c>
@@ -35915,10 +36219,10 @@
         <v>15</v>
       </c>
       <c r="E1665" s="2" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="1666" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1666" s="7">
         <v>46154</v>
       </c>
@@ -35932,10 +36236,10 @@
         <v>15</v>
       </c>
       <c r="E1666" s="2" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="1667" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1667" s="7">
         <v>46154</v>
       </c>
@@ -35952,7 +36256,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="1668" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1668" s="7">
         <v>46154</v>
       </c>
@@ -35969,7 +36273,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="1669" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1669" s="7">
         <v>46154</v>
       </c>
@@ -35986,7 +36290,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="1670" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1670" s="7">
         <v>46109</v>
       </c>
@@ -36002,8 +36306,14 @@
       <c r="E1670" s="2" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="1671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1670" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1670" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1671" s="7">
         <v>46157</v>
       </c>
@@ -36017,10 +36327,16 @@
         <v>15</v>
       </c>
       <c r="E1671" s="2" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="1672" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2059</v>
+      </c>
+      <c r="F1671" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1671" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1672" s="7">
         <v>46006</v>
       </c>
@@ -36034,10 +36350,10 @@
         <v>15</v>
       </c>
       <c r="E1672" s="2" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="1673" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1673" s="7">
         <v>46006</v>
       </c>
@@ -36051,10 +36367,10 @@
         <v>15</v>
       </c>
       <c r="E1673" s="2" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="1674" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1674" s="7">
         <v>46006</v>
       </c>
@@ -36068,10 +36384,10 @@
         <v>15</v>
       </c>
       <c r="E1674" s="2" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="1675" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1675" s="7">
         <v>46006</v>
       </c>
@@ -36085,10 +36401,10 @@
         <v>15</v>
       </c>
       <c r="E1675" s="2" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="1676" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1676" s="7">
         <v>46006</v>
       </c>
@@ -36102,10 +36418,10 @@
         <v>15</v>
       </c>
       <c r="E1676" s="2" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="1677" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1677" s="7">
         <v>46006</v>
       </c>
@@ -36119,10 +36435,10 @@
         <v>15</v>
       </c>
       <c r="E1677" s="2" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="1678" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1678" s="7">
         <v>46006</v>
       </c>
@@ -36136,10 +36452,10 @@
         <v>15</v>
       </c>
       <c r="E1678" s="2" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="1679" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1679" s="7">
         <v>46150</v>
       </c>
@@ -36155,8 +36471,14 @@
       <c r="E1679" s="1">
         <v>965889</v>
       </c>
-    </row>
-    <row r="1680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1679" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1679" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1680" s="7">
         <v>46150</v>
       </c>
@@ -36171,6 +36493,12 @@
       </c>
       <c r="E1680" s="1">
         <v>965890</v>
+      </c>
+      <c r="F1680" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1680" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="1681" spans="1:7" x14ac:dyDescent="0.25">
@@ -36731,7 +37059,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="1713" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1713" s="7">
         <v>46140</v>
       </c>
@@ -36748,7 +37076,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="1714" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1714" s="7">
         <v>46140</v>
       </c>
@@ -36765,7 +37093,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="1715" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1715" s="7">
         <v>46140</v>
       </c>
@@ -36782,7 +37110,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="1716" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1716" s="7">
         <v>46140</v>
       </c>
@@ -36799,7 +37127,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="1717" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1717" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1717" s="7">
         <v>46140</v>
       </c>
@@ -36816,7 +37144,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="1718" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1718" s="7">
         <v>46151</v>
       </c>
@@ -36832,8 +37160,14 @@
       <c r="E1718" s="1">
         <v>814181</v>
       </c>
-    </row>
-    <row r="1719" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1718" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1718" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1719" s="7">
         <v>46151</v>
       </c>
@@ -36850,7 +37184,7 @@
         <v>814182</v>
       </c>
     </row>
-    <row r="1720" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1720" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1720" s="7">
         <v>46151</v>
       </c>
@@ -36867,7 +37201,7 @@
         <v>814183</v>
       </c>
     </row>
-    <row r="1721" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1721" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1721" s="7">
         <v>46151</v>
       </c>
@@ -36884,7 +37218,7 @@
         <v>814184</v>
       </c>
     </row>
-    <row r="1722" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1722" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1722" s="7">
         <v>46151</v>
       </c>
@@ -36901,7 +37235,7 @@
         <v>814185</v>
       </c>
     </row>
-    <row r="1723" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1723" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1723" s="7">
         <v>46151</v>
       </c>
@@ -36918,7 +37252,7 @@
         <v>814187</v>
       </c>
     </row>
-    <row r="1724" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1724" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1724" s="7">
         <v>46151</v>
       </c>
@@ -36935,7 +37269,7 @@
         <v>814188</v>
       </c>
     </row>
-    <row r="1725" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1725" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1725" s="7">
         <v>46151</v>
       </c>
@@ -36952,7 +37286,7 @@
         <v>814189</v>
       </c>
     </row>
-    <row r="1726" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1726" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1726" s="7">
         <v>46151</v>
       </c>
@@ -36969,7 +37303,7 @@
         <v>814190</v>
       </c>
     </row>
-    <row r="1727" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1727" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1727" s="7">
         <v>46151</v>
       </c>
@@ -36986,7 +37320,7 @@
         <v>814191</v>
       </c>
     </row>
-    <row r="1728" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1728" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1728" s="7">
         <v>46151</v>
       </c>
@@ -37238,7 +37572,7 @@
         <v>121</v>
       </c>
       <c r="E1742" s="2" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1743" spans="1:5" x14ac:dyDescent="0.25">
@@ -37255,7 +37589,7 @@
         <v>121</v>
       </c>
       <c r="E1743" s="2" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1744" spans="1:5" x14ac:dyDescent="0.25">
@@ -37272,7 +37606,7 @@
         <v>121</v>
       </c>
       <c r="E1744" s="2" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1745" spans="1:7" x14ac:dyDescent="0.25">
@@ -37558,7 +37892,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="1761" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1761" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1761" s="7">
         <v>46151</v>
       </c>
@@ -37575,7 +37909,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="1762" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1762" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1762" s="7">
         <v>46151</v>
       </c>
@@ -37592,7 +37926,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="1763" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1763" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1763" s="7">
         <v>46151</v>
       </c>
@@ -37609,7 +37943,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="1764" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1764" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1764" s="7">
         <v>46151</v>
       </c>
@@ -37626,7 +37960,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="1765" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1765" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1765" s="7">
         <v>46151</v>
       </c>
@@ -37643,7 +37977,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="1766" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1766" s="7">
         <v>46151</v>
       </c>
@@ -37660,7 +37994,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="1767" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1767" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1767" s="7">
         <v>46151</v>
       </c>
@@ -37677,7 +38011,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="1768" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1768" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1768" s="7">
         <v>46151</v>
       </c>
@@ -37694,7 +38028,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="1769" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1769" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1769" s="7">
         <v>46078</v>
       </c>
@@ -37711,7 +38045,7 @@
         <v>251944</v>
       </c>
     </row>
-    <row r="1770" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1770" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1770" s="7">
         <v>46078</v>
       </c>
@@ -37728,7 +38062,7 @@
         <v>251945</v>
       </c>
     </row>
-    <row r="1771" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1771" s="7">
         <v>46133</v>
       </c>
@@ -37745,7 +38079,7 @@
         <v>257435</v>
       </c>
     </row>
-    <row r="1772" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1772" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1772" s="7">
         <v>46133</v>
       </c>
@@ -37762,7 +38096,7 @@
         <v>257436</v>
       </c>
     </row>
-    <row r="1773" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1773" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1773" s="7">
         <v>46133</v>
       </c>
@@ -37779,7 +38113,7 @@
         <v>257434</v>
       </c>
     </row>
-    <row r="1774" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1774" s="7">
         <v>46133</v>
       </c>
@@ -37796,7 +38130,7 @@
         <v>257433</v>
       </c>
     </row>
-    <row r="1775" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1775" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1775" s="7">
         <v>46122</v>
       </c>
@@ -37812,8 +38146,14 @@
       <c r="E1775" s="1">
         <v>183748</v>
       </c>
-    </row>
-    <row r="1776" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1775" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1775" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1776" s="7">
         <v>46149</v>
       </c>
@@ -37830,7 +38170,7 @@
         <v>110546</v>
       </c>
     </row>
-    <row r="1777" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1777" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1777" s="7">
         <v>46149</v>
       </c>
@@ -37847,7 +38187,7 @@
         <v>110547</v>
       </c>
     </row>
-    <row r="1778" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1778" s="7">
         <v>46149</v>
       </c>
@@ -37864,7 +38204,7 @@
         <v>110548</v>
       </c>
     </row>
-    <row r="1779" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1779" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1779" s="7">
         <v>46135</v>
       </c>
@@ -37881,7 +38221,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="1780" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1780" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1780" s="7">
         <v>46135</v>
       </c>
@@ -37898,7 +38238,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="1781" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1781" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1781" s="7">
         <v>46154</v>
       </c>
@@ -37912,10 +38252,10 @@
         <v>24</v>
       </c>
       <c r="E1781" s="2" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="1782" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1782" s="7">
         <v>46154</v>
       </c>
@@ -37929,10 +38269,10 @@
         <v>24</v>
       </c>
       <c r="E1782" s="2" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="1783" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1783" s="7">
         <v>46151</v>
       </c>
@@ -37949,7 +38289,7 @@
         <v>503067</v>
       </c>
     </row>
-    <row r="1784" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1784" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1784" s="7">
         <v>46151</v>
       </c>
@@ -37966,7 +38306,7 @@
         <v>503068</v>
       </c>
     </row>
-    <row r="1785" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1785" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1785" s="7">
         <v>46151</v>
       </c>
@@ -37983,7 +38323,7 @@
         <v>503069</v>
       </c>
     </row>
-    <row r="1786" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1786" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1786" s="7">
         <v>46151</v>
       </c>
@@ -38000,7 +38340,7 @@
         <v>503070</v>
       </c>
     </row>
-    <row r="1787" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1787" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1787" s="7">
         <v>46151</v>
       </c>
@@ -38017,7 +38357,7 @@
         <v>503071</v>
       </c>
     </row>
-    <row r="1788" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1788" s="7">
         <v>46151</v>
       </c>
@@ -38034,7 +38374,7 @@
         <v>503072</v>
       </c>
     </row>
-    <row r="1789" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1789" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1789" s="7">
         <v>46151</v>
       </c>
@@ -38051,7 +38391,7 @@
         <v>503073</v>
       </c>
     </row>
-    <row r="1790" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1790" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1790" s="7">
         <v>46151</v>
       </c>
@@ -38068,7 +38408,7 @@
         <v>503074</v>
       </c>
     </row>
-    <row r="1791" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1791" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1791" s="7">
         <v>46151</v>
       </c>
@@ -38085,7 +38425,7 @@
         <v>503075</v>
       </c>
     </row>
-    <row r="1792" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1792" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1792" s="7">
         <v>46150</v>
       </c>
@@ -38100,6 +38440,12 @@
       </c>
       <c r="E1792" s="1">
         <v>838241</v>
+      </c>
+      <c r="F1792" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1792" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
@@ -38117,6 +38463,12 @@
       </c>
       <c r="E1793" s="1">
         <v>838242</v>
+      </c>
+      <c r="F1793" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1793" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
@@ -39421,6 +39773,12 @@
       <c r="E1868" s="2" t="s">
         <v>1855</v>
       </c>
+      <c r="F1868" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1868" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="1869" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1869" s="7">
@@ -39770,7 +40128,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="1889" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1889" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1889" s="7">
         <v>46153</v>
       </c>
@@ -39787,7 +40145,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="1890" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1890" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1890" s="7">
         <v>46153</v>
       </c>
@@ -39804,7 +40162,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="1891" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1891" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1891" s="7">
         <v>46153</v>
       </c>
@@ -39821,7 +40179,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="1892" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1892" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1892" s="7">
         <v>46153</v>
       </c>
@@ -39838,7 +40196,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="1893" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1893" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1893" s="7">
         <v>46153</v>
       </c>
@@ -39855,7 +40213,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="1894" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1894" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1894" s="7">
         <v>46153</v>
       </c>
@@ -39872,7 +40230,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="1895" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1895" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1895" s="7">
         <v>46153</v>
       </c>
@@ -39888,8 +40246,14 @@
       <c r="E1895" s="2" t="s">
         <v>1915</v>
       </c>
-    </row>
-    <row r="1896" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1895" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1895" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1896" s="7">
         <v>46069</v>
       </c>
@@ -39906,7 +40270,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="1897" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1897" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1897" s="7">
         <v>46146</v>
       </c>
@@ -39923,7 +40287,7 @@
         <v>170716</v>
       </c>
     </row>
-    <row r="1898" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1898" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1898" s="7">
         <v>46146</v>
       </c>
@@ -39940,7 +40304,7 @@
         <v>170717</v>
       </c>
     </row>
-    <row r="1899" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1899" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1899" s="7">
         <v>46146</v>
       </c>
@@ -39957,7 +40321,7 @@
         <v>170718</v>
       </c>
     </row>
-    <row r="1900" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1900" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1900" s="7">
         <v>46146</v>
       </c>
@@ -39974,7 +40338,7 @@
         <v>170719</v>
       </c>
     </row>
-    <row r="1901" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1901" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1901" s="7">
         <v>46146</v>
       </c>
@@ -39991,7 +40355,7 @@
         <v>170720</v>
       </c>
     </row>
-    <row r="1902" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1902" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1902" s="7">
         <v>46146</v>
       </c>
@@ -40008,7 +40372,7 @@
         <v>170721</v>
       </c>
     </row>
-    <row r="1903" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1903" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1903" s="7">
         <v>46146</v>
       </c>
@@ -40025,7 +40389,7 @@
         <v>170722</v>
       </c>
     </row>
-    <row r="1904" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1904" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1904" s="7">
         <v>46146</v>
       </c>
@@ -40146,6 +40510,12 @@
       <c r="E1910" s="2" t="s">
         <v>1413</v>
       </c>
+      <c r="F1910" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1910" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="1911" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1911" s="7">
@@ -40577,7 +40947,7 @@
         <v>46139</v>
       </c>
       <c r="B1936" s="3" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C1936" s="1" t="s">
         <v>37</v>
@@ -40594,7 +40964,7 @@
         <v>46139</v>
       </c>
       <c r="B1937" s="3" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C1937" s="1" t="s">
         <v>37</v>
@@ -40611,7 +40981,7 @@
         <v>46139</v>
       </c>
       <c r="B1938" s="3" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C1938" s="1" t="s">
         <v>37</v>
@@ -40628,7 +40998,7 @@
         <v>46139</v>
       </c>
       <c r="B1939" s="3" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C1939" s="1" t="s">
         <v>37</v>
@@ -40878,6 +41248,12 @@
       </c>
       <c r="E1952" s="2" t="s">
         <v>1517</v>
+      </c>
+      <c r="F1952" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1952" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="1953" spans="1:8" x14ac:dyDescent="0.25">
@@ -41766,7 +42142,7 @@
         <v>4</v>
       </c>
       <c r="E2002" s="2" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
@@ -41783,7 +42159,7 @@
         <v>4</v>
       </c>
       <c r="E2003" s="2" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="2004" spans="1:7" x14ac:dyDescent="0.25">
@@ -41800,7 +42176,7 @@
         <v>4</v>
       </c>
       <c r="E2004" s="2" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="2005" spans="1:7" x14ac:dyDescent="0.25">
@@ -42280,7 +42656,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="2033" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2033" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2033" s="7">
         <v>46129</v>
       </c>
@@ -42297,7 +42673,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="2034" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2034" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2034" s="7">
         <v>46129</v>
       </c>
@@ -42314,7 +42690,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="2035" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2035" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2035" s="7">
         <v>46129</v>
       </c>
@@ -42331,7 +42707,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="2036" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2036" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2036" s="7">
         <v>46129</v>
       </c>
@@ -42348,7 +42724,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="2037" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2037" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2037" s="7">
         <v>46129</v>
       </c>
@@ -42365,7 +42741,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="2038" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2038" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2038" s="7">
         <v>46129</v>
       </c>
@@ -42382,7 +42758,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="2039" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2039" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2039" s="7">
         <v>46129</v>
       </c>
@@ -42399,7 +42775,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="2040" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2040" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2040" s="7">
         <v>46129</v>
       </c>
@@ -42416,7 +42792,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="2041" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2041" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2041" s="7">
         <v>46129</v>
       </c>
@@ -42433,7 +42809,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="2042" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2042" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2042" s="7">
         <v>46129</v>
       </c>
@@ -42450,7 +42826,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="2043" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2043" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2043" s="7">
         <v>46129</v>
       </c>
@@ -42467,7 +42843,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="2044" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2044" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2044" s="7">
         <v>46129</v>
       </c>
@@ -42484,7 +42860,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="2045" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2045" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2045" s="7">
         <v>46119</v>
       </c>
@@ -42501,7 +42877,7 @@
         <v>215238</v>
       </c>
     </row>
-    <row r="2046" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2046" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2046" s="7">
         <v>46128</v>
       </c>
@@ -42517,8 +42893,14 @@
       <c r="E2046" s="1">
         <v>152471</v>
       </c>
-    </row>
-    <row r="2047" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2046" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2046" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2047" s="7">
         <v>46128</v>
       </c>
@@ -42534,8 +42916,14 @@
       <c r="E2047" s="1">
         <v>152472</v>
       </c>
-    </row>
-    <row r="2048" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2047" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2047" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2048" s="7">
         <v>46128</v>
       </c>
@@ -42550,6 +42938,12 @@
       </c>
       <c r="E2048" s="1">
         <v>152473</v>
+      </c>
+      <c r="F2048" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2048" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="2049" spans="1:5" x14ac:dyDescent="0.25">
@@ -46155,16 +46549,16 @@
         <v>46154</v>
       </c>
       <c r="B2258" s="3" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="C2258" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D2258" s="1" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="E2258" s="2" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="2259" spans="1:7" x14ac:dyDescent="0.25">
@@ -46357,7 +46751,7 @@
         <v>24</v>
       </c>
       <c r="E2269" s="2" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="2270" spans="1:7" x14ac:dyDescent="0.25">
@@ -46374,7 +46768,7 @@
         <v>24</v>
       </c>
       <c r="E2270" s="2" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="2271" spans="1:7" x14ac:dyDescent="0.25">
@@ -47312,6 +47706,12 @@
       <c r="E2324" s="2" t="s">
         <v>1154</v>
       </c>
+      <c r="F2324" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2324" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="2325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2325" s="7">
@@ -47329,6 +47729,12 @@
       <c r="E2325" s="2" t="s">
         <v>1155</v>
       </c>
+      <c r="F2325" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2325" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="2326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2326" s="7">
@@ -47783,7 +48189,7 @@
         <v>26</v>
       </c>
       <c r="E2351" s="2" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="2352" spans="1:7" x14ac:dyDescent="0.25">
@@ -47800,7 +48206,7 @@
         <v>26</v>
       </c>
       <c r="E2352" s="2" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="2353" spans="1:7" x14ac:dyDescent="0.25">
@@ -47817,7 +48223,7 @@
         <v>26</v>
       </c>
       <c r="E2353" s="2" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="2354" spans="1:7" x14ac:dyDescent="0.25">
@@ -47834,7 +48240,7 @@
         <v>26</v>
       </c>
       <c r="E2354" s="2" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="2355" spans="1:7" x14ac:dyDescent="0.25">
@@ -47851,7 +48257,7 @@
         <v>26</v>
       </c>
       <c r="E2355" s="2" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="2356" spans="1:7" x14ac:dyDescent="0.25">
@@ -47868,7 +48274,7 @@
         <v>26</v>
       </c>
       <c r="E2356" s="2" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="2357" spans="1:7" x14ac:dyDescent="0.25">
@@ -47885,7 +48291,7 @@
         <v>26</v>
       </c>
       <c r="E2357" s="2" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="2358" spans="1:7" x14ac:dyDescent="0.25">
@@ -47902,7 +48308,7 @@
         <v>26</v>
       </c>
       <c r="E2358" s="2" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G2358" s="7"/>
     </row>
@@ -47920,7 +48326,7 @@
         <v>26</v>
       </c>
       <c r="E2359" s="2" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="2360" spans="1:7" x14ac:dyDescent="0.25">
@@ -47939,6 +48345,12 @@
       <c r="E2360" s="2" t="s">
         <v>1381</v>
       </c>
+      <c r="F2360" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2360" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="2361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2361" s="7">
@@ -48527,6 +48939,12 @@
       </c>
       <c r="E2393" s="1">
         <v>733723</v>
+      </c>
+      <c r="F2393" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2393" s="7">
+        <v>46161</v>
       </c>
     </row>
     <row r="2394" spans="1:7" x14ac:dyDescent="0.25">
@@ -49941,6 +50359,12 @@
       <c r="E2478" s="1">
         <v>312742</v>
       </c>
+      <c r="F2478" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2478" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="2479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2479" s="7">
@@ -50248,7 +50672,7 @@
         <v>46158</v>
       </c>
       <c r="B2496" s="3" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C2496" s="1" t="s">
         <v>17</v>
@@ -50257,7 +50681,7 @@
         <v>15</v>
       </c>
       <c r="E2496" s="2" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F2496" s="1" t="s">
         <v>0</v>
@@ -50271,7 +50695,7 @@
         <v>46158</v>
       </c>
       <c r="B2497" s="3" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C2497" s="1" t="s">
         <v>17</v>
@@ -50280,7 +50704,7 @@
         <v>15</v>
       </c>
       <c r="E2497" s="2" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="2498" spans="1:7" x14ac:dyDescent="0.25">
@@ -50288,7 +50712,7 @@
         <v>46158</v>
       </c>
       <c r="B2498" s="3" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C2498" s="1" t="s">
         <v>17</v>
@@ -50297,7 +50721,7 @@
         <v>15</v>
       </c>
       <c r="E2498" s="2" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="2499" spans="1:7" x14ac:dyDescent="0.25">
@@ -50305,7 +50729,7 @@
         <v>46158</v>
       </c>
       <c r="B2499" s="3" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C2499" s="1" t="s">
         <v>12</v>
@@ -50314,7 +50738,7 @@
         <v>15</v>
       </c>
       <c r="E2499" s="2" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="F2499" s="1" t="s">
         <v>0</v>
@@ -50328,7 +50752,7 @@
         <v>46158</v>
       </c>
       <c r="B2500" s="3" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C2500" s="1" t="s">
         <v>12</v>
@@ -50337,7 +50761,7 @@
         <v>15</v>
       </c>
       <c r="E2500" s="2" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="F2500" s="1" t="s">
         <v>0</v>
@@ -50351,7 +50775,7 @@
         <v>46158</v>
       </c>
       <c r="B2501" s="3" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C2501" s="1" t="s">
         <v>12</v>
@@ -50360,7 +50784,7 @@
         <v>15</v>
       </c>
       <c r="E2501" s="2" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="F2501" s="1" t="s">
         <v>0</v>
@@ -50374,7 +50798,7 @@
         <v>46158</v>
       </c>
       <c r="B2502" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2502" s="1" t="s">
         <v>120</v>
@@ -50397,7 +50821,7 @@
         <v>46158</v>
       </c>
       <c r="B2503" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2503" s="1" t="s">
         <v>120</v>
@@ -50420,7 +50844,7 @@
         <v>46158</v>
       </c>
       <c r="B2504" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2504" s="1" t="s">
         <v>120</v>
@@ -50429,7 +50853,7 @@
         <v>300</v>
       </c>
       <c r="E2504" s="2" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="2505" spans="1:7" x14ac:dyDescent="0.25">
@@ -50437,7 +50861,7 @@
         <v>46158</v>
       </c>
       <c r="B2505" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2505" s="1" t="s">
         <v>120</v>
@@ -50446,7 +50870,7 @@
         <v>300</v>
       </c>
       <c r="E2505" s="2" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="2506" spans="1:7" x14ac:dyDescent="0.25">
@@ -50454,7 +50878,7 @@
         <v>46158</v>
       </c>
       <c r="B2506" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2506" s="1" t="s">
         <v>120</v>
@@ -50463,7 +50887,7 @@
         <v>300</v>
       </c>
       <c r="E2506" s="2" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="2507" spans="1:7" x14ac:dyDescent="0.25">
@@ -50471,7 +50895,7 @@
         <v>46158</v>
       </c>
       <c r="B2507" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2507" s="1" t="s">
         <v>120</v>
@@ -50480,7 +50904,7 @@
         <v>300</v>
       </c>
       <c r="E2507" s="2" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="2508" spans="1:7" x14ac:dyDescent="0.25">
@@ -50488,7 +50912,7 @@
         <v>46158</v>
       </c>
       <c r="B2508" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2508" s="1" t="s">
         <v>120</v>
@@ -50505,7 +50929,7 @@
         <v>46158</v>
       </c>
       <c r="B2509" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2509" s="1" t="s">
         <v>120</v>
@@ -50514,7 +50938,7 @@
         <v>300</v>
       </c>
       <c r="E2509" s="2" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="2510" spans="1:7" x14ac:dyDescent="0.25">
@@ -50522,7 +50946,7 @@
         <v>46158</v>
       </c>
       <c r="B2510" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2510" s="1" t="s">
         <v>120</v>
@@ -50531,7 +50955,7 @@
         <v>300</v>
       </c>
       <c r="E2510" s="2" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="2511" spans="1:7" x14ac:dyDescent="0.25">
@@ -50539,7 +50963,7 @@
         <v>46158</v>
       </c>
       <c r="B2511" s="3" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C2511" s="1" t="s">
         <v>120</v>
@@ -50548,7 +50972,7 @@
         <v>300</v>
       </c>
       <c r="E2511" s="2" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="2512" spans="1:7" x14ac:dyDescent="0.25">
@@ -50556,7 +50980,7 @@
         <v>46158</v>
       </c>
       <c r="B2512" s="3" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C2512" s="1" t="s">
         <v>12</v>
@@ -50565,7 +50989,7 @@
         <v>15</v>
       </c>
       <c r="E2512" s="2" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="2513" spans="1:7" x14ac:dyDescent="0.25">
@@ -50573,7 +50997,7 @@
         <v>46158</v>
       </c>
       <c r="B2513" s="3" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C2513" s="1" t="s">
         <v>12</v>
@@ -50582,7 +51006,7 @@
         <v>15</v>
       </c>
       <c r="E2513" s="2" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="2514" spans="1:7" x14ac:dyDescent="0.25">
@@ -50590,7 +51014,7 @@
         <v>46158</v>
       </c>
       <c r="B2514" s="3" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="C2514" s="1" t="s">
         <v>139</v>
@@ -50613,7 +51037,7 @@
         <v>46158</v>
       </c>
       <c r="B2515" s="3" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="C2515" s="1" t="s">
         <v>139</v>
@@ -50630,7 +51054,7 @@
         <v>46158</v>
       </c>
       <c r="B2516" s="3" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C2516" s="1" t="s">
         <v>139</v>
@@ -50639,7 +51063,7 @@
         <v>4</v>
       </c>
       <c r="E2516" s="2" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="F2516" s="1" t="s">
         <v>0</v>
@@ -50653,7 +51077,7 @@
         <v>46158</v>
       </c>
       <c r="B2517" s="3" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C2517" s="1" t="s">
         <v>139</v>
@@ -50662,7 +51086,7 @@
         <v>4</v>
       </c>
       <c r="E2517" s="2" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="F2517" s="1" t="s">
         <v>0</v>
@@ -50676,7 +51100,7 @@
         <v>46158</v>
       </c>
       <c r="B2518" s="3" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C2518" s="1" t="s">
         <v>6</v>
@@ -50685,7 +51109,7 @@
         <v>36</v>
       </c>
       <c r="E2518" s="2" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="2519" spans="1:7" x14ac:dyDescent="0.25">
@@ -50693,7 +51117,7 @@
         <v>46158</v>
       </c>
       <c r="B2519" s="3" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C2519" s="1" t="s">
         <v>6</v>
@@ -50702,7 +51126,7 @@
         <v>36</v>
       </c>
       <c r="E2519" s="2" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="2520" spans="1:7" x14ac:dyDescent="0.25">
@@ -50710,7 +51134,7 @@
         <v>46158</v>
       </c>
       <c r="B2520" s="3" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C2520" s="1" t="s">
         <v>6</v>
@@ -50719,7 +51143,7 @@
         <v>36</v>
       </c>
       <c r="E2520" s="2" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="F2520" s="1" t="s">
         <v>0</v>
@@ -50733,7 +51157,7 @@
         <v>46158</v>
       </c>
       <c r="B2521" s="3" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C2521" s="1" t="s">
         <v>6</v>
@@ -50742,7 +51166,7 @@
         <v>36</v>
       </c>
       <c r="E2521" s="2" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="F2521" s="1" t="s">
         <v>0</v>
@@ -50756,7 +51180,7 @@
         <v>46158</v>
       </c>
       <c r="B2522" s="3" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="C2522" s="1" t="s">
         <v>12</v>
@@ -50765,7 +51189,7 @@
         <v>10</v>
       </c>
       <c r="E2522" s="2" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="F2522" s="1" t="s">
         <v>0</v>
@@ -50779,16 +51203,16 @@
         <v>46158</v>
       </c>
       <c r="B2523" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2523" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D2523" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="C2523" s="1" t="s">
+      <c r="E2523" s="2" t="s">
         <v>2120</v>
-      </c>
-      <c r="D2523" s="1" t="s">
-        <v>2121</v>
-      </c>
-      <c r="E2523" s="2" t="s">
-        <v>2122</v>
       </c>
       <c r="F2523" s="1" t="s">
         <v>0</v>
@@ -50802,16 +51226,16 @@
         <v>46158</v>
       </c>
       <c r="B2524" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2524" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D2524" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="C2524" s="1" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D2524" s="1" t="s">
+      <c r="E2524" s="2" t="s">
         <v>2121</v>
-      </c>
-      <c r="E2524" s="2" t="s">
-        <v>2123</v>
       </c>
       <c r="F2524" s="1" t="s">
         <v>0</v>
@@ -50825,16 +51249,16 @@
         <v>46158</v>
       </c>
       <c r="B2525" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2525" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D2525" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="C2525" s="1" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D2525" s="1" t="s">
-        <v>2121</v>
-      </c>
       <c r="E2525" s="2" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="2526" spans="1:7" x14ac:dyDescent="0.25">
@@ -50842,16 +51266,16 @@
         <v>46158</v>
       </c>
       <c r="B2526" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2526" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D2526" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="C2526" s="1" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D2526" s="1" t="s">
-        <v>2121</v>
-      </c>
       <c r="E2526" s="2" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2527" spans="1:7" x14ac:dyDescent="0.25">
@@ -50859,16 +51283,16 @@
         <v>46158</v>
       </c>
       <c r="B2527" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2527" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D2527" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="C2527" s="1" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D2527" s="1" t="s">
-        <v>2121</v>
-      </c>
       <c r="E2527" s="2" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="2528" spans="1:7" x14ac:dyDescent="0.25">
@@ -50876,24 +51300,24 @@
         <v>46158</v>
       </c>
       <c r="B2528" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2528" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D2528" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="C2528" s="1" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D2528" s="1" t="s">
-        <v>2121</v>
-      </c>
       <c r="E2528" s="2" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="2529" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2529" s="7">
         <v>46158</v>
       </c>
       <c r="B2529" s="3" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="C2529" s="1" t="s">
         <v>12</v>
@@ -50902,15 +51326,15 @@
         <v>10</v>
       </c>
       <c r="E2529" s="2" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="2530" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2530" s="7">
         <v>46158</v>
       </c>
       <c r="B2530" s="3" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="C2530" s="1" t="s">
         <v>12</v>
@@ -50919,15 +51343,15 @@
         <v>10</v>
       </c>
       <c r="E2530" s="2" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="2531" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2531" s="7">
         <v>46158</v>
       </c>
       <c r="B2531" s="3" t="s">
-        <v>2130</v>
+        <v>2225</v>
       </c>
       <c r="C2531" s="1" t="s">
         <v>12</v>
@@ -50936,15 +51360,21 @@
         <v>26</v>
       </c>
       <c r="E2531" s="2" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="2532" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2129</v>
+      </c>
+      <c r="F2531" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2531" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2532" s="7">
         <v>46158</v>
       </c>
       <c r="B2532" s="3" t="s">
-        <v>2130</v>
+        <v>2225</v>
       </c>
       <c r="C2532" s="1" t="s">
         <v>12</v>
@@ -50953,10 +51383,10 @@
         <v>26</v>
       </c>
       <c r="E2532" s="2" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="2533" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2533" s="7">
         <v>46158</v>
       </c>
@@ -50970,10 +51400,10 @@
         <v>13</v>
       </c>
       <c r="E2533" s="2" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="2534" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2534" s="7">
         <v>46158</v>
       </c>
@@ -50987,10 +51417,10 @@
         <v>13</v>
       </c>
       <c r="E2534" s="2" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="2535" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2535" s="7">
         <v>46158</v>
       </c>
@@ -51004,10 +51434,10 @@
         <v>13</v>
       </c>
       <c r="E2535" s="2" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="2536" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2536" s="7">
         <v>46158</v>
       </c>
@@ -51021,10 +51451,10 @@
         <v>13</v>
       </c>
       <c r="E2536" s="2" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="2537" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2537" s="7">
         <v>46158</v>
       </c>
@@ -51038,10 +51468,10 @@
         <v>13</v>
       </c>
       <c r="E2537" s="2" t="s">
-        <v>2137</v>
-      </c>
-    </row>
-    <row r="2538" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2538" s="7">
         <v>46158</v>
       </c>
@@ -51055,10 +51485,10 @@
         <v>13</v>
       </c>
       <c r="E2538" s="2" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="2539" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2539" s="7">
         <v>46158</v>
       </c>
@@ -51072,10 +51502,10 @@
         <v>13</v>
       </c>
       <c r="E2539" s="2" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="2540" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2540" s="7">
         <v>46158</v>
       </c>
@@ -51089,10 +51519,10 @@
         <v>13</v>
       </c>
       <c r="E2540" s="2" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="2541" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2541" s="7">
         <v>46158</v>
       </c>
@@ -51106,10 +51536,10 @@
         <v>13</v>
       </c>
       <c r="E2541" s="2" t="s">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="2542" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2542" s="7">
         <v>46158</v>
       </c>
@@ -51123,10 +51553,10 @@
         <v>13</v>
       </c>
       <c r="E2542" s="2" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="2543" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2543" s="7">
         <v>46158</v>
       </c>
@@ -51143,7 +51573,7 @@
         <v>471051</v>
       </c>
     </row>
-    <row r="2544" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2544" s="7">
         <v>46158</v>
       </c>
@@ -51312,6 +51742,12 @@
       <c r="E2553" s="1">
         <v>334915</v>
       </c>
+      <c r="F2553" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2553" s="7">
+        <v>46161</v>
+      </c>
     </row>
     <row r="2554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2554" s="7">
@@ -51353,7 +51789,7 @@
         <v>46160</v>
       </c>
       <c r="H2555" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="2556" spans="1:8" x14ac:dyDescent="0.25">
@@ -51393,7 +51829,7 @@
         <v>24</v>
       </c>
       <c r="E2557" s="2" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="F2557" s="1" t="s">
         <v>0</v>
@@ -51402,7 +51838,7 @@
         <v>46160</v>
       </c>
       <c r="H2557" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="2558" spans="1:8" x14ac:dyDescent="0.25">
@@ -51410,7 +51846,7 @@
         <v>46160</v>
       </c>
       <c r="B2558" s="3" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="C2558" s="1" t="s">
         <v>25</v>
@@ -51433,7 +51869,7 @@
         <v>46160</v>
       </c>
       <c r="B2559" s="3" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C2559" s="1" t="s">
         <v>25</v>
@@ -51442,7 +51878,7 @@
         <v>4</v>
       </c>
       <c r="E2559" s="2" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="F2559" s="1" t="s">
         <v>0</v>
@@ -51451,7 +51887,7 @@
         <v>46160</v>
       </c>
       <c r="H2559" s="1" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="2560" spans="1:8" x14ac:dyDescent="0.25">
@@ -51459,7 +51895,7 @@
         <v>46160</v>
       </c>
       <c r="B2560" s="3" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C2560" s="1" t="s">
         <v>25</v>
@@ -51468,7 +51904,7 @@
         <v>4</v>
       </c>
       <c r="E2560" s="2" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="F2560" s="1" t="s">
         <v>0</v>
@@ -51477,7 +51913,7 @@
         <v>46160</v>
       </c>
       <c r="H2560" s="1" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="2561" spans="1:7" x14ac:dyDescent="0.25">
@@ -51485,7 +51921,7 @@
         <v>46160</v>
       </c>
       <c r="B2561" s="3" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C2561" s="1" t="s">
         <v>54</v>
@@ -51494,7 +51930,7 @@
         <v>16</v>
       </c>
       <c r="E2561" s="2" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="F2561" s="1" t="s">
         <v>0</v>
@@ -51508,7 +51944,7 @@
         <v>46160</v>
       </c>
       <c r="B2562" s="3" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C2562" s="1" t="s">
         <v>54</v>
@@ -51517,7 +51953,7 @@
         <v>16</v>
       </c>
       <c r="E2562" s="2" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="F2562" s="1" t="s">
         <v>0</v>
@@ -51531,7 +51967,7 @@
         <v>46160</v>
       </c>
       <c r="B2563" s="3" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C2563" s="1" t="s">
         <v>54</v>
@@ -51540,7 +51976,7 @@
         <v>16</v>
       </c>
       <c r="E2563" s="2" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="G2563" s="7"/>
     </row>
@@ -51549,7 +51985,7 @@
         <v>46160</v>
       </c>
       <c r="B2564" s="3" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C2564" s="1" t="s">
         <v>54</v>
@@ -51558,7 +51994,7 @@
         <v>16</v>
       </c>
       <c r="E2564" s="2" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="2565" spans="1:7" x14ac:dyDescent="0.25">
@@ -51566,7 +52002,7 @@
         <v>46160</v>
       </c>
       <c r="B2565" s="3" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C2565" s="1" t="s">
         <v>54</v>
@@ -51575,7 +52011,7 @@
         <v>16</v>
       </c>
       <c r="E2565" s="2" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="2566" spans="1:7" x14ac:dyDescent="0.25">
@@ -51583,7 +52019,7 @@
         <v>46160</v>
       </c>
       <c r="B2566" s="3" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="C2566" s="1" t="s">
         <v>37</v>
@@ -51592,7 +52028,7 @@
         <v>7</v>
       </c>
       <c r="E2566" s="2" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="F2566" s="1" t="s">
         <v>0</v>
@@ -51606,7 +52042,7 @@
         <v>46160</v>
       </c>
       <c r="B2567" s="3" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="C2567" s="1" t="s">
         <v>37</v>
@@ -51615,7 +52051,7 @@
         <v>7</v>
       </c>
       <c r="E2567" s="2" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="2568" spans="1:7" x14ac:dyDescent="0.25">
@@ -51632,7 +52068,7 @@
         <v>24</v>
       </c>
       <c r="E2568" s="2" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="2569" spans="1:7" x14ac:dyDescent="0.25">
@@ -51649,7 +52085,7 @@
         <v>24</v>
       </c>
       <c r="E2569" s="2" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="2570" spans="1:7" x14ac:dyDescent="0.25">
@@ -51666,7 +52102,7 @@
         <v>24</v>
       </c>
       <c r="E2570" s="2" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="2571" spans="1:7" x14ac:dyDescent="0.25">
@@ -51683,7 +52119,7 @@
         <v>24</v>
       </c>
       <c r="E2571" s="2" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="2572" spans="1:7" x14ac:dyDescent="0.25">
@@ -51700,7 +52136,7 @@
         <v>24</v>
       </c>
       <c r="E2572" s="2" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="2573" spans="1:7" x14ac:dyDescent="0.25">
@@ -51708,7 +52144,7 @@
         <v>46160</v>
       </c>
       <c r="B2573" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2573" s="1" t="s">
         <v>1589</v>
@@ -51726,7 +52162,7 @@
         <v>46160</v>
       </c>
       <c r="B2574" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2574" s="1" t="s">
         <v>1589</v>
@@ -51749,7 +52185,7 @@
         <v>46160</v>
       </c>
       <c r="B2575" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2575" s="1" t="s">
         <v>1589</v>
@@ -51772,7 +52208,7 @@
         <v>46160</v>
       </c>
       <c r="B2576" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2576" s="1" t="s">
         <v>1589</v>
@@ -51795,7 +52231,7 @@
         <v>46160</v>
       </c>
       <c r="B2577" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2577" s="1" t="s">
         <v>1589</v>
@@ -51804,7 +52240,7 @@
         <v>4</v>
       </c>
       <c r="E2577" s="2" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="F2577" s="1" t="s">
         <v>0</v>
@@ -52022,7 +52458,7 @@
         <v>46160</v>
       </c>
       <c r="B2590" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2590" s="1" t="s">
         <v>12</v>
@@ -52039,7 +52475,7 @@
         <v>46160</v>
       </c>
       <c r="B2591" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2591" s="1" t="s">
         <v>12</v>
@@ -52056,7 +52492,7 @@
         <v>46160</v>
       </c>
       <c r="B2592" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2592" s="1" t="s">
         <v>12</v>
@@ -52073,7 +52509,7 @@
         <v>46160</v>
       </c>
       <c r="B2593" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2593" s="1" t="s">
         <v>12</v>
@@ -52090,7 +52526,7 @@
         <v>46160</v>
       </c>
       <c r="B2594" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2594" s="1" t="s">
         <v>12</v>
@@ -52107,7 +52543,7 @@
         <v>46160</v>
       </c>
       <c r="B2595" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2595" s="1" t="s">
         <v>12</v>
@@ -52124,7 +52560,7 @@
         <v>46160</v>
       </c>
       <c r="B2596" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2596" s="1" t="s">
         <v>12</v>
@@ -52141,7 +52577,7 @@
         <v>46160</v>
       </c>
       <c r="B2597" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2597" s="1" t="s">
         <v>12</v>
@@ -52158,7 +52594,7 @@
         <v>46160</v>
       </c>
       <c r="B2598" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2598" s="1" t="s">
         <v>12</v>
@@ -52175,7 +52611,7 @@
         <v>46160</v>
       </c>
       <c r="B2599" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2599" s="1" t="s">
         <v>12</v>
@@ -52192,7 +52628,7 @@
         <v>46160</v>
       </c>
       <c r="B2600" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2600" s="1" t="s">
         <v>12</v>
@@ -52209,7 +52645,7 @@
         <v>46160</v>
       </c>
       <c r="B2601" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2601" s="1" t="s">
         <v>12</v>
@@ -52226,7 +52662,7 @@
         <v>46160</v>
       </c>
       <c r="B2602" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2602" s="1" t="s">
         <v>12</v>
@@ -52243,7 +52679,7 @@
         <v>46160</v>
       </c>
       <c r="B2603" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2603" s="1" t="s">
         <v>12</v>
@@ -52260,7 +52696,7 @@
         <v>46160</v>
       </c>
       <c r="B2604" s="3" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C2604" s="1" t="s">
         <v>12</v>
@@ -52277,7 +52713,7 @@
         <v>46160</v>
       </c>
       <c r="B2605" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2605" s="1" t="s">
         <v>1589</v>
@@ -52294,7 +52730,7 @@
         <v>46160</v>
       </c>
       <c r="B2606" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2606" s="1" t="s">
         <v>1589</v>
@@ -52311,7 +52747,7 @@
         <v>46160</v>
       </c>
       <c r="B2607" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2607" s="1" t="s">
         <v>1589</v>
@@ -52328,7 +52764,7 @@
         <v>46160</v>
       </c>
       <c r="B2608" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2608" s="1" t="s">
         <v>1589</v>
@@ -52345,7 +52781,7 @@
         <v>46160</v>
       </c>
       <c r="B2609" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2609" s="1" t="s">
         <v>1589</v>
@@ -52362,7 +52798,7 @@
         <v>46160</v>
       </c>
       <c r="B2610" s="3" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C2610" s="1" t="s">
         <v>1589</v>
@@ -52388,7 +52824,7 @@
         <v>26</v>
       </c>
       <c r="E2611" s="2" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="2612" spans="1:5" x14ac:dyDescent="0.25">
@@ -52405,7 +52841,7 @@
         <v>26</v>
       </c>
       <c r="E2612" s="2" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="2613" spans="1:5" x14ac:dyDescent="0.25">
@@ -52422,7 +52858,7 @@
         <v>26</v>
       </c>
       <c r="E2613" s="2" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="2614" spans="1:5" x14ac:dyDescent="0.25">
@@ -52439,7 +52875,7 @@
         <v>26</v>
       </c>
       <c r="E2614" s="2" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="2615" spans="1:5" x14ac:dyDescent="0.25">
@@ -52456,7 +52892,7 @@
         <v>26</v>
       </c>
       <c r="E2615" s="2" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="2616" spans="1:5" x14ac:dyDescent="0.25">
@@ -52473,7 +52909,7 @@
         <v>26</v>
       </c>
       <c r="E2616" s="2" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="2617" spans="1:5" x14ac:dyDescent="0.25">
@@ -52490,7 +52926,7 @@
         <v>26</v>
       </c>
       <c r="E2617" s="2" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="2618" spans="1:5" x14ac:dyDescent="0.25">
@@ -52507,7 +52943,7 @@
         <v>26</v>
       </c>
       <c r="E2618" s="2" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="2619" spans="1:5" x14ac:dyDescent="0.25">
@@ -52524,7 +52960,7 @@
         <v>26</v>
       </c>
       <c r="E2619" s="2" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="2620" spans="1:5" x14ac:dyDescent="0.25">
@@ -52541,7 +52977,7 @@
         <v>26</v>
       </c>
       <c r="E2620" s="2" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="2621" spans="1:5" x14ac:dyDescent="0.25">
@@ -52549,7 +52985,7 @@
         <v>46160</v>
       </c>
       <c r="B2621" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2621" s="1" t="s">
         <v>1589</v>
@@ -52558,7 +52994,7 @@
         <v>4</v>
       </c>
       <c r="E2621" s="2" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="2622" spans="1:5" x14ac:dyDescent="0.25">
@@ -52566,7 +53002,7 @@
         <v>46160</v>
       </c>
       <c r="B2622" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2622" s="1" t="s">
         <v>1589</v>
@@ -52575,7 +53011,7 @@
         <v>4</v>
       </c>
       <c r="E2622" s="2" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="2623" spans="1:5" x14ac:dyDescent="0.25">
@@ -52583,7 +53019,7 @@
         <v>46160</v>
       </c>
       <c r="B2623" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2623" s="1" t="s">
         <v>1589</v>
@@ -52592,7 +53028,7 @@
         <v>4</v>
       </c>
       <c r="E2623" s="2" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="2624" spans="1:5" x14ac:dyDescent="0.25">
@@ -52600,16 +53036,16 @@
         <v>46160</v>
       </c>
       <c r="B2624" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2624" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="D2624" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2624" s="2" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="2625" spans="1:8" x14ac:dyDescent="0.25">
@@ -52617,7 +53053,7 @@
         <v>46160</v>
       </c>
       <c r="B2625" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2625" s="1" t="s">
         <v>1589</v>
@@ -52626,7 +53062,7 @@
         <v>4</v>
       </c>
       <c r="E2625" s="2" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="2626" spans="1:8" x14ac:dyDescent="0.25">
@@ -52634,7 +53070,7 @@
         <v>46160</v>
       </c>
       <c r="B2626" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2626" s="1" t="s">
         <v>1589</v>
@@ -52643,7 +53079,7 @@
         <v>4</v>
       </c>
       <c r="E2626" s="2" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="2627" spans="1:8" x14ac:dyDescent="0.25">
@@ -52651,7 +53087,7 @@
         <v>46160</v>
       </c>
       <c r="B2627" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2627" s="1" t="s">
         <v>1589</v>
@@ -52660,7 +53096,7 @@
         <v>4</v>
       </c>
       <c r="E2627" s="2" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="2628" spans="1:8" x14ac:dyDescent="0.25">
@@ -52668,7 +53104,7 @@
         <v>46160</v>
       </c>
       <c r="B2628" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2628" s="1" t="s">
         <v>1589</v>
@@ -52677,7 +53113,7 @@
         <v>4</v>
       </c>
       <c r="E2628" s="2" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="2629" spans="1:8" x14ac:dyDescent="0.25">
@@ -52685,7 +53121,7 @@
         <v>46160</v>
       </c>
       <c r="B2629" s="3" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C2629" s="1" t="s">
         <v>1589</v>
@@ -52694,7 +53130,7 @@
         <v>4</v>
       </c>
       <c r="E2629" s="2" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="2630" spans="1:8" x14ac:dyDescent="0.25">
@@ -52711,7 +53147,7 @@
         <v>24</v>
       </c>
       <c r="E2630" s="2" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="F2630" s="1" t="s">
         <v>0</v>
@@ -52734,7 +53170,7 @@
         <v>24</v>
       </c>
       <c r="E2631" s="2" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="F2631" s="1" t="s">
         <v>0</v>
@@ -52748,7 +53184,7 @@
         <v>46160</v>
       </c>
       <c r="B2632" s="3" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="C2632" s="1" t="s">
         <v>12</v>
@@ -52757,7 +53193,7 @@
         <v>24</v>
       </c>
       <c r="E2632" s="2" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="F2632" s="1" t="s">
         <v>0</v>
@@ -52766,7 +53202,7 @@
         <v>46160</v>
       </c>
       <c r="H2632" s="1" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="2633" spans="1:8" x14ac:dyDescent="0.25">
@@ -52774,7 +53210,7 @@
         <v>46160</v>
       </c>
       <c r="B2633" s="3" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="C2633" s="1" t="s">
         <v>12</v>
@@ -52783,7 +53219,7 @@
         <v>82</v>
       </c>
       <c r="E2633" s="2" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="F2633" s="1" t="s">
         <v>0</v>
@@ -52792,7 +53228,7 @@
         <v>46160</v>
       </c>
       <c r="H2633" s="1" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="2634" spans="1:8" x14ac:dyDescent="0.25">
@@ -52914,7 +53350,7 @@
         <v>821145</v>
       </c>
     </row>
-    <row r="2641" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2641" s="7">
         <v>46130</v>
       </c>
@@ -52931,7 +53367,7 @@
         <v>821146</v>
       </c>
     </row>
-    <row r="2642" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2642" s="7">
         <v>46130</v>
       </c>
@@ -52948,7 +53384,7 @@
         <v>821147</v>
       </c>
     </row>
-    <row r="2643" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2643" s="7">
         <v>46130</v>
       </c>
@@ -52965,12 +53401,12 @@
         <v>821148</v>
       </c>
     </row>
-    <row r="2644" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2644" s="7">
         <v>46130</v>
       </c>
       <c r="B2644" s="3" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C2644" s="1" t="s">
         <v>37</v>
@@ -52979,15 +53415,15 @@
         <v>49</v>
       </c>
       <c r="E2644" s="2" t="s">
-        <v>2199</v>
-      </c>
-    </row>
-    <row r="2645" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2645" s="7">
         <v>46130</v>
       </c>
       <c r="B2645" s="3" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C2645" s="1" t="s">
         <v>37</v>
@@ -52996,15 +53432,15 @@
         <v>49</v>
       </c>
       <c r="E2645" s="2" t="s">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="2646" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2646" s="7">
         <v>46130</v>
       </c>
       <c r="B2646" s="3" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C2646" s="1" t="s">
         <v>37</v>
@@ -53013,15 +53449,15 @@
         <v>49</v>
       </c>
       <c r="E2646" s="2" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="2647" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2647" s="7">
         <v>46130</v>
       </c>
       <c r="B2647" s="3" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C2647" s="1" t="s">
         <v>37</v>
@@ -53030,15 +53466,15 @@
         <v>49</v>
       </c>
       <c r="E2647" s="2" t="s">
-        <v>2202</v>
-      </c>
-    </row>
-    <row r="2648" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2648" s="7">
         <v>46130</v>
       </c>
       <c r="B2648" s="3" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C2648" s="1" t="s">
         <v>37</v>
@@ -53047,15 +53483,15 @@
         <v>49</v>
       </c>
       <c r="E2648" s="2" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="2649" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2649" s="7">
         <v>46130</v>
       </c>
       <c r="B2649" s="3" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C2649" s="1" t="s">
         <v>37</v>
@@ -53064,10 +53500,10 @@
         <v>49</v>
       </c>
       <c r="E2649" s="2" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="2650" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2650" s="7">
         <v>46160</v>
       </c>
@@ -53084,7 +53520,7 @@
         <v>377629</v>
       </c>
     </row>
-    <row r="2651" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2651" s="7">
         <v>46160</v>
       </c>
@@ -53101,7 +53537,7 @@
         <v>377630</v>
       </c>
     </row>
-    <row r="2652" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2652" s="7">
         <v>46160</v>
       </c>
@@ -53118,7 +53554,7 @@
         <v>377631</v>
       </c>
     </row>
-    <row r="2653" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2653" s="7">
         <v>46160</v>
       </c>
@@ -53135,7 +53571,7 @@
         <v>377632</v>
       </c>
     </row>
-    <row r="2654" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2654" s="7">
         <v>46160</v>
       </c>
@@ -53152,17 +53588,1556 @@
         <v>482463</v>
       </c>
     </row>
-    <row r="2659" spans="3:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2659" s="18"/>
-    </row>
-    <row r="1045562" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1045562" s="7"/>
-    </row>
-    <row r="1045572" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1045572" s="7"/>
-    </row>
-    <row r="1048575" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1048575" s="7"/>
+    <row r="2655" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2655" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2655" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2655" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2655" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2655" s="1">
+        <v>207833</v>
+      </c>
+      <c r="F2655" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2655" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2656" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2656" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="C2656" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2656" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2656" s="1">
+        <v>381710</v>
+      </c>
+      <c r="F2656" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2656" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2657" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2657" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="C2657" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2657" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2657" s="1">
+        <v>381711</v>
+      </c>
+      <c r="F2657" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2657" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2658" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2658" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C2658" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2658" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2658" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F2658" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2658" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2659" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2659" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C2659" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2659" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2659" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G2659" s="7"/>
+    </row>
+    <row r="2660" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2660" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2660" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2660" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2660" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2660" s="1">
+        <v>218028</v>
+      </c>
+      <c r="F2660" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2660" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2661" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2661" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2661" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2661" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2661" s="1">
+        <v>218029</v>
+      </c>
+      <c r="F2661" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2661" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2662" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2662" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C2662" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2662" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2662" s="2" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2663" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2663" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2663" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2663" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2663" s="1">
+        <v>207834</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2664" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2664" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2664" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2664" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2664" s="1">
+        <v>207835</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2665" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2665" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2665" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2665" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2665" s="1">
+        <v>207836</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2666" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2666" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2666" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2666" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2666" s="1">
+        <v>207837</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2667" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2667" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2667" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2667" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2667" s="1">
+        <v>207838</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2668" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2668" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2668" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2668" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2668" s="1">
+        <v>207839</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2669" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2669" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2669" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2669" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2669" s="1">
+        <v>207840</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2670" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2670" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2670" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2670" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2670" s="1">
+        <v>207841</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2671" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2671" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C2671" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2671" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2671" s="1">
+        <v>207842</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2672" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2672" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C2672" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2672" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2672" s="2" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2673" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2673" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C2673" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2673" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2673" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2674" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2674" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C2674" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2674" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2674" s="2" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2675" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2675" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C2675" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2675" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2675" s="2" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2676" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2676" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C2676" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2676" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2676" s="2" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2677" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2677" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C2677" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2677" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2677" s="2" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2678" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2678" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2678" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2678" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2678" s="1">
+        <v>128796</v>
+      </c>
+      <c r="F2678" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2678" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2679" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2679" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2679" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2679" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2679" s="1">
+        <v>128795</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2680" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2680" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2680" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2680" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2680" s="1">
+        <v>128794</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2681" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2681" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2681" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2681" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2681" s="1">
+        <v>128793</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2682" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2682" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2682" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2682" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2682" s="1">
+        <v>128792</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2683" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2683" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2683" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2683" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2683" s="1">
+        <v>128791</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2684" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2684" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2684" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2684" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2684" s="1">
+        <v>128790</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2685" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2685" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2685" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2685" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2685" s="1">
+        <v>128789</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2686" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2686" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2686" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2686" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2686" s="1">
+        <v>128798</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2687" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2687" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C2687" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2687" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2687" s="1">
+        <v>128787</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2688" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2688" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C2688" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2688" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2688" s="2" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2689" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2689" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2689" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2689" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2689" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2690" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2690" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2690" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2690" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2690" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2691" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2691" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2691" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2691" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2691" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2692" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2692" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2692" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2692" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2692" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2693" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2693" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2693" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2693" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2693" s="2" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2694" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2694" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2694" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2694" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2694" s="2" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2695" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2695" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C2695" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2695" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2695" s="2" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2696" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2696" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C2696" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2696" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2696" s="2" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2697" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2697" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C2697" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2697" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2697" s="2" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2698" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2698" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C2698" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2698" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2698" s="2" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2699" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2699" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2699" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2699" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2699" s="1">
+        <v>218030</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2700" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2700" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2700" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2700" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2700" s="1">
+        <v>218031</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2701" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2701" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2701" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2701" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2701" s="1">
+        <v>218032</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2702" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2702" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C2702" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2702" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2702" s="1">
+        <v>218033</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2703" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2703" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2703" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2703" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2703" s="1">
+        <v>706982</v>
+      </c>
+      <c r="F2703" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2703" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2704" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2704" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2704" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2704" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2704" s="1">
+        <v>706983</v>
+      </c>
+      <c r="G2704" s="7"/>
+    </row>
+    <row r="2705" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2705" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2705" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C2705" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2705" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2705" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F2705" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2705" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2706" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2706" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C2706" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2706" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2706" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F2706" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2706" s="7">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2707" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2707" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2707" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2707" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2707" s="1">
+        <v>706984</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2708" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2708" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2708" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2708" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2708" s="1">
+        <v>706985</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2709" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2709" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2709" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2709" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2709" s="1">
+        <v>706986</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2710" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2710" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2710" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2710" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2710" s="1">
+        <v>706987</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2711" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2711" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2711" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2711" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2711" s="1">
+        <v>706988</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2712" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2712" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2712" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2712" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2712" s="1">
+        <v>706989</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2713" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2713" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C2713" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2713" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2713" s="1">
+        <v>706990</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2714" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2714" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C2714" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2714" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2714" s="2" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2715" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2715" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C2715" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2715" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2715" s="2" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2716" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2716" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C2716" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2716" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2716" s="2" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2717" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2717" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2717" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2717" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2717" s="2" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2718" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2718" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2718" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2718" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2718" s="1">
+        <v>458737</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2719" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2719" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2719" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2719" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2719" s="1">
+        <v>458738</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2720" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2720" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2720" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2720" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2720" s="1">
+        <v>458739</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2721" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2721" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2721" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2721" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2721" s="1">
+        <v>458740</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2722" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2722" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2722" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2722" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2722" s="1">
+        <v>458741</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2723" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2723" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2723" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2723" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2723" s="1">
+        <v>458742</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2724" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2724" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2724" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2724" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2724" s="1">
+        <v>458743</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2725" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2725" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2725" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2725" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2725" s="1">
+        <v>458744</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2726" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2726" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2726" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2726" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2726" s="1">
+        <v>458745</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2727" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2727" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2727" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2727" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2727" s="1">
+        <v>458746</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2728" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2728" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2728" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2728" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2728" s="1">
+        <v>458747</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2729" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2729" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2729" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2729" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2729" s="1">
+        <v>458748</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2730" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2730" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2730" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2730" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2730" s="1">
+        <v>458749</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2731" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2731" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2731" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2731" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2731" s="1">
+        <v>458750</v>
+      </c>
+    </row>
+    <row r="2732" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2732" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2732" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2732" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2732" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2732" s="1">
+        <v>458751</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2733" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2733" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2733" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2733" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2733" s="1">
+        <v>458752</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2734" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2734" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2734" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2734" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2734" s="1">
+        <v>458753</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2735" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2735" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2735" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2735" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2735" s="1">
+        <v>458754</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2736" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2736" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2736" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2736" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2736" s="1">
+        <v>458755</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2737" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2737" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C2737" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2737" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2737" s="1">
+        <v>458756</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2738" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2738" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2738" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2738" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2738" s="2" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2739" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2739" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C2739" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2739" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2739" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="F2739" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2739" s="7">
+        <v>46161</v>
+      </c>
+      <c r="H2739" s="1" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2740" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B2740" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C2740" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2740" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2740" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F2740" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2740" s="7">
+        <v>46161</v>
+      </c>
+      <c r="H2740" s="1" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="1045560" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1045560" s="7"/>
+    </row>
+    <row r="1045570" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1045570" s="7"/>
+    </row>
+    <row r="1048573" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1048573" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H172">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8537BAA0-3F18-4D4E-8673-25E9D6BDBA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BDF049-29A8-4B90-A368-DA252BEFFBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$3034</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$3177</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11641" uniqueCount="2542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12223" uniqueCount="2642">
   <si>
     <t>USE</t>
   </si>
@@ -7640,6 +7640,306 @@
   </si>
   <si>
     <t xml:space="preserve">       </t>
+  </si>
+  <si>
+    <t>SHUKLA MEDICAL STORE</t>
+  </si>
+  <si>
+    <t>019801</t>
+  </si>
+  <si>
+    <t>TANEJA TRADERS</t>
+  </si>
+  <si>
+    <t>16702/-</t>
+  </si>
+  <si>
+    <t>34985/-</t>
+  </si>
+  <si>
+    <t>007633</t>
+  </si>
+  <si>
+    <t>55746/-</t>
+  </si>
+  <si>
+    <t>DHAWAN SONS</t>
+  </si>
+  <si>
+    <t>18386/-</t>
+  </si>
+  <si>
+    <t>GOBIND MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>004002</t>
+  </si>
+  <si>
+    <t>50298/-</t>
+  </si>
+  <si>
+    <t>057527</t>
+  </si>
+  <si>
+    <t>057528</t>
+  </si>
+  <si>
+    <t>057526</t>
+  </si>
+  <si>
+    <t>019802</t>
+  </si>
+  <si>
+    <t>019803</t>
+  </si>
+  <si>
+    <t>019804</t>
+  </si>
+  <si>
+    <t>019805</t>
+  </si>
+  <si>
+    <t>019806</t>
+  </si>
+  <si>
+    <t>019807</t>
+  </si>
+  <si>
+    <t>019808</t>
+  </si>
+  <si>
+    <t>019809</t>
+  </si>
+  <si>
+    <t>019810</t>
+  </si>
+  <si>
+    <t>019811</t>
+  </si>
+  <si>
+    <t>019812</t>
+  </si>
+  <si>
+    <t>019813</t>
+  </si>
+  <si>
+    <t>019814</t>
+  </si>
+  <si>
+    <t>019815</t>
+  </si>
+  <si>
+    <t>019816</t>
+  </si>
+  <si>
+    <t>019817</t>
+  </si>
+  <si>
+    <t>019818</t>
+  </si>
+  <si>
+    <t>019819</t>
+  </si>
+  <si>
+    <t>019820</t>
+  </si>
+  <si>
+    <t>TARA MEDICAL AGENCY</t>
+  </si>
+  <si>
+    <t>CL MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>PREETI MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>003076</t>
+  </si>
+  <si>
+    <t>VRINDA MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>042845</t>
+  </si>
+  <si>
+    <t>042846</t>
+  </si>
+  <si>
+    <t>042847</t>
+  </si>
+  <si>
+    <t>042848</t>
+  </si>
+  <si>
+    <t>GURU KRIPA MEDICOS</t>
+  </si>
+  <si>
+    <t>008426</t>
+  </si>
+  <si>
+    <t>008427</t>
+  </si>
+  <si>
+    <t>006485</t>
+  </si>
+  <si>
+    <t>HURIA MEDICAL STORE</t>
+  </si>
+  <si>
+    <t>NEW JITENDAR AND SONS MEDICAL STORE</t>
+  </si>
+  <si>
+    <t>003305</t>
+  </si>
+  <si>
+    <t>VAISNOO TRADERS</t>
+  </si>
+  <si>
+    <t>GUPTA BROTHER</t>
+  </si>
+  <si>
+    <t>007551</t>
+  </si>
+  <si>
+    <t>007552</t>
+  </si>
+  <si>
+    <t>007553</t>
+  </si>
+  <si>
+    <t>007554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADAUN </t>
+  </si>
+  <si>
+    <t>003306</t>
+  </si>
+  <si>
+    <t>003307</t>
+  </si>
+  <si>
+    <t>003308</t>
+  </si>
+  <si>
+    <t>003309</t>
+  </si>
+  <si>
+    <t>NEELU PHARMA AGENCIS</t>
+  </si>
+  <si>
+    <t>BARAILLY</t>
+  </si>
+  <si>
+    <t>090073</t>
+  </si>
+  <si>
+    <t>090074</t>
+  </si>
+  <si>
+    <t>090075</t>
+  </si>
+  <si>
+    <t>090076</t>
+  </si>
+  <si>
+    <t>008428</t>
+  </si>
+  <si>
+    <t>008429</t>
+  </si>
+  <si>
+    <t>008430</t>
+  </si>
+  <si>
+    <t>006486</t>
+  </si>
+  <si>
+    <t>006487</t>
+  </si>
+  <si>
+    <t>006488</t>
+  </si>
+  <si>
+    <t>006489</t>
+  </si>
+  <si>
+    <t>006490</t>
+  </si>
+  <si>
+    <t>003077</t>
+  </si>
+  <si>
+    <t>003078</t>
+  </si>
+  <si>
+    <t>003079</t>
+  </si>
+  <si>
+    <t>003080</t>
+  </si>
+  <si>
+    <t>003081</t>
+  </si>
+  <si>
+    <t>003082</t>
+  </si>
+  <si>
+    <t>003083</t>
+  </si>
+  <si>
+    <t>042849</t>
+  </si>
+  <si>
+    <t>042850</t>
+  </si>
+  <si>
+    <t>042851</t>
+  </si>
+  <si>
+    <t>042840</t>
+  </si>
+  <si>
+    <t>042841</t>
+  </si>
+  <si>
+    <t>042842</t>
+  </si>
+  <si>
+    <t>042843</t>
+  </si>
+  <si>
+    <t>042844</t>
+  </si>
+  <si>
+    <t>042835</t>
+  </si>
+  <si>
+    <t>042836</t>
+  </si>
+  <si>
+    <t>042837</t>
+  </si>
+  <si>
+    <t>042838</t>
+  </si>
+  <si>
+    <t>042839</t>
+  </si>
+  <si>
+    <t>042852</t>
+  </si>
+  <si>
+    <t>042853</t>
+  </si>
+  <si>
+    <t>042854</t>
+  </si>
+  <si>
+    <t>000612</t>
+  </si>
+  <si>
+    <t>002710</t>
   </si>
   <si>
     <t>Party Name</t>
@@ -8141,7 +8441,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="44.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16" style="1" customWidth="1"/>
@@ -8156,7 +8456,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>2539</v>
+        <v>2639</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>367</v>
@@ -8165,10 +8465,10 @@
         <v>694</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>2540</v>
+        <v>2640</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>2541</v>
+        <v>2641</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>393</v>
@@ -8605,7 +8905,12 @@
       <c r="E26" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="G26" s="7"/>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
@@ -8851,6 +9156,12 @@
       <c r="E40" s="2" t="s">
         <v>820</v>
       </c>
+      <c r="F40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
@@ -8885,6 +9196,12 @@
       <c r="E42" s="1">
         <v>110890</v>
       </c>
+      <c r="F42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
@@ -8901,6 +9218,12 @@
       </c>
       <c r="E43" s="1">
         <v>110891</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7">
+        <v>46167</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13229,6 +13552,12 @@
       <c r="E284" s="1">
         <v>460397</v>
       </c>
+      <c r="F284" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G284" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="285" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="7">
@@ -13246,6 +13575,12 @@
       <c r="E285" s="1">
         <v>460398</v>
       </c>
+      <c r="F285" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G285" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="286" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="7">
@@ -13576,6 +13911,12 @@
       <c r="E303" s="2" t="s">
         <v>1718</v>
       </c>
+      <c r="F303" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G303" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="304" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="7">
@@ -14671,6 +15012,12 @@
       <c r="E366" s="2" t="s">
         <v>1826</v>
       </c>
+      <c r="F366" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G366" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="367" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="7">
@@ -15390,6 +15737,12 @@
       <c r="E406" s="1">
         <v>388405</v>
       </c>
+      <c r="F406" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G406" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="407" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="7">
@@ -15967,7 +16320,7 @@
         <v>12</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>245</v>
+        <v>2267</v>
       </c>
       <c r="E438" s="1">
         <v>113690</v>
@@ -16517,6 +16870,12 @@
       <c r="E468" s="2" t="s">
         <v>536</v>
       </c>
+      <c r="F468" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G468" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="469" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="7">
@@ -17593,6 +17952,12 @@
       <c r="E527" s="2" t="s">
         <v>2038</v>
       </c>
+      <c r="F527" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G527" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="528" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="7">
@@ -19938,6 +20303,12 @@
       <c r="E655" s="1">
         <v>184759</v>
       </c>
+      <c r="F655" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G655" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="656" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="7">
@@ -24229,6 +24600,12 @@
       <c r="E901" s="2" t="s">
         <v>1966</v>
       </c>
+      <c r="F901" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G901" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="902" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="7">
@@ -24246,6 +24623,12 @@
       <c r="E902" s="2" t="s">
         <v>1967</v>
       </c>
+      <c r="F902" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G902" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="903" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="7">
@@ -26530,7 +26913,12 @@
       <c r="E1027" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="G1027" s="7"/>
+      <c r="F1027" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1027" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1028" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="7">
@@ -26565,6 +26953,12 @@
       <c r="E1029" s="2" t="s">
         <v>807</v>
       </c>
+      <c r="F1029" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1029" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1030" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="7">
@@ -27343,7 +27737,12 @@
       <c r="E1072" s="2" t="s">
         <v>1694</v>
       </c>
-      <c r="G1072" s="7"/>
+      <c r="F1072" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1072" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1073" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1073" s="7">
@@ -27361,6 +27760,12 @@
       <c r="E1073" s="2" t="s">
         <v>1701</v>
       </c>
+      <c r="F1073" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1073" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1074" s="7">
@@ -27726,6 +28131,12 @@
       <c r="E1093" s="1">
         <v>446522</v>
       </c>
+      <c r="F1093" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1093" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1094" s="7">
@@ -28153,6 +28564,12 @@
       <c r="E1117" s="1">
         <v>684269</v>
       </c>
+      <c r="F1117" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1117" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1118" s="7">
@@ -28170,6 +28587,12 @@
       <c r="E1118" s="1">
         <v>684270</v>
       </c>
+      <c r="F1118" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1118" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1119" s="7">
@@ -28187,6 +28610,12 @@
       <c r="E1119" s="1">
         <v>684271</v>
       </c>
+      <c r="F1119" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1119" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1120" s="7">
@@ -28496,6 +28925,12 @@
       <c r="E1134" s="2" t="s">
         <v>1789</v>
       </c>
+      <c r="F1134" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1134" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1135" s="7">
@@ -31641,6 +32076,12 @@
       <c r="E1305" s="1">
         <v>867828</v>
       </c>
+      <c r="F1305" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1305" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1306" s="7">
@@ -31658,6 +32099,12 @@
       <c r="E1306" s="1">
         <v>867829</v>
       </c>
+      <c r="F1306" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1306" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1307" s="7">
@@ -35861,6 +36308,12 @@
       <c r="E1543" s="2" t="s">
         <v>579</v>
       </c>
+      <c r="F1543" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1543" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1544" s="7">
@@ -35878,6 +36331,12 @@
       <c r="E1544" s="2" t="s">
         <v>580</v>
       </c>
+      <c r="F1544" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1544" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1545" s="7">
@@ -38646,6 +39105,12 @@
       <c r="E1696" s="2" t="s">
         <v>537</v>
       </c>
+      <c r="F1696" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1696" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1697" s="7">
@@ -38822,6 +39287,12 @@
       <c r="E1706" s="2" t="s">
         <v>1705</v>
       </c>
+      <c r="F1706" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1706" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1707" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1707" s="7">
@@ -40418,7 +40889,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="1793" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1793" s="7">
         <v>46107</v>
       </c>
@@ -40434,8 +40905,14 @@
       <c r="E1793" s="2" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="1794" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1793" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1793" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1794" s="7">
         <v>46107</v>
       </c>
@@ -40451,8 +40928,9 @@
       <c r="E1794" s="2" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="1795" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G1794" s="7"/>
+    </row>
+    <row r="1795" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1795" s="7">
         <v>46107</v>
       </c>
@@ -40468,8 +40946,14 @@
       <c r="E1795" s="2" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="1796" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1795" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1795" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1796" s="7">
         <v>46107</v>
       </c>
@@ -40486,7 +40970,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="1797" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1797" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1797" s="7">
         <v>46107</v>
       </c>
@@ -40503,7 +40987,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="1798" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1798" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1798" s="7">
         <v>46107</v>
       </c>
@@ -40520,7 +41004,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="1799" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1799" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1799" s="7">
         <v>46107</v>
       </c>
@@ -40537,7 +41021,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="1800" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1800" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1800" s="7">
         <v>46107</v>
       </c>
@@ -40554,7 +41038,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="1801" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1801" s="7">
         <v>46107</v>
       </c>
@@ -40571,7 +41055,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="1802" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1802" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1802" s="7">
         <v>46107</v>
       </c>
@@ -40588,7 +41072,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="1803" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1803" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1803" s="7">
         <v>46107</v>
       </c>
@@ -40605,7 +41089,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="1804" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1804" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1804" s="7">
         <v>46107</v>
       </c>
@@ -40622,7 +41106,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="1805" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1805" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1805" s="7">
         <v>46107</v>
       </c>
@@ -40639,7 +41123,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="1806" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1806" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1806" s="7">
         <v>46107</v>
       </c>
@@ -40656,7 +41140,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1807" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1807" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1807" s="7">
         <v>46107</v>
       </c>
@@ -40673,7 +41157,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="1808" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1808" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1808" s="7">
         <v>46107</v>
       </c>
@@ -41536,6 +42020,12 @@
       <c r="E1856" s="1">
         <v>792422</v>
       </c>
+      <c r="F1856" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1856" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1857" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1857" s="7">
@@ -41553,6 +42043,12 @@
       <c r="E1857" s="1">
         <v>792423</v>
       </c>
+      <c r="F1857" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1857" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1858" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1858" s="7">
@@ -41627,6 +42123,12 @@
       <c r="E1861" s="2" t="s">
         <v>1837</v>
       </c>
+      <c r="F1861" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1861" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1862" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1862" s="7">
@@ -41696,6 +42198,12 @@
       <c r="E1865" s="2" t="s">
         <v>729</v>
       </c>
+      <c r="F1865" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1865" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1866" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1866" s="7">
@@ -42933,6 +43441,12 @@
       <c r="E1934" s="2" t="s">
         <v>1906</v>
       </c>
+      <c r="F1934" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1934" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1935" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1935" s="7">
@@ -43276,6 +43790,12 @@
       </c>
       <c r="E1953" s="2" t="s">
         <v>1646</v>
+      </c>
+      <c r="F1953" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1953" s="7">
+        <v>46167</v>
       </c>
     </row>
     <row r="1954" spans="1:8" x14ac:dyDescent="0.25">
@@ -43602,6 +44122,12 @@
       <c r="E1970" s="2" t="s">
         <v>1915</v>
       </c>
+      <c r="F1970" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1970" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="1971" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1971" s="7">
@@ -44955,6 +45481,12 @@
       <c r="E2046" s="2" t="s">
         <v>1053</v>
       </c>
+      <c r="F2046" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2046" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2047" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2047" s="7">
@@ -46338,6 +46870,12 @@
       <c r="E2123" s="2" t="s">
         <v>1043</v>
       </c>
+      <c r="F2123" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2123" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2124" s="7">
@@ -47326,6 +47864,12 @@
       <c r="E2180" s="2" t="s">
         <v>669</v>
       </c>
+      <c r="F2180" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2180" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2181" s="7">
@@ -47637,6 +48181,12 @@
       <c r="E2197" s="1">
         <v>329730</v>
       </c>
+      <c r="F2197" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2197" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2198" s="7">
@@ -48963,6 +49513,12 @@
       <c r="E2270" s="1">
         <v>102513</v>
       </c>
+      <c r="F2270" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2270" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2271" s="7">
@@ -50702,6 +51258,12 @@
       </c>
       <c r="E2365" s="2" t="s">
         <v>1347</v>
+      </c>
+      <c r="F2365" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2365" s="7">
+        <v>46167</v>
       </c>
     </row>
     <row r="2366" spans="1:7" x14ac:dyDescent="0.25">
@@ -53523,6 +54085,12 @@
       <c r="E2520" s="2" t="s">
         <v>2105</v>
       </c>
+      <c r="F2520" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2520" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2521" s="7">
@@ -55313,6 +55881,12 @@
       <c r="E2615" s="2" t="s">
         <v>2159</v>
       </c>
+      <c r="F2615" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2615" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2616" s="7">
@@ -56675,6 +57249,12 @@
       <c r="E2688" s="2" t="s">
         <v>2202</v>
       </c>
+      <c r="F2688" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2688" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2689" s="7">
@@ -57109,6 +57689,12 @@
       <c r="E2711" s="1">
         <v>458739</v>
       </c>
+      <c r="F2711" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2711" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2712" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2712" s="7">
@@ -57662,6 +58248,12 @@
       <c r="E2740" s="1">
         <v>814149</v>
       </c>
+      <c r="F2740" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2740" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="2741" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2741" s="7">
@@ -62752,7 +63344,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="3009" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3009" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3009" s="7">
         <v>46165</v>
       </c>
@@ -62769,7 +63361,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="3010" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3010" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3010" s="7">
         <v>46165</v>
       </c>
@@ -62786,7 +63378,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="3011" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3011" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3011" s="7">
         <v>46165</v>
       </c>
@@ -62803,7 +63395,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="3012" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3012" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3012" s="7">
         <v>46165</v>
       </c>
@@ -62820,7 +63412,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="3013" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3013" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3013" s="7">
         <v>46165</v>
       </c>
@@ -62837,7 +63429,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="3014" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3014" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3014" s="7">
         <v>46165</v>
       </c>
@@ -62854,7 +63446,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="3015" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3015" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3015" s="7">
         <v>46165</v>
       </c>
@@ -62871,7 +63463,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="3016" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3016" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3016" s="7">
         <v>46165</v>
       </c>
@@ -62888,7 +63480,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="3017" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3017" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3017" s="7">
         <v>46165</v>
       </c>
@@ -62905,7 +63497,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="3018" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3018" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3018" s="7">
         <v>46165</v>
       </c>
@@ -62922,7 +63514,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="3019" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3019" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3019" s="7">
         <v>46165</v>
       </c>
@@ -62939,7 +63531,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="3020" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3020" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3020" s="7">
         <v>46165</v>
       </c>
@@ -62956,7 +63548,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="3021" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3021" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3021" s="7">
         <v>46165</v>
       </c>
@@ -62972,8 +63564,14 @@
       <c r="E3021" s="2" t="s">
         <v>2526</v>
       </c>
-    </row>
-    <row r="3022" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3021" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3021" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3022" s="7">
         <v>46165</v>
       </c>
@@ -62990,7 +63588,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="3023" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3023" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3023" s="7">
         <v>46165</v>
       </c>
@@ -63007,7 +63605,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="3024" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3024" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3024" s="7">
         <v>46165</v>
       </c>
@@ -63040,6 +63638,12 @@
       <c r="E3025" s="1">
         <v>456789</v>
       </c>
+      <c r="F3025" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3025" s="7">
+        <v>46167</v>
+      </c>
     </row>
     <row r="3026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3026" s="7">
@@ -63253,6 +63857,2545 @@
         <v>2538</v>
       </c>
     </row>
+    <row r="3036" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3036" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3036" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3036" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3036" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3036" s="2" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F3036" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3036" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3037" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3037" s="3" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C3037" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3037" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3037" s="1">
+        <v>547081</v>
+      </c>
+      <c r="F3037" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3037" s="7">
+        <v>46167</v>
+      </c>
+      <c r="H3037" s="1" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3038" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3038" s="3" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C3038" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3038" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3038" s="1">
+        <v>547080</v>
+      </c>
+      <c r="F3038" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3038" s="7">
+        <v>46167</v>
+      </c>
+      <c r="H3038" s="1" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3039" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3039" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C3039" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3039" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3039" s="2" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F3039" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3039" s="7">
+        <v>46167</v>
+      </c>
+      <c r="H3039" s="1" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3040" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3040" s="3" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C3040" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3040" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3040" s="1">
+        <v>342630</v>
+      </c>
+      <c r="F3040" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3040" s="7">
+        <v>46167</v>
+      </c>
+      <c r="H3040" s="1" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3041" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3041" s="3" t="s">
+        <v>2548</v>
+      </c>
+      <c r="C3041" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3041" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3041" s="2" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F3041" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3041" s="7">
+        <v>46167</v>
+      </c>
+      <c r="H3041" s="1" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3042" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3042" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C3042" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3042" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3042" s="2" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3043" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3043" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C3043" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3043" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3043" s="2" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3044" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3044" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C3044" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3044" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3044" s="2" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3045" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3045" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3045" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3045" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3045" s="2" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3046" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3046" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3046" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3046" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3046" s="2" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3047" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3047" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3047" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3047" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3047" s="2" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3048" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3048" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3048" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3048" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3048" s="2" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3049" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3049" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3049" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3049" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3049" s="2" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3050" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3050" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3050" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3050" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3050" s="2" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3051" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3051" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3051" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3051" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3051" s="2" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3052" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3052" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3052" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3052" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3052" s="2" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3053" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3053" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3053" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3053" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3053" s="2" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3054" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3054" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3054" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3054" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3054" s="2" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3055" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3055" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3055" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3055" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3055" s="2" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3056" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3056" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3056" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3056" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3056" s="2" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3057" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3057" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3057" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3057" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3057" s="2" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3058" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3058" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3058" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3058" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3058" s="2" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3059" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3059" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3059" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3059" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3059" s="2" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3060" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3060" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3060" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3060" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3060" s="2" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3061" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3061" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3061" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3061" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3061" s="2" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3062" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3062" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3062" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3062" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3062" s="2" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3063" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3063" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C3063" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3063" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E3063" s="2" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3064" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3064" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C3064" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3064" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3064" s="1">
+        <v>122230</v>
+      </c>
+      <c r="F3064" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3064" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3065" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3065" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C3065" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3065" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3065" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F3065" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3065" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3066" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3066" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C3066" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3066" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3066" s="1">
+        <v>265276</v>
+      </c>
+      <c r="F3066" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3066" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3067" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3067" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C3067" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3067" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3067" s="1">
+        <v>265277</v>
+      </c>
+      <c r="F3067" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3067" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3068" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3068" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3068" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3068" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3068" s="2" t="s">
+        <v>2576</v>
+      </c>
+      <c r="F3068" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3068" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3069" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3069" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3069" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3069" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3069" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F3069" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3069" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3070" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3070" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3070" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3070" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3070" s="2" t="s">
+        <v>2579</v>
+      </c>
+      <c r="F3070" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3070" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3071" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3071" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3071" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3071" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3071" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F3071" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3071" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3072" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3072" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3072" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3072" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3072" s="2" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F3072" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3072" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3073" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3073" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C3073" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3073" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3073" s="2" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F3073" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3073" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3074" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3074" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C3074" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3074" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3074" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F3074" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3074" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3075" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3075" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3075" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C3075" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3075" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3075" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F3075" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3075" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3076" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3076" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3076" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3076" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3076" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3076" s="1">
+        <v>812190</v>
+      </c>
+      <c r="F3076" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3076" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3077" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3077" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3077" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3077" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3077" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3077" s="1">
+        <v>812191</v>
+      </c>
+      <c r="F3077" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3077" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3078" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3078" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3078" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C3078" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3078" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3078" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F3078" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3078" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3079" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3079" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3079" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C3079" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D3079" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3079" s="1">
+        <v>947155</v>
+      </c>
+      <c r="F3079" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3079" s="7">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="3080" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3080" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3080" s="3" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C3080" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3080" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3080" s="2" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="3081" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3081" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3081" s="3" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C3081" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3081" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3081" s="2" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="3082" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3082" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3082" s="3" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C3082" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3082" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3082" s="2" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="3083" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3083" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3083" s="3" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C3083" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3083" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3083" s="2" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="3084" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3084" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3084" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C3084" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D3084" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3084" s="1">
+        <v>947156</v>
+      </c>
+    </row>
+    <row r="3085" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3085" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3085" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C3085" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D3085" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3085" s="1">
+        <v>947157</v>
+      </c>
+    </row>
+    <row r="3086" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3086" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3086" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C3086" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D3086" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3086" s="1">
+        <v>947153</v>
+      </c>
+    </row>
+    <row r="3087" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3087" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3087" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C3087" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D3087" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3087" s="1">
+        <v>947154</v>
+      </c>
+    </row>
+    <row r="3088" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3088" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3088" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C3088" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3088" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3088" s="2" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="3089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3089" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3089" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C3089" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3089" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3089" s="2" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="3090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3090" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3090" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C3090" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3090" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3090" s="2" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="3091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3091" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3091" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C3091" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3091" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3091" s="2" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="3092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3092" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3092" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C3092" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D3092" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3092" s="2" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="3093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3093" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3093" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C3093" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D3093" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3093" s="2" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="3094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3094" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3094" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C3094" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D3094" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3094" s="2" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="3095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3095" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3095" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C3095" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D3095" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3095" s="2" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="3096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3096" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3096" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3096" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3096" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3096" s="1">
+        <v>481425</v>
+      </c>
+    </row>
+    <row r="3097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3097" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3097" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3097" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3097" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3097" s="1">
+        <v>481426</v>
+      </c>
+    </row>
+    <row r="3098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3098" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3098" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3098" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3098" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3098" s="1">
+        <v>481427</v>
+      </c>
+    </row>
+    <row r="3099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3099" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3099" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3099" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3099" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3099" s="1">
+        <v>481428</v>
+      </c>
+    </row>
+    <row r="3100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3100" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3100" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3100" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3100" s="1">
+        <v>481429</v>
+      </c>
+    </row>
+    <row r="3101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3101" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3101" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3101" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3101" s="1">
+        <v>481430</v>
+      </c>
+    </row>
+    <row r="3102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3102" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3102" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3102" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3102" s="1">
+        <v>481431</v>
+      </c>
+    </row>
+    <row r="3103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3103" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3103" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3103" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3103" s="1">
+        <v>481432</v>
+      </c>
+    </row>
+    <row r="3104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3104" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3104" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3104" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3104" s="1">
+        <v>481433</v>
+      </c>
+    </row>
+    <row r="3105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3105" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3105" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C3105" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3105" s="2" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="3106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3106" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3106" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C3106" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3106" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3106" s="2" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="3107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3107" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3107" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C3107" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3107" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3107" s="2" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="3108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3108" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3108" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3108" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3108" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3108" s="1">
+        <v>812192</v>
+      </c>
+    </row>
+    <row r="3109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3109" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3109" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3109" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3109" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3109" s="1">
+        <v>812193</v>
+      </c>
+    </row>
+    <row r="3110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3110" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3110" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3110" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3110" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3110" s="1">
+        <v>812194</v>
+      </c>
+    </row>
+    <row r="3111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3111" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3111" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3111" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3111" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3111" s="1">
+        <v>812195</v>
+      </c>
+    </row>
+    <row r="3112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3112" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3112" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3112" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3112" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3112" s="1">
+        <v>812196</v>
+      </c>
+    </row>
+    <row r="3113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3113" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3113" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3113" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3113" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3113" s="1">
+        <v>812197</v>
+      </c>
+    </row>
+    <row r="3114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3114" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3114" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3114" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3114" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3114" s="1">
+        <v>812198</v>
+      </c>
+    </row>
+    <row r="3115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3115" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3115" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C3115" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3115" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3115" s="1">
+        <v>812199</v>
+      </c>
+    </row>
+    <row r="3116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3116" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3116" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3116" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3116" s="1">
+        <v>727502</v>
+      </c>
+    </row>
+    <row r="3117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3117" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3117" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3117" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3117" s="1">
+        <v>727503</v>
+      </c>
+    </row>
+    <row r="3118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3118" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3118" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3118" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3118" s="1">
+        <v>727504</v>
+      </c>
+    </row>
+    <row r="3119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3119" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3119" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3119" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3119" s="1">
+        <v>727505</v>
+      </c>
+    </row>
+    <row r="3120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3120" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3120" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3120" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3120" s="1">
+        <v>727506</v>
+      </c>
+    </row>
+    <row r="3121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3121" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3121" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3121" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3121" s="1">
+        <v>727507</v>
+      </c>
+    </row>
+    <row r="3122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3122" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3122" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3122" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3122" s="1">
+        <v>727508</v>
+      </c>
+    </row>
+    <row r="3123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3123" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3123" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3123" s="1">
+        <v>727509</v>
+      </c>
+    </row>
+    <row r="3124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3124" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3124" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3124" s="1">
+        <v>727510</v>
+      </c>
+    </row>
+    <row r="3125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3125" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3125" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3125" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3125" s="1">
+        <v>727511</v>
+      </c>
+    </row>
+    <row r="3126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3126" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3126" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3126" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3126" s="1">
+        <v>727512</v>
+      </c>
+    </row>
+    <row r="3127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3127" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3127" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3127" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3127" s="1">
+        <v>727513</v>
+      </c>
+    </row>
+    <row r="3128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3128" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3128" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3128" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3128" s="1">
+        <v>727514</v>
+      </c>
+    </row>
+    <row r="3129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3129" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3129" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3129" s="1">
+        <v>727515</v>
+      </c>
+    </row>
+    <row r="3130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3130" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3130" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3130" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3130" s="1">
+        <v>727516</v>
+      </c>
+    </row>
+    <row r="3131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3131" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3131" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3131" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3131" s="1">
+        <v>727517</v>
+      </c>
+    </row>
+    <row r="3132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3132" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3132" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3132" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3132" s="1">
+        <v>727518</v>
+      </c>
+    </row>
+    <row r="3133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3133" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3133" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3133" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3133" s="1">
+        <v>727519</v>
+      </c>
+    </row>
+    <row r="3134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3134" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3134" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C3134" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3134" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3134" s="2" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="3135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3135" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3135" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C3135" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3135" s="2" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="3136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3136" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3136" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C3136" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3136" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3136" s="2" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="3137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3137" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3137" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C3137" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3137" s="2" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="3138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3138" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3138" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C3138" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3138" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3138" s="2" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="3139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3139" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3139" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C3139" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3139" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3139" s="1">
+        <v>122231</v>
+      </c>
+    </row>
+    <row r="3140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3140" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3140" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C3140" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3140" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3140" s="1">
+        <v>122232</v>
+      </c>
+    </row>
+    <row r="3141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3141" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3141" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C3141" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3141" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3141" s="1">
+        <v>122233</v>
+      </c>
+    </row>
+    <row r="3142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3142" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3142" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C3142" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3142" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3142" s="1">
+        <v>122234</v>
+      </c>
+    </row>
+    <row r="3143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3143" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3143" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C3143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3143" s="2" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="3144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3144" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3144" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C3144" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3144" s="2" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="3145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3145" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3145" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C3145" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3145" s="2" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="3146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3146" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3146" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C3146" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3146" s="2" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="3147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3147" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3147" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C3147" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3147" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3147" s="1">
+        <v>265278</v>
+      </c>
+    </row>
+    <row r="3148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3148" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3148" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C3148" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3148" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3148" s="1">
+        <v>265279</v>
+      </c>
+    </row>
+    <row r="3149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3149" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3149" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C3149" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3149" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3149" s="1">
+        <v>265280</v>
+      </c>
+    </row>
+    <row r="3150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3150" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3150" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3150" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3150" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3150" s="2" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="3151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3151" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3151" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3151" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3151" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3151" s="2" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="3152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3152" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3152" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3152" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3152" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3152" s="2" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="3153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3153" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3153" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3153" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3153" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3153" s="2" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="3154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3154" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3154" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3154" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3154" s="2" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="3155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3155" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3155" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3155" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3155" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3155" s="2" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="3156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3156" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3156" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3156" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3156" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3156" s="2" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="3157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3157" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3157" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3157" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3157" s="2" t="s">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="3158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3158" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3158" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3158" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3158" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3158" s="2" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="3159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3159" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3159" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3159" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3159" s="2" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="3160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3160" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3160" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3160" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3160" s="2" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="3161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3161" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3161" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3161" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3161" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3161" s="2" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="3162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3162" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3162" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3162" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3162" s="2" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="3163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3163" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3163" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3163" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3163" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3163" s="2" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="3164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3164" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3164" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3164" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3164" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3164" s="2" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="3165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3165" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3165" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3165" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3165" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3165" s="2" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="3166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3166" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3166" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3166" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3166" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3166" s="2" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="3167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3167" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3167" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3167" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3167" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3167" s="2" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="3168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3168" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3168" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3168" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3168" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3168" s="2" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="3169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3169" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3169" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3169" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3169" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3169" s="2" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="3170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3170" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3170" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3170" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3170" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3170" s="2" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="3171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3171" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3171" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3171" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3171" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3171" s="2" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="3172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3172" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3172" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C3172" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3172" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3172" s="2" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="3173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3173" s="7"/>
+      <c r="E3173" s="2"/>
+    </row>
+    <row r="3174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3174" s="7"/>
+      <c r="E3174" s="2"/>
+    </row>
+    <row r="3175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3175" s="7"/>
+      <c r="E3175" s="2"/>
+    </row>
+    <row r="3176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3176" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3176" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3176" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3176" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3176" s="2" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="3177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3177" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3177" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C3177" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3177" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3177" s="1">
+        <v>244521</v>
+      </c>
+    </row>
+    <row r="3178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3178" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B3178" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3178" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3178" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3178" s="2" t="s">
+        <v>2638</v>
+      </c>
+    </row>
     <row r="1045546" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1045546" s="7"/>
     </row>
@@ -63262,10 +66405,11 @@
     <row r="1048559" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G1048559" s="7"/>
     </row>
-    <row r="1048575" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1048575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1048575" s="7"/>
     </row>
-    <row r="1048576" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1048576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="7"/>
       <c r="G1048576" s="7"/>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{400AA8E2-B710-45D3-99A1-A0748A45DC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91CF8E7-73F9-435A-B80E-34829AECD855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4063</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4069</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16325" uniqueCount="3186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16359" uniqueCount="3190">
   <si>
     <t>USE</t>
   </si>
@@ -9572,6 +9572,18 @@
   </si>
   <si>
     <t>065268</t>
+  </si>
+  <si>
+    <t>GUPTA MEDICAL STORE</t>
+  </si>
+  <si>
+    <t>VARDHMAN MEDICAL STORE</t>
+  </si>
+  <si>
+    <t>083478</t>
+  </si>
+  <si>
+    <t>083479</t>
   </si>
   <si>
     <t>Party Name</t>
@@ -10090,7 +10102,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>3183</v>
+        <v>3187</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>365</v>
@@ -10099,10 +10111,10 @@
         <v>692</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3184</v>
+        <v>3188</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3185</v>
+        <v>3189</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>391</v>
@@ -43979,6 +43991,12 @@
       <c r="E1777" s="1">
         <v>503069</v>
       </c>
+      <c r="F1777" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1777" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="1778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1778" s="7">
@@ -69752,6 +69770,12 @@
       <c r="E3079" s="2" t="s">
         <v>2566</v>
       </c>
+      <c r="F3079" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3079" s="7">
+        <v>46150</v>
+      </c>
     </row>
     <row r="3080" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3080" s="7">
@@ -76608,6 +76632,12 @@
       <c r="E3431" s="1">
         <v>981073</v>
       </c>
+      <c r="F3431" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3431" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="3432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3432" s="7">
@@ -76812,6 +76842,12 @@
       <c r="E3443" s="2" t="s">
         <v>2811</v>
       </c>
+      <c r="F3443" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3443" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="3444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3444" s="7">
@@ -79346,6 +79382,7 @@
       <c r="E3578" s="1">
         <v>955149</v>
       </c>
+      <c r="G3578" s="7"/>
     </row>
     <row r="3579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3579" s="7">
@@ -87584,7 +87621,12 @@
       <c r="E4024" s="2" t="s">
         <v>3164</v>
       </c>
-      <c r="G4024" s="7"/>
+      <c r="F4024" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4024" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="4025" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4025" s="7">
@@ -87602,6 +87644,12 @@
       <c r="E4025" s="2" t="s">
         <v>3165</v>
       </c>
+      <c r="F4025" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4025" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="4026" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4026" s="7">
@@ -88295,6 +88343,158 @@
       </c>
       <c r="E4063" s="1">
         <v>174961</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4064" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4064" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C4064" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4064" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4064" s="1">
+        <v>448350</v>
+      </c>
+      <c r="F4064" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4064" s="7">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4065" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4065" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C4065" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4065" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4065" s="1">
+        <v>448351</v>
+      </c>
+      <c r="F4065" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4065" s="7">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4066" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4066" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C4066" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4066" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4066" s="1">
+        <v>448352</v>
+      </c>
+      <c r="G4066" s="7"/>
+    </row>
+    <row r="4067" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4067" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4067" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C4067" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4067" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4067" s="1">
+        <v>485516</v>
+      </c>
+      <c r="G4067" s="7"/>
+    </row>
+    <row r="4068" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4068" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4068" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C4068" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4068" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4068" s="1">
+        <v>485517</v>
+      </c>
+      <c r="G4068" s="7"/>
+    </row>
+    <row r="4069" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4069" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4069" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C4069" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4069" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4069" s="1">
+        <v>485518</v>
+      </c>
+      <c r="G4069" s="7"/>
+    </row>
+    <row r="4070" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4070" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4070" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="C4070" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4070" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4070" s="2" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4071" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B4071" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="C4071" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4071" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4071" s="2" t="s">
+        <v>3186</v>
       </c>
     </row>
     <row r="1045525" spans="1:7" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91CF8E7-73F9-435A-B80E-34829AECD855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D441726-57AC-4887-8843-0A35837556EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4069</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4146</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16359" uniqueCount="3190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16742" uniqueCount="3225">
   <si>
     <t>USE</t>
   </si>
@@ -9584,6 +9584,111 @@
   </si>
   <si>
     <t>083479</t>
+  </si>
+  <si>
+    <t>001859</t>
+  </si>
+  <si>
+    <t>001858</t>
+  </si>
+  <si>
+    <t>371540</t>
+  </si>
+  <si>
+    <t>033151</t>
+  </si>
+  <si>
+    <t>033135</t>
+  </si>
+  <si>
+    <t>033136</t>
+  </si>
+  <si>
+    <t>004021</t>
+  </si>
+  <si>
+    <t>004020</t>
+  </si>
+  <si>
+    <t>008553</t>
+  </si>
+  <si>
+    <t>033255</t>
+  </si>
+  <si>
+    <t>033256</t>
+  </si>
+  <si>
+    <t>033257</t>
+  </si>
+  <si>
+    <t>033275</t>
+  </si>
+  <si>
+    <t>076344</t>
+  </si>
+  <si>
+    <t>063958</t>
+  </si>
+  <si>
+    <t>063272</t>
+  </si>
+  <si>
+    <t>28849/-</t>
+  </si>
+  <si>
+    <t>208696/-</t>
+  </si>
+  <si>
+    <t>076345</t>
+  </si>
+  <si>
+    <t>076346</t>
+  </si>
+  <si>
+    <t>076347</t>
+  </si>
+  <si>
+    <t>076348</t>
+  </si>
+  <si>
+    <t>AMC HEALTHCARE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>HARYANA</t>
+  </si>
+  <si>
+    <t>000086</t>
+  </si>
+  <si>
+    <t>000087</t>
+  </si>
+  <si>
+    <t>000088</t>
+  </si>
+  <si>
+    <t>000090</t>
+  </si>
+  <si>
+    <t>SHIVA MEDICINE CENTRE</t>
+  </si>
+  <si>
+    <t>005585</t>
+  </si>
+  <si>
+    <t>005587</t>
+  </si>
+  <si>
+    <t>27854/-</t>
+  </si>
+  <si>
+    <t>12826/-</t>
+  </si>
+  <si>
+    <t>8555/-</t>
+  </si>
+  <si>
+    <t>922/-</t>
   </si>
   <si>
     <t>Party Name</t>
@@ -10087,8 +10192,8 @@
   <dimension ref="A1:O1048558"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="20.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
@@ -10102,7 +10207,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>3187</v>
+        <v>3222</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>365</v>
@@ -10111,10 +10216,10 @@
         <v>692</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3188</v>
+        <v>3223</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3189</v>
+        <v>3224</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>391</v>
@@ -11359,6 +11464,12 @@
       <c r="E65" s="2" t="s">
         <v>746</v>
       </c>
+      <c r="F65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="66" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
@@ -12060,6 +12171,12 @@
       <c r="E102" s="2" t="s">
         <v>1613</v>
       </c>
+      <c r="F102" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G102" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="103" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
@@ -12516,6 +12633,12 @@
       <c r="E127" s="2" t="s">
         <v>1740</v>
       </c>
+      <c r="F127" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G127" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
@@ -12533,6 +12656,12 @@
       <c r="E128" s="2" t="s">
         <v>1741</v>
       </c>
+      <c r="F128" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G128" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="129" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
@@ -12550,6 +12679,12 @@
       <c r="E129" s="2" t="s">
         <v>1742</v>
       </c>
+      <c r="F129" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G129" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="130" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
@@ -13095,6 +13230,12 @@
       <c r="E157" s="2" t="s">
         <v>1626</v>
       </c>
+      <c r="F157" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G157" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="158" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
@@ -13112,6 +13253,12 @@
       <c r="E158" s="2" t="s">
         <v>1627</v>
       </c>
+      <c r="F158" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G158" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="159" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
@@ -13209,12 +13356,7 @@
       <c r="E163" s="1">
         <v>995747</v>
       </c>
-      <c r="F163" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G163" s="7">
-        <v>46161</v>
-      </c>
+      <c r="G163" s="7"/>
     </row>
     <row r="164" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
@@ -13403,6 +13545,12 @@
       <c r="E173" s="1">
         <v>578186</v>
       </c>
+      <c r="F173" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G173" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="174" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7">
@@ -13753,6 +13901,12 @@
       <c r="E193" s="1">
         <v>169861</v>
       </c>
+      <c r="F193" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G193" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="194" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
@@ -14004,6 +14158,12 @@
       <c r="E206" s="2" t="s">
         <v>1475</v>
       </c>
+      <c r="F206" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G206" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="207" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7">
@@ -14419,6 +14579,12 @@
       <c r="E229" s="2" t="s">
         <v>490</v>
       </c>
+      <c r="F229" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G229" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="230" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="7">
@@ -17016,6 +17182,12 @@
       <c r="E368" s="2" t="s">
         <v>735</v>
       </c>
+      <c r="F368" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G368" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="369" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="7">
@@ -17033,6 +17205,12 @@
       <c r="E369" s="2" t="s">
         <v>767</v>
       </c>
+      <c r="F369" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G369" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="370" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="7">
@@ -19573,6 +19751,12 @@
       <c r="E501" s="1">
         <v>476138</v>
       </c>
+      <c r="F501" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G501" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="502" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="7">
@@ -19890,7 +20074,12 @@
       <c r="E516" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="G516" s="7"/>
+      <c r="F516" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G516" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="517" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="7">
@@ -21558,6 +21747,12 @@
       <c r="E604" s="1">
         <v>160471</v>
       </c>
+      <c r="F604" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G604" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="605" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="7">
@@ -21575,6 +21770,12 @@
       <c r="E605" s="1">
         <v>160472</v>
       </c>
+      <c r="F605" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G605" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="606" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="7">
@@ -21732,6 +21933,9 @@
       <c r="B613" s="3" t="s">
         <v>294</v>
       </c>
+      <c r="C613" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="D613" s="1" t="s">
         <v>296</v>
       </c>
@@ -21864,6 +22068,12 @@
       <c r="E619" s="2" t="s">
         <v>1276</v>
       </c>
+      <c r="F619" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G619" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="620" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="7">
@@ -21881,6 +22091,12 @@
       <c r="E620" s="2" t="s">
         <v>1277</v>
       </c>
+      <c r="F620" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G620" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="621" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="7">
@@ -22232,6 +22448,12 @@
       <c r="E637" s="2" t="s">
         <v>1730</v>
       </c>
+      <c r="F637" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G637" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="638" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="7">
@@ -22523,6 +22745,12 @@
       <c r="E652" s="1">
         <v>184756</v>
       </c>
+      <c r="F652" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G652" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="653" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="7">
@@ -22947,6 +23175,12 @@
       <c r="E672" s="1">
         <v>365201</v>
       </c>
+      <c r="F672" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G672" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="673" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="7">
@@ -23227,7 +23461,12 @@
       <c r="E686" s="1">
         <v>451788</v>
       </c>
-      <c r="G686" s="7"/>
+      <c r="F686" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G686" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="687" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="7">
@@ -23245,6 +23484,12 @@
       <c r="E687" s="1">
         <v>451789</v>
       </c>
+      <c r="F687" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G687" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="688" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="7">
@@ -25124,6 +25369,12 @@
       <c r="E796" s="2" t="s">
         <v>1021</v>
       </c>
+      <c r="F796" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G796" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="797" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="7">
@@ -26814,6 +27065,12 @@
       <c r="E893" s="2" t="s">
         <v>1949</v>
       </c>
+      <c r="F893" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G893" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="894" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="7">
@@ -27642,7 +27899,7 @@
         <v>0</v>
       </c>
       <c r="G934" s="7">
-        <v>46169</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="935" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31958,7 +32215,12 @@
       <c r="E1150" s="2" t="s">
         <v>1629</v>
       </c>
-      <c r="G1150" s="7"/>
+      <c r="F1150" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1150" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1151" s="7">
@@ -32614,6 +32876,12 @@
       <c r="E1182" s="2" t="s">
         <v>1994</v>
       </c>
+      <c r="F1182" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1182" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="1183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1183" s="7">
@@ -34402,6 +34670,12 @@
       <c r="E1277" s="2" t="s">
         <v>1606</v>
       </c>
+      <c r="F1277" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1277" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="1278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1278" s="7">
@@ -34419,6 +34693,12 @@
       <c r="E1278" s="2" t="s">
         <v>1607</v>
       </c>
+      <c r="F1278" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1278" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1279" s="7">
@@ -35627,6 +35907,12 @@
       <c r="E1338" s="2" t="s">
         <v>1989</v>
       </c>
+      <c r="F1338" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1338" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1339" s="7">
@@ -35644,6 +35930,12 @@
       <c r="E1339" s="2" t="s">
         <v>1990</v>
       </c>
+      <c r="F1339" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1339" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1340" s="7">
@@ -37959,6 +38251,12 @@
       <c r="E1465" s="2" t="s">
         <v>1487</v>
       </c>
+      <c r="F1465" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1465" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1466" s="7">
@@ -37976,6 +38274,12 @@
       <c r="E1466" s="2" t="s">
         <v>1488</v>
       </c>
+      <c r="F1466" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1466" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1467" s="7">
@@ -38510,7 +38814,7 @@
         <v>0</v>
       </c>
       <c r="G1495" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="1496" spans="1:7" x14ac:dyDescent="0.25">
@@ -38529,7 +38833,12 @@
       <c r="E1496" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="G1496" s="7"/>
+      <c r="F1496" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1496" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1497" s="7">
@@ -38547,7 +38856,12 @@
       <c r="E1497" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="G1497" s="7"/>
+      <c r="F1497" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1497" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1498" s="7">
@@ -38860,7 +39174,12 @@
       <c r="E1515" s="1">
         <v>679014</v>
       </c>
-      <c r="G1515" s="7"/>
+      <c r="F1515" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1515" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1516" s="7">
@@ -40846,6 +41165,12 @@
       <c r="E1615" s="2" t="s">
         <v>1405</v>
       </c>
+      <c r="F1615" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1615" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1616" s="7">
@@ -40863,6 +41188,12 @@
       <c r="E1616" s="2" t="s">
         <v>1404</v>
       </c>
+      <c r="F1616" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1616" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="1617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1617" s="7">
@@ -40880,6 +41211,12 @@
       <c r="E1617" s="2" t="s">
         <v>1936</v>
       </c>
+      <c r="F1617" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1617" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="1618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1618" s="7">
@@ -41399,6 +41736,12 @@
       <c r="E1644" s="1">
         <v>658455</v>
       </c>
+      <c r="F1644" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1644" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1645" s="7">
@@ -41439,6 +41782,12 @@
       <c r="E1646" s="1">
         <v>509444</v>
       </c>
+      <c r="F1646" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1646" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1647" s="7">
@@ -41656,6 +42005,12 @@
       <c r="E1657" s="2" t="s">
         <v>1922</v>
       </c>
+      <c r="F1657" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1657" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1658" s="7">
@@ -41673,6 +42028,12 @@
       <c r="E1658" s="2" t="s">
         <v>1923</v>
       </c>
+      <c r="F1658" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1658" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1659" s="7">
@@ -41787,6 +42148,7 @@
       <c r="E1664" s="2" t="s">
         <v>2031</v>
       </c>
+      <c r="G1664" s="7"/>
     </row>
     <row r="1665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1665" s="7">
@@ -41804,6 +42166,12 @@
       <c r="E1665" s="2" t="s">
         <v>2032</v>
       </c>
+      <c r="F1665" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1665" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="1666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1666" s="7">
@@ -43648,12 +44016,7 @@
       <c r="E1760" s="2" t="s">
         <v>1868</v>
       </c>
-      <c r="F1760" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1760" s="7">
-        <v>46163</v>
-      </c>
+      <c r="G1760" s="7"/>
     </row>
     <row r="1761" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1761" s="7">
@@ -43694,6 +44057,12 @@
       <c r="E1762" s="1">
         <v>251945</v>
       </c>
+      <c r="F1762" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1762" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1763" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1763" s="7">
@@ -44326,7 +44695,12 @@
       <c r="E1794" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="G1794" s="7"/>
+      <c r="F1794" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1794" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="1795" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1795" s="7">
@@ -44366,6 +44740,12 @@
       </c>
       <c r="E1796" s="2" t="s">
         <v>1062</v>
+      </c>
+      <c r="F1796" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1796" s="7">
+        <v>46183</v>
       </c>
     </row>
     <row r="1797" spans="1:7" x14ac:dyDescent="0.25">
@@ -46259,12 +46639,7 @@
       <c r="E1897" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="F1897" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1897" s="7">
-        <v>46171</v>
-      </c>
+      <c r="G1897" s="7"/>
     </row>
     <row r="1898" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1898" s="7">
@@ -48371,6 +48746,12 @@
       <c r="E2004" s="2" t="s">
         <v>1423</v>
       </c>
+      <c r="F2004" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2004" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2005" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2005" s="7">
@@ -48388,6 +48769,12 @@
       <c r="E2005" s="2" t="s">
         <v>1424</v>
       </c>
+      <c r="F2005" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2005" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2006" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2006" s="7">
@@ -48405,6 +48792,12 @@
       <c r="E2006" s="2" t="s">
         <v>1425</v>
       </c>
+      <c r="F2006" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2006" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2007" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2007" s="7">
@@ -49190,6 +49583,12 @@
       <c r="E2049" s="2" t="s">
         <v>1053</v>
       </c>
+      <c r="F2049" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2049" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2050" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2050" s="7">
@@ -50196,6 +50595,12 @@
       <c r="E2100" s="1">
         <v>745970</v>
       </c>
+      <c r="F2100" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2100" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2101" s="7">
@@ -50737,6 +51142,12 @@
       <c r="E2127" s="1">
         <v>242091</v>
       </c>
+      <c r="F2127" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2127" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2128" s="7">
@@ -53568,6 +53979,12 @@
       <c r="E2277" s="2" t="s">
         <v>2784</v>
       </c>
+      <c r="F2277" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2277" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2278" s="7">
@@ -55841,12 +56258,7 @@
       <c r="E2390" s="1">
         <v>733744</v>
       </c>
-      <c r="F2390" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2390" s="7">
-        <v>46178</v>
-      </c>
+      <c r="G2390" s="7"/>
     </row>
     <row r="2391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2391" s="7">
@@ -56085,6 +56497,12 @@
       <c r="E2404" s="1">
         <v>608700</v>
       </c>
+      <c r="F2404" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2404" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2405" s="7">
@@ -56335,6 +56753,12 @@
       <c r="E2418" s="2" t="s">
         <v>1766</v>
       </c>
+      <c r="F2418" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2418" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2419" s="7">
@@ -56352,6 +56776,12 @@
       <c r="E2419" s="2" t="s">
         <v>1767</v>
       </c>
+      <c r="F2419" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2419" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2420" s="7">
@@ -56461,6 +56891,12 @@
       <c r="E2424" s="1">
         <v>680180</v>
       </c>
+      <c r="F2424" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2424" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2425" s="7">
@@ -56657,6 +57093,12 @@
       </c>
       <c r="E2437" s="1">
         <v>525655</v>
+      </c>
+      <c r="F2437" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2437" s="7">
+        <v>46182</v>
       </c>
     </row>
     <row r="2438" spans="1:7" x14ac:dyDescent="0.25">
@@ -57093,6 +57535,12 @@
       <c r="E2459" s="1">
         <v>152109</v>
       </c>
+      <c r="F2459" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2459" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2460" s="7">
@@ -58379,6 +58827,12 @@
       <c r="E2524" s="2" t="s">
         <v>2100</v>
       </c>
+      <c r="F2524" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2524" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2525" s="7">
@@ -59448,6 +59902,12 @@
       <c r="E2577" s="1">
         <v>724588</v>
       </c>
+      <c r="F2577" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2577" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2578" s="7">
@@ -59769,6 +60229,12 @@
       <c r="E2592" s="1">
         <v>458705</v>
       </c>
+      <c r="F2592" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2592" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2593" s="7">
@@ -59786,6 +60252,7 @@
       <c r="E2593" s="1">
         <v>458706</v>
       </c>
+      <c r="G2593" s="7"/>
     </row>
     <row r="2594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2594" s="7">
@@ -59803,6 +60270,12 @@
       <c r="E2594" s="1">
         <v>458707</v>
       </c>
+      <c r="F2594" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2594" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2595" s="7">
@@ -60021,6 +60494,12 @@
       <c r="E2604" s="2" t="s">
         <v>2134</v>
       </c>
+      <c r="F2604" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2604" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2605" s="7">
@@ -60038,6 +60517,12 @@
       <c r="E2605" s="2" t="s">
         <v>2135</v>
       </c>
+      <c r="F2605" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2605" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2606" s="7">
@@ -61660,6 +62145,12 @@
       <c r="E2682" s="2" t="s">
         <v>865</v>
       </c>
+      <c r="F2682" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2682" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2683" s="7">
@@ -61677,6 +62168,12 @@
       <c r="E2683" s="2" t="s">
         <v>866</v>
       </c>
+      <c r="F2683" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2683" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2684" s="7">
@@ -62033,6 +62530,12 @@
       <c r="E2699" s="1">
         <v>706985</v>
       </c>
+      <c r="F2699" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2699" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2700" s="7">
@@ -62050,6 +62553,12 @@
       <c r="E2700" s="1">
         <v>706986</v>
       </c>
+      <c r="F2700" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2700" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2701" s="7">
@@ -62405,6 +62914,12 @@
       <c r="E2717" s="1">
         <v>458745</v>
       </c>
+      <c r="F2717" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2717" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2718" s="7">
@@ -63097,7 +63612,12 @@
       <c r="E2750" s="2" t="s">
         <v>2228</v>
       </c>
-      <c r="G2750" s="7"/>
+      <c r="F2750" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2750" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2751" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2751" s="7">
@@ -63115,6 +63635,12 @@
       <c r="E2751" s="2" t="s">
         <v>2229</v>
       </c>
+      <c r="F2751" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2751" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2752" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2752" s="7">
@@ -64227,6 +64753,12 @@
       <c r="E2809" s="2" t="s">
         <v>2288</v>
       </c>
+      <c r="F2809" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2809" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2810" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2810" s="7">
@@ -65058,6 +65590,12 @@
       <c r="E2848" s="2" t="s">
         <v>2313</v>
       </c>
+      <c r="F2848" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2848" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2849" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2849" s="7">
@@ -65149,6 +65687,12 @@
       <c r="E2853" s="2" t="s">
         <v>2318</v>
       </c>
+      <c r="F2853" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2853" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2854" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2854" s="7">
@@ -65166,6 +65710,12 @@
       <c r="E2854" s="2" t="s">
         <v>2319</v>
       </c>
+      <c r="F2854" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2854" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="2855" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2855" s="7">
@@ -65337,6 +65887,12 @@
       <c r="E2863" s="2" t="s">
         <v>2328</v>
       </c>
+      <c r="F2863" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2863" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2864" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2864" s="7">
@@ -70647,12 +71203,7 @@
       <c r="E3126" s="2" t="s">
         <v>2580</v>
       </c>
-      <c r="F3126" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3126" s="7">
-        <v>46170</v>
-      </c>
+      <c r="G3126" s="7"/>
     </row>
     <row r="3127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3127" s="7">
@@ -71071,6 +71622,12 @@
       <c r="E3146" s="2" t="s">
         <v>2589</v>
       </c>
+      <c r="F3146" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3146" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3147" s="7">
@@ -71770,7 +72327,12 @@
       <c r="E3179" s="2" t="s">
         <v>2618</v>
       </c>
-      <c r="G3179" s="7"/>
+      <c r="F3179" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3179" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3180" s="7">
@@ -71887,7 +72449,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="3185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3185" s="7">
         <v>46168</v>
       </c>
@@ -71903,8 +72465,14 @@
       <c r="E3185" s="1">
         <v>868287</v>
       </c>
-    </row>
-    <row r="3186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3185" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3185" s="7">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="3186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3186" s="7">
         <v>46168</v>
       </c>
@@ -71921,7 +72489,7 @@
         <v>868288</v>
       </c>
     </row>
-    <row r="3187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3187" s="7">
         <v>46168</v>
       </c>
@@ -71938,7 +72506,7 @@
         <v>868289</v>
       </c>
     </row>
-    <row r="3188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3188" s="7">
         <v>46168</v>
       </c>
@@ -71955,7 +72523,7 @@
         <v>868290</v>
       </c>
     </row>
-    <row r="3189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3189" s="7">
         <v>46168</v>
       </c>
@@ -71972,7 +72540,7 @@
         <v>868291</v>
       </c>
     </row>
-    <row r="3190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3190" s="7">
         <v>46168</v>
       </c>
@@ -71989,7 +72557,7 @@
         <v>868292</v>
       </c>
     </row>
-    <row r="3191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3191" s="7">
         <v>46168</v>
       </c>
@@ -72006,7 +72574,7 @@
         <v>868293</v>
       </c>
     </row>
-    <row r="3192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3192" s="7">
         <v>46168</v>
       </c>
@@ -72023,7 +72591,7 @@
         <v>868294</v>
       </c>
     </row>
-    <row r="3193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3193" s="7">
         <v>46168</v>
       </c>
@@ -72040,7 +72608,7 @@
         <v>868295</v>
       </c>
     </row>
-    <row r="3194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3194" s="7">
         <v>46168</v>
       </c>
@@ -72057,7 +72625,7 @@
         <v>868296</v>
       </c>
     </row>
-    <row r="3195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3195" s="7">
         <v>46168</v>
       </c>
@@ -72074,7 +72642,7 @@
         <v>868297</v>
       </c>
     </row>
-    <row r="3196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3196" s="7">
         <v>46168</v>
       </c>
@@ -72091,7 +72659,7 @@
         <v>868298</v>
       </c>
     </row>
-    <row r="3197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3197" s="7">
         <v>46168</v>
       </c>
@@ -72108,7 +72676,7 @@
         <v>868299</v>
       </c>
     </row>
-    <row r="3198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3198" s="7">
         <v>46168</v>
       </c>
@@ -72125,7 +72693,7 @@
         <v>868300</v>
       </c>
     </row>
-    <row r="3199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3199" s="7">
         <v>46168</v>
       </c>
@@ -72142,7 +72710,7 @@
         <v>868301</v>
       </c>
     </row>
-    <row r="3200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3200" s="7">
         <v>46168</v>
       </c>
@@ -72266,6 +72834,12 @@
       <c r="E3206" s="2" t="s">
         <v>2624</v>
       </c>
+      <c r="F3206" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3206" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3207" s="7">
@@ -72283,6 +72857,12 @@
       <c r="E3207" s="2" t="s">
         <v>2625</v>
       </c>
+      <c r="F3207" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3207" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3208" s="7">
@@ -72346,6 +72926,12 @@
       <c r="E3210" s="1">
         <v>559240</v>
       </c>
+      <c r="F3210" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3210" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3211" s="7">
@@ -72618,6 +73204,12 @@
       <c r="E3226" s="2" t="s">
         <v>2634</v>
       </c>
+      <c r="F3226" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3226" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3227" s="7">
@@ -75336,6 +75928,12 @@
       <c r="E3365" s="1">
         <v>261428</v>
       </c>
+      <c r="F3365" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3365" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3366" s="7">
@@ -75889,6 +76487,12 @@
       <c r="E3394" s="2" t="s">
         <v>2781</v>
       </c>
+      <c r="F3394" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3394" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3395" s="7">
@@ -75929,6 +76533,12 @@
       <c r="E3396" s="1">
         <v>186687</v>
       </c>
+      <c r="F3396" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3396" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3397" s="7">
@@ -76808,6 +77418,12 @@
       <c r="E3441" s="2" t="s">
         <v>2809</v>
       </c>
+      <c r="F3441" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3441" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3442" s="7">
@@ -76825,6 +77441,12 @@
       <c r="E3442" s="2" t="s">
         <v>2810</v>
       </c>
+      <c r="F3442" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3442" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3443" s="7">
@@ -78839,6 +79461,12 @@
       <c r="E3550" s="2" t="s">
         <v>2893</v>
       </c>
+      <c r="F3550" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3550" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3551" s="7">
@@ -78856,6 +79484,12 @@
       <c r="E3551" s="2" t="s">
         <v>2894</v>
       </c>
+      <c r="F3551" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3551" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3552" s="7">
@@ -79251,6 +79885,12 @@
       <c r="E3571" s="2" t="s">
         <v>2908</v>
       </c>
+      <c r="F3571" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3571" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3572" s="7">
@@ -79268,6 +79908,12 @@
       <c r="E3572" s="2" t="s">
         <v>2909</v>
       </c>
+      <c r="F3572" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3572" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3573" s="7">
@@ -79382,7 +80028,12 @@
       <c r="E3578" s="1">
         <v>955149</v>
       </c>
-      <c r="G3578" s="7"/>
+      <c r="F3578" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3578" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3579" s="7">
@@ -79726,6 +80377,12 @@
       <c r="E3595" s="2" t="s">
         <v>571</v>
       </c>
+      <c r="F3595" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3595" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3596" s="7">
@@ -79743,6 +80400,12 @@
       <c r="E3596" s="2" t="s">
         <v>2921</v>
       </c>
+      <c r="F3596" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3596" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3597" s="7">
@@ -81668,6 +82331,12 @@
       <c r="E3697" s="1">
         <v>327959</v>
       </c>
+      <c r="F3697" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3697" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="3698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3698" s="7">
@@ -81838,6 +82507,12 @@
       <c r="E3707" s="1">
         <v>251564</v>
       </c>
+      <c r="F3707" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3707" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3708" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3708" s="7">
@@ -82497,6 +83172,12 @@
       <c r="E3742" s="1">
         <v>335074</v>
       </c>
+      <c r="F3742" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3742" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3743" s="7">
@@ -82514,6 +83195,12 @@
       <c r="E3743" s="1">
         <v>335075</v>
       </c>
+      <c r="F3743" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3743" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3744" s="7">
@@ -84089,6 +84776,12 @@
       <c r="E3830" s="1">
         <v>947352</v>
       </c>
+      <c r="F3830" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3830" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3831" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3831" s="7">
@@ -84106,6 +84799,12 @@
       <c r="E3831" s="1">
         <v>947353</v>
       </c>
+      <c r="F3831" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3831" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3832" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3832" s="7">
@@ -84520,6 +85219,12 @@
       <c r="E3855" s="1">
         <v>111479</v>
       </c>
+      <c r="F3855" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3855" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3856" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3856" s="7">
@@ -86392,6 +87097,12 @@
       <c r="E3957" s="2" t="s">
         <v>3101</v>
       </c>
+      <c r="F3957" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3957" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3958" s="7">
@@ -86637,7 +87348,7 @@
         <v>316838</v>
       </c>
     </row>
-    <row r="3969" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3969" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3969" s="7">
         <v>46179</v>
       </c>
@@ -86654,7 +87365,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="3970" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3970" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3970" s="7">
         <v>46179</v>
       </c>
@@ -86671,7 +87382,7 @@
         <v>3111</v>
       </c>
     </row>
-    <row r="3971" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3971" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3971" s="7">
         <v>46179</v>
       </c>
@@ -86688,7 +87399,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="3972" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3972" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3972" s="7">
         <v>46179</v>
       </c>
@@ -86705,7 +87416,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="3973" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3973" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3973" s="7">
         <v>46179</v>
       </c>
@@ -86722,7 +87433,7 @@
         <v>3114</v>
       </c>
     </row>
-    <row r="3974" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3974" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3974" s="7">
         <v>46179</v>
       </c>
@@ -86738,8 +87449,14 @@
       <c r="E3974" s="2" t="s">
         <v>3115</v>
       </c>
-    </row>
-    <row r="3975" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3974" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3974" s="7">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="3975" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3975" s="7">
         <v>46179</v>
       </c>
@@ -86756,7 +87473,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="3976" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3976" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3976" s="7">
         <v>46179</v>
       </c>
@@ -86773,7 +87490,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="3977" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3977" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3977" s="7">
         <v>46179</v>
       </c>
@@ -86790,7 +87507,7 @@
         <v>3118</v>
       </c>
     </row>
-    <row r="3978" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3978" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3978" s="7">
         <v>46179</v>
       </c>
@@ -86807,7 +87524,7 @@
         <v>3119</v>
       </c>
     </row>
-    <row r="3979" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3979" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3979" s="7">
         <v>46179</v>
       </c>
@@ -86824,7 +87541,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="3980" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3980" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3980" s="7">
         <v>46179</v>
       </c>
@@ -86841,7 +87558,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="3981" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3981" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3981" s="7">
         <v>46179</v>
       </c>
@@ -86858,7 +87575,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="3982" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3982" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3982" s="7">
         <v>46179</v>
       </c>
@@ -86875,7 +87592,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="3983" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3983" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3983" s="7">
         <v>46179</v>
       </c>
@@ -86892,7 +87609,7 @@
         <v>3124</v>
       </c>
     </row>
-    <row r="3984" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3984" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3984" s="7">
         <v>46179</v>
       </c>
@@ -87305,6 +88022,12 @@
       <c r="E4007" s="2" t="s">
         <v>3147</v>
       </c>
+      <c r="F4007" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4007" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="4008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4008" s="7">
@@ -87322,6 +88045,12 @@
       <c r="E4008" s="2" t="s">
         <v>3148</v>
       </c>
+      <c r="F4008" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4008" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="4009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4009" s="7">
@@ -87570,6 +88299,12 @@
       <c r="E4021" s="2" t="s">
         <v>3161</v>
       </c>
+      <c r="F4021" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4021" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="4022" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4022" s="7">
@@ -88060,6 +88795,12 @@
       <c r="E4047" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="F4047" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4047" s="7">
+        <v>46182</v>
+      </c>
     </row>
     <row r="4048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4048" s="7">
@@ -88495,6 +89236,1359 @@
       </c>
       <c r="E4071" s="2" t="s">
         <v>3186</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4072" s="7">
+        <v>46182</v>
+      </c>
+      <c r="B4072" s="3" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C4072" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4072" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E4072" s="2" t="s">
+        <v>3188</v>
+      </c>
+      <c r="F4072" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4072" s="7">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4073" s="7">
+        <v>46182</v>
+      </c>
+      <c r="B4073" s="3" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C4073" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4073" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E4073" s="2" t="s">
+        <v>3187</v>
+      </c>
+      <c r="F4073" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4073" s="7">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4074" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4074" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C4074" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4074" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4074" s="2" t="s">
+        <v>3189</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4075" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4075" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4075" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4075" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4075" s="1">
+        <v>341962</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4076" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4076" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4076" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4076" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4076" s="1">
+        <v>341963</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4077" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4077" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4077" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4077" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4077" s="1">
+        <v>341964</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4078" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4078" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4078" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4078" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4078" s="1">
+        <v>341965</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4079" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4079" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4079" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4079" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4079" s="1">
+        <v>341966</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4080" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4080" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4080" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4080" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4080" s="1">
+        <v>341967</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4081" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4081" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4081" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4081" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4081" s="1">
+        <v>341968</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4082" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4082" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4082" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4082" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4082" s="1">
+        <v>341969</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4083" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4083" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C4083" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4083" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4083" s="1">
+        <v>341970</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4084" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4084" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4084" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4084" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4084" s="1">
+        <v>867844</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4085" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4085" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4085" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4085" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4085" s="1">
+        <v>867845</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4086" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4086" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4086" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4086" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4086" s="1">
+        <v>867846</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4087" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4087" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4087" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4087" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4087" s="1">
+        <v>867847</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4088" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4088" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4088" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4088" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4088" s="1">
+        <v>867848</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4089" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4089" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4089" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4089" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4089" s="1">
+        <v>867849</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4090" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4090" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4090" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4090" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4090" s="1">
+        <v>867850</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4091" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4091" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4091" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4091" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4091" s="1">
+        <v>867851</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4092" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4092" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4092" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4092" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4092" s="1">
+        <v>867852</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4093" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4093" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4093" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4093" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4093" s="1">
+        <v>867841</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4094" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4094" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4094" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4094" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4094" s="1">
+        <v>867840</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4095" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4095" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4095" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4095" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4095" s="1">
+        <v>867839</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4096" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4096" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4096" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4096" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4096" s="1">
+        <v>867838</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4097" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4097" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C4097" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4097" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4097" s="1">
+        <v>867837</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4098" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4098" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4098" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4098" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4098" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4099" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4099" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4099" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4099" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4099" s="2" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4100" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4100" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4100" s="2" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4101" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4101" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4101" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4101" s="2" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4102" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4102" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4102" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4102" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4102" s="2" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4103" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4103" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C4103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4103" s="1" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E4103" s="1">
+        <v>136324</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4104" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4104" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4104" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4104" s="2" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4105" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4105" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4105" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4105" s="2" t="s">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4106" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4106" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4106" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4106" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4106" s="2" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4107" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4107" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4107" s="2" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4108" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4108" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C4108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4108" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4108" s="2" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4109" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4109" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C4109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4109" s="2" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4110" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4110" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C4110" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4110" s="2" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4111" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4111" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4111" s="2" t="s">
+        <v>3196</v>
+      </c>
+      <c r="F4111" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4111" s="7">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4112" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4112" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4112" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4112" s="2" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4113" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4113" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4113" s="2" t="s">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4114" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4114" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4114" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4114" s="2" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4115" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4115" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4115" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4115" s="2" t="s">
+        <v>3200</v>
+      </c>
+      <c r="F4115" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4115" s="7">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4116" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4116" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C4116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4116" s="2" t="s">
+        <v>3201</v>
+      </c>
+      <c r="F4116" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4116" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4116" s="1" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4117" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4117" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C4117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4117" s="2" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F4117" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4117" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4117" s="1" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4118" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4118" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4118" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4118" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4118" s="1">
+        <v>990351</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4119" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4119" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4119" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4119" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4119" s="1">
+        <v>990352</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4120" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4120" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4120" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4120" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4120" s="1">
+        <v>990353</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4121" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4121" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4121" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4121" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4121" s="1">
+        <v>990354</v>
+      </c>
+    </row>
+    <row r="4122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4122" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4122" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4122" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4122" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4122" s="1">
+        <v>990355</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4123" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4123" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4123" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4123" s="2" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4124" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4124" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4124" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4124" s="2" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4125" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4125" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4125" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4125" s="2" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4126" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4126" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4126" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4126" s="2" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4127" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4127" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4127" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4127" s="1">
+        <v>450714</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4128" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4128" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4128" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4128" s="1">
+        <v>450715</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4129" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4129" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4129" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4129" s="1">
+        <v>450716</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4130" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4130" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4130" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4130" s="1">
+        <v>450717</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4131" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4131" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4131" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4131" s="1">
+        <v>450718</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4132" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4132" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4132" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4132" s="1">
+        <v>450719</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4133" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4133" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4133" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4133" s="1">
+        <v>450720</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4134" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4134" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4134" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4134" s="1">
+        <v>450721</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4135" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4135" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4135" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4135" s="1">
+        <v>450722</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4136" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4136" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4136" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4136" s="1">
+        <v>450723</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4137" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4137" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C4137" s="1" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D4137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4137" s="2" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4138" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4138" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C4138" s="1" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D4138" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4138" s="2" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4139" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4139" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C4139" s="1" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D4139" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4139" s="2" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4140" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4140" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C4140" s="1" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D4140" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4140" s="2" t="s">
+        <v>3213</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4141" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4141" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C4141" s="1" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D4141" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4141" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4142" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4142" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C4142" s="1" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D4142" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4142" s="2" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4143" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4143" s="3" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C4143" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4143" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4143" s="2" t="s">
+        <v>3216</v>
+      </c>
+      <c r="F4143" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4143" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4143" s="1" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4144" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4144" s="3" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C4144" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4144" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4144" s="2" t="s">
+        <v>3217</v>
+      </c>
+      <c r="F4144" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4144" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4144" s="1" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="4145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4145" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4145" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4145" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4145" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4145" s="1">
+        <v>115544</v>
+      </c>
+      <c r="F4145" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4145" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4145" s="1" t="s">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4146" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B4146" s="3" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C4146" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4146" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E4146" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F4146" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4146" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4146" s="1" t="s">
+        <v>3221</v>
       </c>
     </row>
     <row r="1045525" spans="1:7" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D441726-57AC-4887-8843-0A35837556EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE908B56-5212-42D4-A06B-A87AC6BEA33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10193,7 +10193,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="20.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE908B56-5212-42D4-A06B-A87AC6BEA33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD06BF4-245B-40C9-A625-A03D1D0F902D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4214</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16742" uniqueCount="3225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17063" uniqueCount="3295">
   <si>
     <t>USE</t>
   </si>
@@ -9202,9 +9202,6 @@
     <t>054961</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>000139</t>
   </si>
   <si>
@@ -9689,6 +9686,219 @@
   </si>
   <si>
     <t>922/-</t>
+  </si>
+  <si>
+    <t>19986/-</t>
+  </si>
+  <si>
+    <t>006359</t>
+  </si>
+  <si>
+    <t>006358</t>
+  </si>
+  <si>
+    <t>006411</t>
+  </si>
+  <si>
+    <t>BAWA MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>ASF</t>
+  </si>
+  <si>
+    <t>003158</t>
+  </si>
+  <si>
+    <t>006360</t>
+  </si>
+  <si>
+    <t>006361</t>
+  </si>
+  <si>
+    <t>006362</t>
+  </si>
+  <si>
+    <t>5345/-</t>
+  </si>
+  <si>
+    <t>017111</t>
+  </si>
+  <si>
+    <t>DINESH PHARMACEUTICALS</t>
+  </si>
+  <si>
+    <t>029731</t>
+  </si>
+  <si>
+    <t>003117</t>
+  </si>
+  <si>
+    <t>076302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUSHAR TRADERS  </t>
+  </si>
+  <si>
+    <t>001640</t>
+  </si>
+  <si>
+    <t>KP TRADING AGENCIES</t>
+  </si>
+  <si>
+    <t>053077</t>
+  </si>
+  <si>
+    <t>053078</t>
+  </si>
+  <si>
+    <t>053079</t>
+  </si>
+  <si>
+    <t>053080</t>
+  </si>
+  <si>
+    <t>053081</t>
+  </si>
+  <si>
+    <t>076303</t>
+  </si>
+  <si>
+    <t>076304</t>
+  </si>
+  <si>
+    <t>076305</t>
+  </si>
+  <si>
+    <t>003118</t>
+  </si>
+  <si>
+    <t>003119</t>
+  </si>
+  <si>
+    <t>003120</t>
+  </si>
+  <si>
+    <t>003121</t>
+  </si>
+  <si>
+    <t>003122</t>
+  </si>
+  <si>
+    <t>003123</t>
+  </si>
+  <si>
+    <t>003124</t>
+  </si>
+  <si>
+    <t>003125</t>
+  </si>
+  <si>
+    <t>003126</t>
+  </si>
+  <si>
+    <t>029732</t>
+  </si>
+  <si>
+    <t>029733</t>
+  </si>
+  <si>
+    <t>029734</t>
+  </si>
+  <si>
+    <t>029735</t>
+  </si>
+  <si>
+    <t>001910</t>
+  </si>
+  <si>
+    <t>001909</t>
+  </si>
+  <si>
+    <t>001908</t>
+  </si>
+  <si>
+    <t>001907</t>
+  </si>
+  <si>
+    <t>001906</t>
+  </si>
+  <si>
+    <t>017112</t>
+  </si>
+  <si>
+    <t>017113</t>
+  </si>
+  <si>
+    <t>017114</t>
+  </si>
+  <si>
+    <t>017115</t>
+  </si>
+  <si>
+    <t>017116</t>
+  </si>
+  <si>
+    <t>017117</t>
+  </si>
+  <si>
+    <t>017118</t>
+  </si>
+  <si>
+    <t>017119</t>
+  </si>
+  <si>
+    <t>017120</t>
+  </si>
+  <si>
+    <t>063770</t>
+  </si>
+  <si>
+    <t>063771</t>
+  </si>
+  <si>
+    <t>063772</t>
+  </si>
+  <si>
+    <t>43075/-</t>
+  </si>
+  <si>
+    <t>6384/-</t>
+  </si>
+  <si>
+    <t>78489/-</t>
+  </si>
+  <si>
+    <t>000378</t>
+  </si>
+  <si>
+    <t>000379</t>
+  </si>
+  <si>
+    <t>048813</t>
+  </si>
+  <si>
+    <t>048814</t>
+  </si>
+  <si>
+    <t>048815</t>
+  </si>
+  <si>
+    <t>AKASH MEDICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">              </t>
   </si>
   <si>
     <t>Party Name</t>
@@ -9782,7 +9992,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -9805,13 +10015,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -9862,6 +10100,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10189,11 +10442,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1048558"/>
+  <dimension ref="A1:O1048557"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="20.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
@@ -10207,7 +10460,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>3222</v>
+        <v>3292</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>365</v>
@@ -10216,10 +10469,10 @@
         <v>692</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3223</v>
+        <v>3293</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3224</v>
+        <v>3294</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>391</v>
@@ -18432,7 +18685,12 @@
       <c r="E432" s="2">
         <v>481233</v>
       </c>
-      <c r="G432" s="7"/>
+      <c r="F432" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G432" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="433" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B433" s="3" t="s">
@@ -18447,6 +18705,12 @@
       <c r="E433" s="2">
         <v>481234</v>
       </c>
+      <c r="F433" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G433" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="434" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="7">
@@ -21268,12 +21532,7 @@
       <c r="E578" s="2" t="s">
         <v>1535</v>
       </c>
-      <c r="F578" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G578" s="7">
-        <v>46164</v>
-      </c>
+      <c r="G578" s="7"/>
     </row>
     <row r="579" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="7">
@@ -22114,6 +22373,12 @@
       <c r="E621" s="2" t="s">
         <v>1278</v>
       </c>
+      <c r="F621" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G621" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="622" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="7">
@@ -28308,7 +28573,12 @@
       <c r="E953" s="2" t="s">
         <v>1754</v>
       </c>
-      <c r="G953" s="7"/>
+      <c r="F953" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G953" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="954" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="7">
@@ -28326,6 +28596,12 @@
       <c r="E954" s="2" t="s">
         <v>1755</v>
       </c>
+      <c r="F954" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G954" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="955" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="7">
@@ -28924,6 +29200,12 @@
       <c r="E986" s="2" t="s">
         <v>868</v>
       </c>
+      <c r="F986" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G986" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="987" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="7">
@@ -29449,6 +29731,12 @@
       <c r="E1014" s="2" t="s">
         <v>1913</v>
       </c>
+      <c r="F1014" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1014" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1015" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="7">
@@ -30791,7 +31079,12 @@
       <c r="E1082" s="2" t="s">
         <v>1857</v>
       </c>
-      <c r="G1082" s="7"/>
+      <c r="F1082" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1082" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1083" s="7">
@@ -31330,6 +31623,12 @@
       <c r="E1109" s="2" t="s">
         <v>496</v>
       </c>
+      <c r="F1109" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1109" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1110" s="7">
@@ -33865,6 +34164,12 @@
       <c r="E1238" s="1">
         <v>343236</v>
       </c>
+      <c r="F1238" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1238" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1239" s="7">
@@ -33882,6 +34187,12 @@
       <c r="E1239" s="1">
         <v>343237</v>
       </c>
+      <c r="F1239" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1239" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1240" s="7">
@@ -40119,6 +40430,12 @@
       <c r="E1562" s="2" t="s">
         <v>1016</v>
       </c>
+      <c r="F1562" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1562" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1563" s="7">
@@ -42320,6 +42637,12 @@
       <c r="E1673" s="1">
         <v>965891</v>
       </c>
+      <c r="F1673" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1673" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1674" s="7">
@@ -42341,7 +42664,7 @@
         <v>0</v>
       </c>
       <c r="G1674" s="7">
-        <v>46172</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="1675" spans="1:7" x14ac:dyDescent="0.25">
@@ -45470,7 +45793,12 @@
       <c r="E1836" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G1836" s="7"/>
+      <c r="F1836" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1836" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1837" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1837" s="7">
@@ -46898,6 +47226,12 @@
       <c r="E1909" s="2" t="s">
         <v>413</v>
       </c>
+      <c r="F1909" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1909" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="1910" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1910" s="7">
@@ -50113,7 +50447,12 @@
       <c r="E2077" s="1">
         <v>662853</v>
       </c>
-      <c r="G2077" s="7"/>
+      <c r="F2077" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2077" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2078" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2078" s="7">
@@ -51611,6 +51950,12 @@
       <c r="E2150" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="F2150" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2150" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2151" s="7">
@@ -51628,6 +51973,12 @@
       <c r="E2151" s="2" t="s">
         <v>1169</v>
       </c>
+      <c r="F2151" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2151" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2152" s="7">
@@ -51645,6 +51996,12 @@
       <c r="E2152" s="2" t="s">
         <v>1170</v>
       </c>
+      <c r="F2152" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2152" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2153" s="7">
@@ -54117,6 +54474,12 @@
       <c r="E2283" s="2" t="s">
         <v>1894</v>
       </c>
+      <c r="F2283" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2283" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2284" s="7">
@@ -56258,7 +56621,12 @@
       <c r="E2390" s="1">
         <v>733744</v>
       </c>
-      <c r="G2390" s="7"/>
+      <c r="F2390" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2390" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2391" s="7">
@@ -56822,12 +57190,7 @@
       <c r="E2421" s="1">
         <v>680177</v>
       </c>
-      <c r="F2421" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2421" s="7">
-        <v>46164</v>
-      </c>
+      <c r="G2421" s="7"/>
     </row>
     <row r="2422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2422" s="7">
@@ -56845,12 +57208,7 @@
       <c r="E2422" s="1">
         <v>680178</v>
       </c>
-      <c r="F2422" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2422" s="7">
-        <v>46164</v>
-      </c>
+      <c r="G2422" s="7"/>
     </row>
     <row r="2423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2423" s="7">
@@ -57299,7 +57657,12 @@
       <c r="E2447" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="G2447" s="7"/>
+      <c r="F2447" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2447" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2448" s="7">
@@ -57558,6 +57921,12 @@
       <c r="E2460" s="1">
         <v>152108</v>
       </c>
+      <c r="F2460" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2460" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2461" s="7">
@@ -57575,6 +57944,7 @@
       <c r="E2461" s="1">
         <v>152107</v>
       </c>
+      <c r="G2461" s="19"/>
     </row>
     <row r="2462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2462" s="7">
@@ -63658,6 +64028,12 @@
       <c r="E2752" s="2" t="s">
         <v>2230</v>
       </c>
+      <c r="F2752" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2752" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2753" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2753" s="7">
@@ -64776,6 +65152,12 @@
       <c r="E2810" s="2" t="s">
         <v>2289</v>
       </c>
+      <c r="F2810" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2810" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2811" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2811" s="7">
@@ -66430,6 +66812,12 @@
       <c r="E2891" s="2" t="s">
         <v>2358</v>
       </c>
+      <c r="F2891" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2891" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="2892" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2892" s="7">
@@ -70463,6 +70851,12 @@
       <c r="E3086" s="1">
         <v>481425</v>
       </c>
+      <c r="F3086" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3086" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3087" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3087" s="7">
@@ -71829,6 +72223,12 @@
       <c r="E3155" s="2" t="s">
         <v>2596</v>
       </c>
+      <c r="F3155" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3155" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3156" s="7">
@@ -71846,6 +72246,12 @@
       <c r="E3156" s="2" t="s">
         <v>2597</v>
       </c>
+      <c r="F3156" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3156" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3157" s="7">
@@ -71863,6 +72269,12 @@
       <c r="E3157" s="2" t="s">
         <v>2590</v>
       </c>
+      <c r="F3157" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3157" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3158" s="7">
@@ -71880,6 +72292,12 @@
       <c r="E3158" s="2" t="s">
         <v>2591</v>
       </c>
+      <c r="F3158" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3158" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3159" s="7">
@@ -72488,6 +72906,12 @@
       <c r="E3186" s="1">
         <v>868288</v>
       </c>
+      <c r="F3186" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3186" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3187" s="7">
@@ -73461,7 +73885,12 @@
       <c r="E3239" s="1">
         <v>668423</v>
       </c>
-      <c r="G3239" s="7"/>
+      <c r="F3239" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3239" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3240" s="7">
@@ -78959,6 +79388,12 @@
       <c r="E3526" s="2" t="s">
         <v>2868</v>
       </c>
+      <c r="F3526" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3526" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3527" s="7">
@@ -79507,6 +79942,12 @@
       <c r="E3552" s="2">
         <v>278633</v>
       </c>
+      <c r="F3552" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3552" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3553" s="7">
@@ -80905,6 +81346,12 @@
       <c r="E3625" s="2" t="s">
         <v>2147</v>
       </c>
+      <c r="F3625" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3625" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3626" s="7">
@@ -80994,7 +81441,7 @@
         <v>0</v>
       </c>
       <c r="G3630" s="7">
-        <v>46172</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="3631" spans="1:7" x14ac:dyDescent="0.25">
@@ -81013,6 +81460,12 @@
       <c r="E3631" s="2" t="s">
         <v>2947</v>
       </c>
+      <c r="F3631" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3631" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3632" s="7">
@@ -81030,6 +81483,12 @@
       <c r="E3632" s="2" t="s">
         <v>2948</v>
       </c>
+      <c r="F3632" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3632" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3633" s="7">
@@ -82553,6 +83012,12 @@
       <c r="E3709" s="1">
         <v>778422</v>
       </c>
+      <c r="F3709" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3709" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3710" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3710" s="7">
@@ -82854,6 +83319,12 @@
       <c r="E3726" s="2" t="s">
         <v>519</v>
       </c>
+      <c r="F3726" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3726" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3727" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3727" s="7">
@@ -84427,6 +84898,7 @@
       <c r="E3813" s="2" t="s">
         <v>3035</v>
       </c>
+      <c r="G3813" s="7"/>
     </row>
     <row r="3814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3814" s="7">
@@ -85026,6 +85498,12 @@
       <c r="E3844" s="1">
         <v>849378</v>
       </c>
+      <c r="F3844" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3844" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3845" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3845" s="7">
@@ -85043,6 +85521,12 @@
       <c r="E3845" s="1">
         <v>849377</v>
       </c>
+      <c r="F3845" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3845" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3846" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3846" s="7">
@@ -85060,6 +85544,12 @@
       <c r="E3846" s="1">
         <v>849376</v>
       </c>
+      <c r="F3846" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3846" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="3847" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3847" s="7">
@@ -85263,7 +85753,7 @@
         <v>4</v>
       </c>
       <c r="E3857" s="2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="F3857" s="1" t="s">
         <v>0</v>
@@ -85272,7 +85762,7 @@
         <v>46178</v>
       </c>
       <c r="H3857" s="1" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="3858" spans="1:8" x14ac:dyDescent="0.25">
@@ -85367,7 +85857,7 @@
         <v>46178</v>
       </c>
       <c r="H3861" s="1" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="3862" spans="1:8" x14ac:dyDescent="0.25">
@@ -85393,7 +85883,7 @@
         <v>46178</v>
       </c>
       <c r="H3862" s="1" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="3863" spans="1:8" x14ac:dyDescent="0.25">
@@ -85419,12 +85909,33 @@
         <v>46178</v>
       </c>
       <c r="H3863" s="1" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="3864" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3864" s="7">
+        <v>46178</v>
+      </c>
+      <c r="B3864" s="3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C3864" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3864" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3864" s="2" t="s">
         <v>3064</v>
       </c>
-    </row>
-    <row r="3864" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C3864" s="1" t="s">
-        <v>3059</v>
+      <c r="F3864" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3864" s="7">
+        <v>46178</v>
+      </c>
+      <c r="H3864" s="1" t="s">
+        <v>3065</v>
       </c>
     </row>
     <row r="3865" spans="1:8" x14ac:dyDescent="0.25">
@@ -85432,25 +85943,22 @@
         <v>46178</v>
       </c>
       <c r="B3865" s="3" t="s">
-        <v>2156</v>
+        <v>222</v>
       </c>
       <c r="C3865" s="1" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="D3865" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3865" s="2" t="s">
-        <v>3065</v>
+        <v>22</v>
+      </c>
+      <c r="E3865" s="1">
+        <v>553900</v>
       </c>
       <c r="F3865" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3865" s="7">
-        <v>46178</v>
-      </c>
-      <c r="H3865" s="1" t="s">
-        <v>3066</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="3866" spans="1:8" x14ac:dyDescent="0.25">
@@ -85467,13 +85975,13 @@
         <v>22</v>
       </c>
       <c r="E3866" s="1">
-        <v>553900</v>
+        <v>553901</v>
       </c>
       <c r="F3866" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3866" s="7">
-        <v>46179</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="3867" spans="1:8" x14ac:dyDescent="0.25">
@@ -85490,7 +85998,7 @@
         <v>22</v>
       </c>
       <c r="E3867" s="1">
-        <v>553901</v>
+        <v>553902</v>
       </c>
     </row>
     <row r="3868" spans="1:8" x14ac:dyDescent="0.25">
@@ -85507,7 +86015,7 @@
         <v>22</v>
       </c>
       <c r="E3868" s="1">
-        <v>553902</v>
+        <v>553903</v>
       </c>
     </row>
     <row r="3869" spans="1:8" x14ac:dyDescent="0.25">
@@ -85524,7 +86032,7 @@
         <v>22</v>
       </c>
       <c r="E3869" s="1">
-        <v>553903</v>
+        <v>553904</v>
       </c>
     </row>
     <row r="3870" spans="1:8" x14ac:dyDescent="0.25">
@@ -85532,16 +86040,22 @@
         <v>46178</v>
       </c>
       <c r="B3870" s="3" t="s">
-        <v>222</v>
+        <v>2293</v>
       </c>
       <c r="C3870" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D3870" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E3870" s="1">
-        <v>553904</v>
+        <v>390471</v>
+      </c>
+      <c r="F3870" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3870" s="7">
+        <v>46178</v>
       </c>
     </row>
     <row r="3871" spans="1:8" x14ac:dyDescent="0.25">
@@ -85549,16 +86063,16 @@
         <v>46178</v>
       </c>
       <c r="B3871" s="3" t="s">
-        <v>2293</v>
+        <v>3066</v>
       </c>
       <c r="C3871" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="D3871" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E3871" s="1">
-        <v>390471</v>
+        <v>204949</v>
       </c>
       <c r="F3871" s="1" t="s">
         <v>0</v>
@@ -85572,16 +86086,16 @@
         <v>46178</v>
       </c>
       <c r="B3872" s="3" t="s">
-        <v>3067</v>
+        <v>323</v>
       </c>
       <c r="C3872" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D3872" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3872" s="1">
-        <v>204949</v>
+        <v>24</v>
+      </c>
+      <c r="E3872" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="F3872" s="1" t="s">
         <v>0</v>
@@ -85604,13 +86118,7 @@
         <v>24</v>
       </c>
       <c r="E3873" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="F3873" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3873" s="7">
-        <v>46178</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3874" spans="1:7" x14ac:dyDescent="0.25">
@@ -85627,7 +86135,7 @@
         <v>24</v>
       </c>
       <c r="E3874" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3875" spans="1:7" x14ac:dyDescent="0.25">
@@ -85644,7 +86152,7 @@
         <v>24</v>
       </c>
       <c r="E3875" s="2" t="s">
-        <v>399</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="3876" spans="1:7" x14ac:dyDescent="0.25">
@@ -85669,16 +86177,22 @@
         <v>46178</v>
       </c>
       <c r="B3877" s="3" t="s">
-        <v>323</v>
+        <v>210</v>
       </c>
       <c r="C3877" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3877" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3877" s="2" t="s">
-        <v>3069</v>
+        <v>1650</v>
+      </c>
+      <c r="F3877" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3877" s="7">
+        <v>46181</v>
       </c>
     </row>
     <row r="3878" spans="1:7" x14ac:dyDescent="0.25">
@@ -85695,13 +86209,7 @@
         <v>4</v>
       </c>
       <c r="E3878" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="F3878" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3878" s="7">
-        <v>46181</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="3879" spans="1:7" x14ac:dyDescent="0.25">
@@ -85718,7 +86226,7 @@
         <v>4</v>
       </c>
       <c r="E3879" s="2" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="3880" spans="1:7" x14ac:dyDescent="0.25">
@@ -85735,7 +86243,7 @@
         <v>4</v>
       </c>
       <c r="E3880" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="3881" spans="1:7" x14ac:dyDescent="0.25">
@@ -85752,7 +86260,7 @@
         <v>4</v>
       </c>
       <c r="E3881" s="2" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="3882" spans="1:7" x14ac:dyDescent="0.25">
@@ -85769,7 +86277,7 @@
         <v>4</v>
       </c>
       <c r="E3882" s="2" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="3883" spans="1:7" x14ac:dyDescent="0.25">
@@ -85786,7 +86294,7 @@
         <v>4</v>
       </c>
       <c r="E3883" s="2" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="3884" spans="1:7" x14ac:dyDescent="0.25">
@@ -85803,7 +86311,7 @@
         <v>4</v>
       </c>
       <c r="E3884" s="2" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="3885" spans="1:7" x14ac:dyDescent="0.25">
@@ -85820,7 +86328,7 @@
         <v>4</v>
       </c>
       <c r="E3885" s="2" t="s">
-        <v>1657</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="3886" spans="1:7" x14ac:dyDescent="0.25">
@@ -85854,7 +86362,7 @@
         <v>4</v>
       </c>
       <c r="E3887" s="2" t="s">
-        <v>3071</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="3888" spans="1:7" x14ac:dyDescent="0.25">
@@ -85871,7 +86379,7 @@
         <v>4</v>
       </c>
       <c r="E3888" s="2" t="s">
-        <v>2130</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="3889" spans="1:7" x14ac:dyDescent="0.25">
@@ -85888,7 +86396,7 @@
         <v>4</v>
       </c>
       <c r="E3889" s="2" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="3890" spans="1:7" x14ac:dyDescent="0.25">
@@ -85905,7 +86413,7 @@
         <v>4</v>
       </c>
       <c r="E3890" s="2" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="3891" spans="1:7" x14ac:dyDescent="0.25">
@@ -85922,7 +86430,7 @@
         <v>4</v>
       </c>
       <c r="E3891" s="2" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="3892" spans="1:7" x14ac:dyDescent="0.25">
@@ -85939,7 +86447,7 @@
         <v>4</v>
       </c>
       <c r="E3892" s="2" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="3893" spans="1:7" x14ac:dyDescent="0.25">
@@ -85956,7 +86464,7 @@
         <v>4</v>
       </c>
       <c r="E3893" s="2" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="3894" spans="1:7" x14ac:dyDescent="0.25">
@@ -85973,7 +86481,7 @@
         <v>4</v>
       </c>
       <c r="E3894" s="2" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="3895" spans="1:7" x14ac:dyDescent="0.25">
@@ -85990,7 +86498,7 @@
         <v>4</v>
       </c>
       <c r="E3895" s="2" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="3896" spans="1:7" x14ac:dyDescent="0.25">
@@ -86007,7 +86515,7 @@
         <v>4</v>
       </c>
       <c r="E3896" s="2" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="3897" spans="1:7" x14ac:dyDescent="0.25">
@@ -86024,7 +86532,7 @@
         <v>4</v>
       </c>
       <c r="E3897" s="2" t="s">
-        <v>2150</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="3898" spans="1:7" x14ac:dyDescent="0.25">
@@ -86032,16 +86540,22 @@
         <v>46178</v>
       </c>
       <c r="B3898" s="3" t="s">
-        <v>210</v>
+        <v>3071</v>
       </c>
       <c r="C3898" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D3898" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E3898" s="2" t="s">
-        <v>2945</v>
+        <v>1327</v>
+      </c>
+      <c r="F3898" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3898" s="7">
+        <v>46179</v>
       </c>
     </row>
     <row r="3899" spans="1:7" x14ac:dyDescent="0.25">
@@ -86049,7 +86563,7 @@
         <v>46178</v>
       </c>
       <c r="B3899" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3899" s="1" t="s">
         <v>27</v>
@@ -86058,13 +86572,7 @@
         <v>4</v>
       </c>
       <c r="E3899" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="F3899" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3899" s="7">
-        <v>46179</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="3900" spans="1:7" x14ac:dyDescent="0.25">
@@ -86072,7 +86580,7 @@
         <v>46178</v>
       </c>
       <c r="B3900" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3900" s="1" t="s">
         <v>27</v>
@@ -86081,7 +86589,7 @@
         <v>4</v>
       </c>
       <c r="E3900" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3901" spans="1:7" x14ac:dyDescent="0.25">
@@ -86089,7 +86597,7 @@
         <v>46178</v>
       </c>
       <c r="B3901" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3901" s="1" t="s">
         <v>27</v>
@@ -86098,7 +86606,7 @@
         <v>4</v>
       </c>
       <c r="E3901" s="2" t="s">
-        <v>1329</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="3902" spans="1:7" x14ac:dyDescent="0.25">
@@ -86106,7 +86614,7 @@
         <v>46178</v>
       </c>
       <c r="B3902" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3902" s="1" t="s">
         <v>27</v>
@@ -86123,7 +86631,7 @@
         <v>46178</v>
       </c>
       <c r="B3903" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3903" s="1" t="s">
         <v>27</v>
@@ -86140,7 +86648,7 @@
         <v>46178</v>
       </c>
       <c r="B3904" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3904" s="1" t="s">
         <v>27</v>
@@ -86157,7 +86665,7 @@
         <v>46178</v>
       </c>
       <c r="B3905" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3905" s="1" t="s">
         <v>27</v>
@@ -86174,7 +86682,7 @@
         <v>46178</v>
       </c>
       <c r="B3906" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C3906" s="1" t="s">
         <v>27</v>
@@ -86191,16 +86699,16 @@
         <v>46178</v>
       </c>
       <c r="B3907" s="3" t="s">
-        <v>3072</v>
+        <v>3078</v>
       </c>
       <c r="C3907" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D3907" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="E3907" s="2" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="3908" spans="1:5" x14ac:dyDescent="0.25">
@@ -86208,7 +86716,7 @@
         <v>46178</v>
       </c>
       <c r="B3908" s="3" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="C3908" s="1" t="s">
         <v>37</v>
@@ -86225,13 +86733,13 @@
         <v>46178</v>
       </c>
       <c r="B3909" s="3" t="s">
-        <v>3079</v>
+        <v>695</v>
       </c>
       <c r="C3909" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D3909" s="1" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E3909" s="2" t="s">
         <v>3081</v>
@@ -86344,16 +86852,16 @@
         <v>46178</v>
       </c>
       <c r="B3916" s="3" t="s">
-        <v>695</v>
+        <v>628</v>
       </c>
       <c r="C3916" s="1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="D3916" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3916" s="2" t="s">
-        <v>3088</v>
+        <v>49</v>
+      </c>
+      <c r="E3916" s="1">
+        <v>102964</v>
       </c>
     </row>
     <row r="3917" spans="1:5" x14ac:dyDescent="0.25">
@@ -86370,7 +86878,7 @@
         <v>49</v>
       </c>
       <c r="E3917" s="1">
-        <v>102964</v>
+        <v>102965</v>
       </c>
     </row>
     <row r="3918" spans="1:5" x14ac:dyDescent="0.25">
@@ -86387,7 +86895,7 @@
         <v>49</v>
       </c>
       <c r="E3918" s="1">
-        <v>102965</v>
+        <v>102966</v>
       </c>
     </row>
     <row r="3919" spans="1:5" x14ac:dyDescent="0.25">
@@ -86404,7 +86912,7 @@
         <v>49</v>
       </c>
       <c r="E3919" s="1">
-        <v>102966</v>
+        <v>102968</v>
       </c>
     </row>
     <row r="3920" spans="1:5" x14ac:dyDescent="0.25">
@@ -86421,10 +86929,10 @@
         <v>49</v>
       </c>
       <c r="E3920" s="1">
-        <v>102968</v>
-      </c>
-    </row>
-    <row r="3921" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102969</v>
+      </c>
+    </row>
+    <row r="3921" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3921" s="7">
         <v>46178</v>
       </c>
@@ -86438,10 +86946,10 @@
         <v>49</v>
       </c>
       <c r="E3921" s="1">
-        <v>102969</v>
-      </c>
-    </row>
-    <row r="3922" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102970</v>
+      </c>
+    </row>
+    <row r="3922" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3922" s="7">
         <v>46178</v>
       </c>
@@ -86455,10 +86963,10 @@
         <v>49</v>
       </c>
       <c r="E3922" s="1">
-        <v>102970</v>
-      </c>
-    </row>
-    <row r="3923" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102971</v>
+      </c>
+    </row>
+    <row r="3923" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3923" s="7">
         <v>46178</v>
       </c>
@@ -86472,10 +86980,10 @@
         <v>49</v>
       </c>
       <c r="E3923" s="1">
-        <v>102971</v>
-      </c>
-    </row>
-    <row r="3924" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102972</v>
+      </c>
+    </row>
+    <row r="3924" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3924" s="7">
         <v>46178</v>
       </c>
@@ -86489,44 +86997,50 @@
         <v>49</v>
       </c>
       <c r="E3924" s="1">
-        <v>102972</v>
-      </c>
-    </row>
-    <row r="3925" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102973</v>
+      </c>
+    </row>
+    <row r="3925" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3925" s="7">
         <v>46178</v>
       </c>
       <c r="B3925" s="3" t="s">
-        <v>628</v>
+        <v>3066</v>
       </c>
       <c r="C3925" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D3925" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="E3925" s="1">
-        <v>102973</v>
-      </c>
-    </row>
-    <row r="3926" spans="1:5" x14ac:dyDescent="0.25">
+        <v>204950</v>
+      </c>
+      <c r="F3925" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3925" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="3926" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3926" s="7">
         <v>46178</v>
       </c>
       <c r="B3926" s="3" t="s">
-        <v>3067</v>
+        <v>2293</v>
       </c>
       <c r="C3926" s="1" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D3926" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E3926" s="1">
-        <v>204950</v>
-      </c>
-    </row>
-    <row r="3927" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390472</v>
+      </c>
+    </row>
+    <row r="3927" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3927" s="7">
         <v>46178</v>
       </c>
@@ -86540,10 +87054,10 @@
         <v>10</v>
       </c>
       <c r="E3927" s="1">
-        <v>390472</v>
-      </c>
-    </row>
-    <row r="3928" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390473</v>
+      </c>
+    </row>
+    <row r="3928" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3928" s="7">
         <v>46178</v>
       </c>
@@ -86557,10 +87071,10 @@
         <v>10</v>
       </c>
       <c r="E3928" s="1">
-        <v>390473</v>
-      </c>
-    </row>
-    <row r="3929" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390474</v>
+      </c>
+    </row>
+    <row r="3929" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3929" s="7">
         <v>46178</v>
       </c>
@@ -86574,10 +87088,10 @@
         <v>10</v>
       </c>
       <c r="E3929" s="1">
-        <v>390474</v>
-      </c>
-    </row>
-    <row r="3930" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390475</v>
+      </c>
+    </row>
+    <row r="3930" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3930" s="7">
         <v>46178</v>
       </c>
@@ -86591,10 +87105,10 @@
         <v>10</v>
       </c>
       <c r="E3930" s="1">
-        <v>390475</v>
-      </c>
-    </row>
-    <row r="3931" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390476</v>
+      </c>
+    </row>
+    <row r="3931" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3931" s="7">
         <v>46178</v>
       </c>
@@ -86608,10 +87122,10 @@
         <v>10</v>
       </c>
       <c r="E3931" s="1">
-        <v>390476</v>
-      </c>
-    </row>
-    <row r="3932" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390477</v>
+      </c>
+    </row>
+    <row r="3932" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3932" s="7">
         <v>46178</v>
       </c>
@@ -86625,10 +87139,10 @@
         <v>10</v>
       </c>
       <c r="E3932" s="1">
-        <v>390477</v>
-      </c>
-    </row>
-    <row r="3933" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390478</v>
+      </c>
+    </row>
+    <row r="3933" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3933" s="7">
         <v>46178</v>
       </c>
@@ -86642,10 +87156,10 @@
         <v>10</v>
       </c>
       <c r="E3933" s="1">
-        <v>390478</v>
-      </c>
-    </row>
-    <row r="3934" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390479</v>
+      </c>
+    </row>
+    <row r="3934" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3934" s="7">
         <v>46178</v>
       </c>
@@ -86659,27 +87173,27 @@
         <v>10</v>
       </c>
       <c r="E3934" s="1">
-        <v>390479</v>
-      </c>
-    </row>
-    <row r="3935" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390480</v>
+      </c>
+    </row>
+    <row r="3935" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3935" s="7">
         <v>46178</v>
       </c>
       <c r="B3935" s="3" t="s">
-        <v>2293</v>
+        <v>325</v>
       </c>
       <c r="C3935" s="1" t="s">
-        <v>131</v>
+        <v>1189</v>
       </c>
       <c r="D3935" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3935" s="1">
-        <v>390480</v>
-      </c>
-    </row>
-    <row r="3936" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="E3935" s="2" t="s">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="3936" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3936" s="7">
         <v>46178</v>
       </c>
@@ -86769,16 +87283,22 @@
         <v>46178</v>
       </c>
       <c r="B3941" s="3" t="s">
-        <v>325</v>
+        <v>3094</v>
       </c>
       <c r="C3941" s="1" t="s">
-        <v>1189</v>
+        <v>46</v>
       </c>
       <c r="D3941" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3941" s="2" t="s">
-        <v>3094</v>
+      <c r="E3941" s="2">
+        <v>530536</v>
+      </c>
+      <c r="F3941" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3941" s="7">
+        <v>46178</v>
       </c>
     </row>
     <row r="3942" spans="1:8" x14ac:dyDescent="0.25">
@@ -86786,7 +87306,7 @@
         <v>46178</v>
       </c>
       <c r="B3942" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3942" s="1" t="s">
         <v>46</v>
@@ -86795,7 +87315,7 @@
         <v>13</v>
       </c>
       <c r="E3942" s="2">
-        <v>530536</v>
+        <v>530537</v>
       </c>
       <c r="F3942" s="1" t="s">
         <v>0</v>
@@ -86809,7 +87329,7 @@
         <v>46178</v>
       </c>
       <c r="B3943" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3943" s="1" t="s">
         <v>46</v>
@@ -86818,13 +87338,13 @@
         <v>13</v>
       </c>
       <c r="E3943" s="2">
-        <v>530537</v>
+        <v>530538</v>
       </c>
       <c r="F3943" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3943" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="3944" spans="1:8" x14ac:dyDescent="0.25">
@@ -86832,7 +87352,7 @@
         <v>46178</v>
       </c>
       <c r="B3944" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3944" s="1" t="s">
         <v>46</v>
@@ -86841,13 +87361,7 @@
         <v>13</v>
       </c>
       <c r="E3944" s="2">
-        <v>530538</v>
-      </c>
-      <c r="F3944" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3944" s="7">
-        <v>46179</v>
+        <v>530539</v>
       </c>
     </row>
     <row r="3945" spans="1:8" x14ac:dyDescent="0.25">
@@ -86855,7 +87369,7 @@
         <v>46178</v>
       </c>
       <c r="B3945" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3945" s="1" t="s">
         <v>46</v>
@@ -86864,7 +87378,7 @@
         <v>13</v>
       </c>
       <c r="E3945" s="2">
-        <v>530539</v>
+        <v>530540</v>
       </c>
     </row>
     <row r="3946" spans="1:8" x14ac:dyDescent="0.25">
@@ -86872,7 +87386,7 @@
         <v>46178</v>
       </c>
       <c r="B3946" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3946" s="1" t="s">
         <v>46</v>
@@ -86881,7 +87395,7 @@
         <v>13</v>
       </c>
       <c r="E3946" s="2">
-        <v>530540</v>
+        <v>530541</v>
       </c>
     </row>
     <row r="3947" spans="1:8" x14ac:dyDescent="0.25">
@@ -86889,7 +87403,7 @@
         <v>46178</v>
       </c>
       <c r="B3947" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3947" s="1" t="s">
         <v>46</v>
@@ -86898,7 +87412,7 @@
         <v>13</v>
       </c>
       <c r="E3947" s="2">
-        <v>530541</v>
+        <v>530542</v>
       </c>
     </row>
     <row r="3948" spans="1:8" x14ac:dyDescent="0.25">
@@ -86906,7 +87420,7 @@
         <v>46178</v>
       </c>
       <c r="B3948" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3948" s="1" t="s">
         <v>46</v>
@@ -86915,7 +87429,7 @@
         <v>13</v>
       </c>
       <c r="E3948" s="2">
-        <v>530542</v>
+        <v>530543</v>
       </c>
     </row>
     <row r="3949" spans="1:8" x14ac:dyDescent="0.25">
@@ -86923,7 +87437,7 @@
         <v>46178</v>
       </c>
       <c r="B3949" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3949" s="1" t="s">
         <v>46</v>
@@ -86932,7 +87446,7 @@
         <v>13</v>
       </c>
       <c r="E3949" s="2">
-        <v>530543</v>
+        <v>530544</v>
       </c>
     </row>
     <row r="3950" spans="1:8" x14ac:dyDescent="0.25">
@@ -86940,7 +87454,7 @@
         <v>46178</v>
       </c>
       <c r="B3950" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3950" s="1" t="s">
         <v>46</v>
@@ -86949,7 +87463,7 @@
         <v>13</v>
       </c>
       <c r="E3950" s="2">
-        <v>530544</v>
+        <v>530545</v>
       </c>
     </row>
     <row r="3951" spans="1:8" x14ac:dyDescent="0.25">
@@ -86960,13 +87474,22 @@
         <v>3095</v>
       </c>
       <c r="C3951" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D3951" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E3951" s="2">
-        <v>530545</v>
+        <v>981284</v>
+      </c>
+      <c r="F3951" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3951" s="7">
+        <v>46178</v>
+      </c>
+      <c r="H3951" s="1" t="s">
+        <v>3096</v>
       </c>
     </row>
     <row r="3952" spans="1:8" x14ac:dyDescent="0.25">
@@ -86974,25 +87497,22 @@
         <v>46178</v>
       </c>
       <c r="B3952" s="3" t="s">
-        <v>3096</v>
+        <v>1363</v>
       </c>
       <c r="C3952" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D3952" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E3952" s="2">
-        <v>981284</v>
+        <v>742010</v>
       </c>
       <c r="F3952" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3952" s="7">
         <v>46178</v>
-      </c>
-      <c r="H3952" s="1" t="s">
-        <v>3097</v>
       </c>
     </row>
     <row r="3953" spans="1:8" x14ac:dyDescent="0.25">
@@ -87000,16 +87520,16 @@
         <v>46178</v>
       </c>
       <c r="B3953" s="3" t="s">
-        <v>1363</v>
+        <v>634</v>
       </c>
       <c r="C3953" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D3953" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3953" s="2">
-        <v>742010</v>
+        <v>24</v>
+      </c>
+      <c r="E3953" s="2" t="s">
+        <v>3097</v>
       </c>
       <c r="F3953" s="1" t="s">
         <v>0</v>
@@ -87046,22 +87566,16 @@
         <v>46178</v>
       </c>
       <c r="B3955" s="3" t="s">
-        <v>634</v>
+        <v>316</v>
       </c>
       <c r="C3955" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3955" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E3955" s="2" t="s">
         <v>3099</v>
-      </c>
-      <c r="F3955" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3955" s="7">
-        <v>46178</v>
       </c>
     </row>
     <row r="3956" spans="1:8" x14ac:dyDescent="0.25">
@@ -87069,30 +87583,36 @@
         <v>46178</v>
       </c>
       <c r="B3956" s="3" t="s">
-        <v>316</v>
+        <v>148</v>
       </c>
       <c r="C3956" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D3956" s="1" t="s">
-        <v>24</v>
+        <v>2061</v>
       </c>
       <c r="E3956" s="2" t="s">
         <v>3100</v>
       </c>
+      <c r="F3956" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3956" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="3957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3957" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B3957" s="3" t="s">
-        <v>148</v>
+        <v>2212</v>
       </c>
       <c r="C3957" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="D3957" s="1" t="s">
-        <v>2061</v>
+        <v>15</v>
       </c>
       <c r="E3957" s="2" t="s">
         <v>3101</v>
@@ -87101,7 +87621,10 @@
         <v>0</v>
       </c>
       <c r="G3957" s="7">
-        <v>46183</v>
+        <v>46179</v>
+      </c>
+      <c r="H3957" s="1" t="s">
+        <v>3102</v>
       </c>
     </row>
     <row r="3958" spans="1:8" x14ac:dyDescent="0.25">
@@ -87109,25 +87632,22 @@
         <v>46179</v>
       </c>
       <c r="B3958" s="3" t="s">
-        <v>2212</v>
+        <v>1319</v>
       </c>
       <c r="C3958" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D3958" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E3958" s="2" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="F3958" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3958" s="7">
-        <v>46179</v>
-      </c>
-      <c r="H3958" s="1" t="s">
-        <v>3103</v>
+        <v>46181</v>
       </c>
     </row>
     <row r="3959" spans="1:8" x14ac:dyDescent="0.25">
@@ -87135,22 +87655,22 @@
         <v>46179</v>
       </c>
       <c r="B3959" s="3" t="s">
-        <v>1319</v>
+        <v>378</v>
       </c>
       <c r="C3959" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D3959" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3959" s="2" t="s">
-        <v>3104</v>
+        <v>22</v>
+      </c>
+      <c r="E3959" s="1">
+        <v>316836</v>
       </c>
       <c r="F3959" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3959" s="7">
-        <v>46181</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="3960" spans="1:8" x14ac:dyDescent="0.25">
@@ -87167,7 +87687,7 @@
         <v>22</v>
       </c>
       <c r="E3960" s="1">
-        <v>316836</v>
+        <v>316837</v>
       </c>
       <c r="F3960" s="1" t="s">
         <v>0</v>
@@ -87190,7 +87710,7 @@
         <v>22</v>
       </c>
       <c r="E3961" s="1">
-        <v>316837</v>
+        <v>316839</v>
       </c>
       <c r="F3961" s="1" t="s">
         <v>0</v>
@@ -87204,16 +87724,16 @@
         <v>46179</v>
       </c>
       <c r="B3962" s="3" t="s">
-        <v>378</v>
+        <v>662</v>
       </c>
       <c r="C3962" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D3962" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3962" s="1">
-        <v>316839</v>
+        <v>24</v>
+      </c>
+      <c r="E3962" s="2" t="s">
+        <v>3104</v>
       </c>
       <c r="F3962" s="1" t="s">
         <v>0</v>
@@ -87265,7 +87785,7 @@
         <v>0</v>
       </c>
       <c r="G3964" s="7">
-        <v>46179</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="3965" spans="1:8" x14ac:dyDescent="0.25">
@@ -87284,6 +87804,12 @@
       <c r="E3965" s="2" t="s">
         <v>3107</v>
       </c>
+      <c r="F3965" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3965" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="3966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3966" s="7">
@@ -87313,22 +87839,16 @@
         <v>46179</v>
       </c>
       <c r="B3967" s="3" t="s">
-        <v>662</v>
+        <v>378</v>
       </c>
       <c r="C3967" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D3967" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3967" s="2" t="s">
-        <v>3109</v>
-      </c>
-      <c r="F3967" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3967" s="7">
-        <v>46181</v>
+        <v>22</v>
+      </c>
+      <c r="E3967" s="1">
+        <v>316838</v>
       </c>
     </row>
     <row r="3968" spans="1:8" x14ac:dyDescent="0.25">
@@ -87336,16 +87856,16 @@
         <v>46179</v>
       </c>
       <c r="B3968" s="3" t="s">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="C3968" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D3968" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3968" s="1">
-        <v>316838</v>
+        <v>41</v>
+      </c>
+      <c r="E3968" s="2" t="s">
+        <v>3109</v>
       </c>
     </row>
     <row r="3969" spans="1:7" x14ac:dyDescent="0.25">
@@ -87421,16 +87941,22 @@
         <v>46179</v>
       </c>
       <c r="B3973" s="3" t="s">
-        <v>78</v>
+        <v>1201</v>
       </c>
       <c r="C3973" s="1" t="s">
-        <v>40</v>
+        <v>1189</v>
       </c>
       <c r="D3973" s="1" t="s">
-        <v>41</v>
+        <v>1192</v>
       </c>
       <c r="E3973" s="2" t="s">
         <v>3114</v>
+      </c>
+      <c r="F3973" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3973" s="7">
+        <v>46182</v>
       </c>
     </row>
     <row r="3974" spans="1:7" x14ac:dyDescent="0.25">
@@ -87449,12 +87975,6 @@
       <c r="E3974" s="2" t="s">
         <v>3115</v>
       </c>
-      <c r="F3974" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3974" s="7">
-        <v>46182</v>
-      </c>
     </row>
     <row r="3975" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3975" s="7">
@@ -87614,13 +88134,13 @@
         <v>46179</v>
       </c>
       <c r="B3984" s="3" t="s">
-        <v>1201</v>
+        <v>1319</v>
       </c>
       <c r="C3984" s="1" t="s">
-        <v>1189</v>
+        <v>38</v>
       </c>
       <c r="D3984" s="1" t="s">
-        <v>1192</v>
+        <v>26</v>
       </c>
       <c r="E3984" s="2" t="s">
         <v>3125</v>
@@ -87716,13 +88236,13 @@
         <v>46179</v>
       </c>
       <c r="B3990" s="3" t="s">
-        <v>1319</v>
+        <v>52</v>
       </c>
       <c r="C3990" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D3990" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3990" s="2" t="s">
         <v>3131</v>
@@ -87971,16 +88491,22 @@
         <v>46179</v>
       </c>
       <c r="B4005" s="3" t="s">
-        <v>52</v>
+        <v>1176</v>
       </c>
       <c r="C4005" s="1" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D4005" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4005" s="2" t="s">
-        <v>3146</v>
+        <v>36</v>
+      </c>
+      <c r="E4005" s="2">
+        <v>990416</v>
+      </c>
+      <c r="F4005" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4005" s="7">
+        <v>46179</v>
       </c>
     </row>
     <row r="4006" spans="1:8" x14ac:dyDescent="0.25">
@@ -87988,22 +88514,22 @@
         <v>46179</v>
       </c>
       <c r="B4006" s="3" t="s">
-        <v>1176</v>
+        <v>964</v>
       </c>
       <c r="C4006" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D4006" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4006" s="2">
-        <v>990416</v>
+        <v>15</v>
+      </c>
+      <c r="E4006" s="2" t="s">
+        <v>3146</v>
       </c>
       <c r="F4006" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4006" s="7">
-        <v>46179</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="4007" spans="1:8" x14ac:dyDescent="0.25">
@@ -88045,12 +88571,6 @@
       <c r="E4008" s="2" t="s">
         <v>3148</v>
       </c>
-      <c r="F4008" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4008" s="7">
-        <v>46182</v>
-      </c>
     </row>
     <row r="4009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4009" s="7">
@@ -88091,16 +88611,16 @@
         <v>46179</v>
       </c>
       <c r="B4011" s="3" t="s">
-        <v>964</v>
+        <v>3151</v>
       </c>
       <c r="C4011" s="1" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="D4011" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E4011" s="2" t="s">
-        <v>3151</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="4012" spans="1:8" x14ac:dyDescent="0.25">
@@ -88108,7 +88628,7 @@
         <v>46179</v>
       </c>
       <c r="B4012" s="3" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="C4012" s="1" t="s">
         <v>131</v>
@@ -88117,7 +88637,7 @@
         <v>4</v>
       </c>
       <c r="E4012" s="2" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="4013" spans="1:8" x14ac:dyDescent="0.25">
@@ -88125,16 +88645,22 @@
         <v>46179</v>
       </c>
       <c r="B4013" s="3" t="s">
-        <v>3152</v>
+        <v>167</v>
       </c>
       <c r="C4013" s="1" t="s">
-        <v>131</v>
+        <v>6</v>
       </c>
       <c r="D4013" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4013" s="2" t="s">
-        <v>3153</v>
+        <v>26</v>
+      </c>
+      <c r="E4013" s="1">
+        <v>482807</v>
+      </c>
+      <c r="F4013" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4013" s="7">
+        <v>46181</v>
       </c>
     </row>
     <row r="4014" spans="1:8" x14ac:dyDescent="0.25">
@@ -88142,22 +88668,25 @@
         <v>46179</v>
       </c>
       <c r="B4014" s="3" t="s">
-        <v>167</v>
+        <v>634</v>
       </c>
       <c r="C4014" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D4014" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4014" s="1">
-        <v>482807</v>
+        <v>24</v>
+      </c>
+      <c r="E4014" s="2" t="s">
+        <v>3154</v>
       </c>
       <c r="F4014" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4014" s="7">
-        <v>46181</v>
+        <v>46179</v>
+      </c>
+      <c r="H4014" s="1" t="s">
+        <v>3155</v>
       </c>
     </row>
     <row r="4015" spans="1:8" x14ac:dyDescent="0.25">
@@ -88165,25 +88694,22 @@
         <v>46179</v>
       </c>
       <c r="B4015" s="3" t="s">
-        <v>634</v>
+        <v>2303</v>
       </c>
       <c r="C4015" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4015" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4015" s="2" t="s">
-        <v>3155</v>
+        <v>22</v>
+      </c>
+      <c r="E4015" s="1">
+        <v>694404</v>
       </c>
       <c r="F4015" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4015" s="7">
         <v>46179</v>
-      </c>
-      <c r="H4015" s="1" t="s">
-        <v>3156</v>
       </c>
     </row>
     <row r="4016" spans="1:8" x14ac:dyDescent="0.25">
@@ -88191,16 +88717,16 @@
         <v>46179</v>
       </c>
       <c r="B4016" s="3" t="s">
-        <v>2303</v>
+        <v>2109</v>
       </c>
       <c r="C4016" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4016" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4016" s="1">
-        <v>694404</v>
+        <v>4</v>
+      </c>
+      <c r="E4016" s="2" t="s">
+        <v>3156</v>
       </c>
       <c r="F4016" s="1" t="s">
         <v>0</v>
@@ -88214,7 +88740,7 @@
         <v>46179</v>
       </c>
       <c r="B4017" s="3" t="s">
-        <v>2109</v>
+        <v>230</v>
       </c>
       <c r="C4017" s="1" t="s">
         <v>25</v>
@@ -88224,12 +88750,6 @@
       </c>
       <c r="E4017" s="2" t="s">
         <v>3157</v>
-      </c>
-      <c r="F4017" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4017" s="7">
-        <v>46179</v>
       </c>
     </row>
     <row r="4018" spans="1:7" x14ac:dyDescent="0.25">
@@ -88282,28 +88802,28 @@
       <c r="E4020" s="2" t="s">
         <v>3160</v>
       </c>
+      <c r="F4020" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4020" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="4021" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4021" s="7">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B4021" s="3" t="s">
-        <v>230</v>
+        <v>1807</v>
       </c>
       <c r="C4021" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4021" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E4021" s="2" t="s">
         <v>3161</v>
-      </c>
-      <c r="F4021" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4021" s="7">
-        <v>46183</v>
       </c>
     </row>
     <row r="4022" spans="1:7" x14ac:dyDescent="0.25">
@@ -88328,16 +88848,22 @@
         <v>46181</v>
       </c>
       <c r="B4023" s="3" t="s">
-        <v>1807</v>
+        <v>368</v>
       </c>
       <c r="C4023" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4023" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E4023" s="2" t="s">
         <v>3163</v>
+      </c>
+      <c r="F4023" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4023" s="7">
+        <v>46181</v>
       </c>
     </row>
     <row r="4024" spans="1:7" x14ac:dyDescent="0.25">
@@ -88368,22 +88894,16 @@
         <v>46181</v>
       </c>
       <c r="B4025" s="3" t="s">
-        <v>368</v>
+        <v>524</v>
       </c>
       <c r="C4025" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4025" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4025" s="2" t="s">
-        <v>3165</v>
-      </c>
-      <c r="F4025" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4025" s="7">
-        <v>46181</v>
+        <v>26</v>
+      </c>
+      <c r="E4025" s="1">
+        <v>785846</v>
       </c>
     </row>
     <row r="4026" spans="1:7" x14ac:dyDescent="0.25">
@@ -88400,7 +88920,7 @@
         <v>26</v>
       </c>
       <c r="E4026" s="1">
-        <v>785846</v>
+        <v>785847</v>
       </c>
     </row>
     <row r="4027" spans="1:7" x14ac:dyDescent="0.25">
@@ -88408,16 +88928,16 @@
         <v>46181</v>
       </c>
       <c r="B4027" s="3" t="s">
-        <v>524</v>
+        <v>113</v>
       </c>
       <c r="C4027" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4027" s="1" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="E4027" s="1">
-        <v>785847</v>
+        <v>759757</v>
       </c>
     </row>
     <row r="4028" spans="1:7" x14ac:dyDescent="0.25">
@@ -88434,7 +88954,7 @@
         <v>80</v>
       </c>
       <c r="E4028" s="1">
-        <v>759757</v>
+        <v>759758</v>
       </c>
     </row>
     <row r="4029" spans="1:7" x14ac:dyDescent="0.25">
@@ -88451,7 +88971,7 @@
         <v>80</v>
       </c>
       <c r="E4029" s="1">
-        <v>759758</v>
+        <v>759759</v>
       </c>
     </row>
     <row r="4030" spans="1:7" x14ac:dyDescent="0.25">
@@ -88468,7 +88988,7 @@
         <v>80</v>
       </c>
       <c r="E4030" s="1">
-        <v>759759</v>
+        <v>759760</v>
       </c>
     </row>
     <row r="4031" spans="1:7" x14ac:dyDescent="0.25">
@@ -88485,7 +89005,7 @@
         <v>80</v>
       </c>
       <c r="E4031" s="1">
-        <v>759760</v>
+        <v>759761</v>
       </c>
     </row>
     <row r="4032" spans="1:7" x14ac:dyDescent="0.25">
@@ -88502,7 +89022,7 @@
         <v>80</v>
       </c>
       <c r="E4032" s="1">
-        <v>759761</v>
+        <v>759762</v>
       </c>
     </row>
     <row r="4033" spans="1:8" x14ac:dyDescent="0.25">
@@ -88519,7 +89039,7 @@
         <v>80</v>
       </c>
       <c r="E4033" s="1">
-        <v>759762</v>
+        <v>759763</v>
       </c>
     </row>
     <row r="4034" spans="1:8" x14ac:dyDescent="0.25">
@@ -88536,7 +89056,7 @@
         <v>80</v>
       </c>
       <c r="E4034" s="1">
-        <v>759763</v>
+        <v>759764</v>
       </c>
     </row>
     <row r="4035" spans="1:8" x14ac:dyDescent="0.25">
@@ -88553,7 +89073,7 @@
         <v>80</v>
       </c>
       <c r="E4035" s="1">
-        <v>759764</v>
+        <v>759765</v>
       </c>
     </row>
     <row r="4036" spans="1:8" x14ac:dyDescent="0.25">
@@ -88570,7 +89090,7 @@
         <v>80</v>
       </c>
       <c r="E4036" s="1">
-        <v>759765</v>
+        <v>759766</v>
       </c>
     </row>
     <row r="4037" spans="1:8" x14ac:dyDescent="0.25">
@@ -88578,16 +89098,25 @@
         <v>46181</v>
       </c>
       <c r="B4037" s="3" t="s">
-        <v>113</v>
+        <v>2882</v>
       </c>
       <c r="C4037" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4037" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4037" s="1">
-        <v>759766</v>
+        <v>24</v>
+      </c>
+      <c r="E4037" s="2" t="s">
+        <v>3165</v>
+      </c>
+      <c r="F4037" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4037" s="7">
+        <v>46181</v>
+      </c>
+      <c r="H4037" s="1" t="s">
+        <v>3166</v>
       </c>
     </row>
     <row r="4038" spans="1:8" x14ac:dyDescent="0.25">
@@ -88595,25 +89124,25 @@
         <v>46181</v>
       </c>
       <c r="B4038" s="3" t="s">
-        <v>2882</v>
+        <v>2212</v>
       </c>
       <c r="C4038" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4038" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E4038" s="2" t="s">
-        <v>3166</v>
-      </c>
-      <c r="F4038" s="1" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F4038" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G4038" s="7">
         <v>46181</v>
       </c>
       <c r="H4038" s="1" t="s">
-        <v>3167</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="4039" spans="1:8" x14ac:dyDescent="0.25">
@@ -88621,24 +89150,15 @@
         <v>46181</v>
       </c>
       <c r="B4039" s="3" t="s">
-        <v>2212</v>
+        <v>2304</v>
       </c>
       <c r="C4039" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4039" s="1" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="E4039" s="2" t="s">
-        <v>3168</v>
-      </c>
-      <c r="F4039" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4039" s="7">
-        <v>46181</v>
-      </c>
-      <c r="H4039" s="1" t="s">
         <v>3169</v>
       </c>
     </row>
@@ -88698,16 +89218,22 @@
         <v>46181</v>
       </c>
       <c r="B4043" s="3" t="s">
-        <v>2304</v>
+        <v>3173</v>
       </c>
       <c r="C4043" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4043" s="1" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="E4043" s="2" t="s">
-        <v>3173</v>
+        <v>3174</v>
+      </c>
+      <c r="F4043" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4043" s="7">
+        <v>46181</v>
       </c>
     </row>
     <row r="4044" spans="1:8" x14ac:dyDescent="0.25">
@@ -88715,7 +89241,7 @@
         <v>46181</v>
       </c>
       <c r="B4044" s="3" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="C4044" s="1" t="s">
         <v>12</v>
@@ -88738,16 +89264,16 @@
         <v>46181</v>
       </c>
       <c r="B4045" s="3" t="s">
-        <v>3174</v>
+        <v>3176</v>
       </c>
       <c r="C4045" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D4045" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E4045" s="2" t="s">
-        <v>3176</v>
+        <v>28</v>
       </c>
       <c r="F4045" s="1" t="s">
         <v>0</v>
@@ -88761,7 +89287,7 @@
         <v>46181</v>
       </c>
       <c r="B4046" s="3" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="C4046" s="1" t="s">
         <v>21</v>
@@ -88770,13 +89296,13 @@
         <v>7</v>
       </c>
       <c r="E4046" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4046" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4046" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="4047" spans="1:8" x14ac:dyDescent="0.25">
@@ -88784,7 +89310,7 @@
         <v>46181</v>
       </c>
       <c r="B4047" s="3" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="C4047" s="1" t="s">
         <v>21</v>
@@ -88793,13 +89319,7 @@
         <v>7</v>
       </c>
       <c r="E4047" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4047" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4047" s="7">
-        <v>46182</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4048" spans="1:8" x14ac:dyDescent="0.25">
@@ -88807,16 +89327,16 @@
         <v>46181</v>
       </c>
       <c r="B4048" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C4048" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4048" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4048" s="2" t="s">
         <v>3177</v>
-      </c>
-      <c r="C4048" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4048" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4048" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4049" spans="1:7" x14ac:dyDescent="0.25">
@@ -88869,6 +89389,12 @@
       <c r="E4051" s="2" t="s">
         <v>3180</v>
       </c>
+      <c r="F4051" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4051" s="7">
+        <v>46181</v>
+      </c>
     </row>
     <row r="4052" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4052" s="7">
@@ -88898,22 +89424,16 @@
         <v>46181</v>
       </c>
       <c r="B4053" s="3" t="s">
-        <v>1332</v>
+        <v>371</v>
       </c>
       <c r="C4053" s="1" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D4053" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4053" s="2" t="s">
-        <v>3182</v>
-      </c>
-      <c r="F4053" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4053" s="7">
-        <v>46181</v>
+        <v>10</v>
+      </c>
+      <c r="E4053" s="1">
+        <v>514064</v>
       </c>
     </row>
     <row r="4054" spans="1:7" x14ac:dyDescent="0.25">
@@ -88930,7 +89450,7 @@
         <v>10</v>
       </c>
       <c r="E4054" s="1">
-        <v>514064</v>
+        <v>514065</v>
       </c>
     </row>
     <row r="4055" spans="1:7" x14ac:dyDescent="0.25">
@@ -88947,7 +89467,7 @@
         <v>10</v>
       </c>
       <c r="E4055" s="1">
-        <v>514065</v>
+        <v>514066</v>
       </c>
     </row>
     <row r="4056" spans="1:7" x14ac:dyDescent="0.25">
@@ -88964,7 +89484,7 @@
         <v>10</v>
       </c>
       <c r="E4056" s="1">
-        <v>514066</v>
+        <v>514067</v>
       </c>
     </row>
     <row r="4057" spans="1:7" x14ac:dyDescent="0.25">
@@ -88981,7 +89501,7 @@
         <v>10</v>
       </c>
       <c r="E4057" s="1">
-        <v>514067</v>
+        <v>514068</v>
       </c>
     </row>
     <row r="4058" spans="1:7" x14ac:dyDescent="0.25">
@@ -88989,16 +89509,16 @@
         <v>46181</v>
       </c>
       <c r="B4058" s="3" t="s">
-        <v>371</v>
+        <v>939</v>
       </c>
       <c r="C4058" s="1" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D4058" s="1" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E4058" s="1">
-        <v>514068</v>
+        <v>174957</v>
       </c>
     </row>
     <row r="4059" spans="1:7" x14ac:dyDescent="0.25">
@@ -89015,7 +89535,7 @@
         <v>53</v>
       </c>
       <c r="E4059" s="1">
-        <v>174957</v>
+        <v>174958</v>
       </c>
     </row>
     <row r="4060" spans="1:7" x14ac:dyDescent="0.25">
@@ -89032,7 +89552,7 @@
         <v>53</v>
       </c>
       <c r="E4060" s="1">
-        <v>174958</v>
+        <v>174959</v>
       </c>
     </row>
     <row r="4061" spans="1:7" x14ac:dyDescent="0.25">
@@ -89049,7 +89569,7 @@
         <v>53</v>
       </c>
       <c r="E4061" s="1">
-        <v>174959</v>
+        <v>174960</v>
       </c>
     </row>
     <row r="4062" spans="1:7" x14ac:dyDescent="0.25">
@@ -89066,7 +89586,7 @@
         <v>53</v>
       </c>
       <c r="E4062" s="1">
-        <v>174960</v>
+        <v>174961</v>
       </c>
     </row>
     <row r="4063" spans="1:7" x14ac:dyDescent="0.25">
@@ -89074,16 +89594,22 @@
         <v>46181</v>
       </c>
       <c r="B4063" s="3" t="s">
-        <v>939</v>
+        <v>3182</v>
       </c>
       <c r="C4063" s="1" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="D4063" s="1" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="E4063" s="1">
-        <v>174961</v>
+        <v>448350</v>
+      </c>
+      <c r="F4063" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4063" s="7">
+        <v>46181</v>
       </c>
     </row>
     <row r="4064" spans="1:7" x14ac:dyDescent="0.25">
@@ -89091,7 +89617,7 @@
         <v>46181</v>
       </c>
       <c r="B4064" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4064" s="1" t="s">
         <v>118</v>
@@ -89100,7 +89626,7 @@
         <v>111</v>
       </c>
       <c r="E4064" s="1">
-        <v>448350</v>
+        <v>448351</v>
       </c>
       <c r="F4064" s="1" t="s">
         <v>0</v>
@@ -89114,7 +89640,7 @@
         <v>46181</v>
       </c>
       <c r="B4065" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4065" s="1" t="s">
         <v>118</v>
@@ -89123,21 +89649,16 @@
         <v>111</v>
       </c>
       <c r="E4065" s="1">
-        <v>448351</v>
-      </c>
-      <c r="F4065" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4065" s="7">
-        <v>46181</v>
-      </c>
+        <v>448352</v>
+      </c>
+      <c r="G4065" s="7"/>
     </row>
     <row r="4066" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4066" s="7">
         <v>46181</v>
       </c>
       <c r="B4066" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4066" s="1" t="s">
         <v>118</v>
@@ -89146,7 +89667,7 @@
         <v>111</v>
       </c>
       <c r="E4066" s="1">
-        <v>448352</v>
+        <v>485516</v>
       </c>
       <c r="G4066" s="7"/>
     </row>
@@ -89155,7 +89676,7 @@
         <v>46181</v>
       </c>
       <c r="B4067" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4067" s="1" t="s">
         <v>118</v>
@@ -89164,7 +89685,7 @@
         <v>111</v>
       </c>
       <c r="E4067" s="1">
-        <v>485516</v>
+        <v>485517</v>
       </c>
       <c r="G4067" s="7"/>
     </row>
@@ -89173,7 +89694,7 @@
         <v>46181</v>
       </c>
       <c r="B4068" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4068" s="1" t="s">
         <v>118</v>
@@ -89182,7 +89703,7 @@
         <v>111</v>
       </c>
       <c r="E4068" s="1">
-        <v>485517</v>
+        <v>485518</v>
       </c>
       <c r="G4068" s="7"/>
     </row>
@@ -89194,22 +89715,21 @@
         <v>3183</v>
       </c>
       <c r="C4069" s="1" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="D4069" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4069" s="1">
-        <v>485518</v>
-      </c>
-      <c r="G4069" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="E4069" s="2" t="s">
+        <v>3184</v>
+      </c>
     </row>
     <row r="4070" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4070" s="7">
         <v>46181</v>
       </c>
       <c r="B4070" s="3" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="C4070" s="1" t="s">
         <v>188</v>
@@ -89223,19 +89743,25 @@
     </row>
     <row r="4071" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4071" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B4071" s="3" t="s">
-        <v>3184</v>
+        <v>2378</v>
       </c>
       <c r="C4071" s="1" t="s">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="D4071" s="1" t="s">
-        <v>26</v>
+        <v>2380</v>
       </c>
       <c r="E4071" s="2" t="s">
-        <v>3186</v>
+        <v>3187</v>
+      </c>
+      <c r="F4071" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4071" s="7">
+        <v>46182</v>
       </c>
     </row>
     <row r="4072" spans="1:7" x14ac:dyDescent="0.25">
@@ -89252,7 +89778,7 @@
         <v>2380</v>
       </c>
       <c r="E4072" s="2" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="F4072" s="1" t="s">
         <v>0</v>
@@ -89263,25 +89789,19 @@
     </row>
     <row r="4073" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4073" s="7">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B4073" s="3" t="s">
-        <v>2378</v>
+        <v>648</v>
       </c>
       <c r="C4073" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4073" s="1" t="s">
-        <v>2380</v>
+        <v>10</v>
       </c>
       <c r="E4073" s="2" t="s">
-        <v>3187</v>
-      </c>
-      <c r="F4073" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4073" s="7">
-        <v>46182</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="4074" spans="1:7" x14ac:dyDescent="0.25">
@@ -89289,16 +89809,16 @@
         <v>46183</v>
       </c>
       <c r="B4074" s="3" t="s">
-        <v>648</v>
+        <v>911</v>
       </c>
       <c r="C4074" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D4074" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4074" s="2" t="s">
-        <v>3189</v>
+        <v>22</v>
+      </c>
+      <c r="E4074" s="1">
+        <v>341962</v>
       </c>
     </row>
     <row r="4075" spans="1:7" x14ac:dyDescent="0.25">
@@ -89315,7 +89835,7 @@
         <v>22</v>
       </c>
       <c r="E4075" s="1">
-        <v>341962</v>
+        <v>341963</v>
       </c>
     </row>
     <row r="4076" spans="1:7" x14ac:dyDescent="0.25">
@@ -89332,7 +89852,7 @@
         <v>22</v>
       </c>
       <c r="E4076" s="1">
-        <v>341963</v>
+        <v>341964</v>
       </c>
     </row>
     <row r="4077" spans="1:7" x14ac:dyDescent="0.25">
@@ -89349,7 +89869,7 @@
         <v>22</v>
       </c>
       <c r="E4077" s="1">
-        <v>341964</v>
+        <v>341965</v>
       </c>
     </row>
     <row r="4078" spans="1:7" x14ac:dyDescent="0.25">
@@ -89366,7 +89886,7 @@
         <v>22</v>
       </c>
       <c r="E4078" s="1">
-        <v>341965</v>
+        <v>341966</v>
       </c>
     </row>
     <row r="4079" spans="1:7" x14ac:dyDescent="0.25">
@@ -89383,7 +89903,7 @@
         <v>22</v>
       </c>
       <c r="E4079" s="1">
-        <v>341966</v>
+        <v>341967</v>
       </c>
     </row>
     <row r="4080" spans="1:7" x14ac:dyDescent="0.25">
@@ -89400,10 +89920,10 @@
         <v>22</v>
       </c>
       <c r="E4080" s="1">
-        <v>341967</v>
-      </c>
-    </row>
-    <row r="4081" spans="1:5" x14ac:dyDescent="0.25">
+        <v>341968</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4081" s="7">
         <v>46183</v>
       </c>
@@ -89417,10 +89937,10 @@
         <v>22</v>
       </c>
       <c r="E4081" s="1">
-        <v>341968</v>
-      </c>
-    </row>
-    <row r="4082" spans="1:5" x14ac:dyDescent="0.25">
+        <v>341969</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4082" s="7">
         <v>46183</v>
       </c>
@@ -89434,27 +89954,33 @@
         <v>22</v>
       </c>
       <c r="E4082" s="1">
-        <v>341969</v>
-      </c>
-    </row>
-    <row r="4083" spans="1:5" x14ac:dyDescent="0.25">
+        <v>341970</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4083" s="7">
         <v>46183</v>
       </c>
       <c r="B4083" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C4083" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D4083" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="E4083" s="1">
-        <v>341970</v>
-      </c>
-    </row>
-    <row r="4084" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867844</v>
+      </c>
+      <c r="F4083" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4083" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4084" s="7">
         <v>46183</v>
       </c>
@@ -89468,10 +89994,10 @@
         <v>72</v>
       </c>
       <c r="E4084" s="1">
-        <v>867844</v>
-      </c>
-    </row>
-    <row r="4085" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867845</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4085" s="7">
         <v>46183</v>
       </c>
@@ -89485,10 +90011,10 @@
         <v>72</v>
       </c>
       <c r="E4085" s="1">
-        <v>867845</v>
-      </c>
-    </row>
-    <row r="4086" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867846</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4086" s="7">
         <v>46183</v>
       </c>
@@ -89502,10 +90028,10 @@
         <v>72</v>
       </c>
       <c r="E4086" s="1">
-        <v>867846</v>
-      </c>
-    </row>
-    <row r="4087" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867847</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4087" s="7">
         <v>46183</v>
       </c>
@@ -89519,10 +90045,10 @@
         <v>72</v>
       </c>
       <c r="E4087" s="1">
-        <v>867847</v>
-      </c>
-    </row>
-    <row r="4088" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867848</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4088" s="7">
         <v>46183</v>
       </c>
@@ -89536,10 +90062,10 @@
         <v>72</v>
       </c>
       <c r="E4088" s="1">
-        <v>867848</v>
-      </c>
-    </row>
-    <row r="4089" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867849</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4089" s="7">
         <v>46183</v>
       </c>
@@ -89553,10 +90079,10 @@
         <v>72</v>
       </c>
       <c r="E4089" s="1">
-        <v>867849</v>
-      </c>
-    </row>
-    <row r="4090" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867850</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4090" s="7">
         <v>46183</v>
       </c>
@@ -89570,10 +90096,10 @@
         <v>72</v>
       </c>
       <c r="E4090" s="1">
-        <v>867850</v>
-      </c>
-    </row>
-    <row r="4091" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867851</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4091" s="7">
         <v>46183</v>
       </c>
@@ -89587,10 +90113,10 @@
         <v>72</v>
       </c>
       <c r="E4091" s="1">
-        <v>867851</v>
-      </c>
-    </row>
-    <row r="4092" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867852</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4092" s="7">
         <v>46183</v>
       </c>
@@ -89604,10 +90130,10 @@
         <v>72</v>
       </c>
       <c r="E4092" s="1">
-        <v>867852</v>
-      </c>
-    </row>
-    <row r="4093" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867841</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4093" s="7">
         <v>46183</v>
       </c>
@@ -89621,10 +90147,10 @@
         <v>72</v>
       </c>
       <c r="E4093" s="1">
-        <v>867841</v>
-      </c>
-    </row>
-    <row r="4094" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867840</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4094" s="7">
         <v>46183</v>
       </c>
@@ -89638,10 +90164,10 @@
         <v>72</v>
       </c>
       <c r="E4094" s="1">
-        <v>867840</v>
-      </c>
-    </row>
-    <row r="4095" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867839</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4095" s="7">
         <v>46183</v>
       </c>
@@ -89655,10 +90181,10 @@
         <v>72</v>
       </c>
       <c r="E4095" s="1">
-        <v>867839</v>
-      </c>
-    </row>
-    <row r="4096" spans="1:5" x14ac:dyDescent="0.25">
+        <v>867838</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4096" s="7">
         <v>46183</v>
       </c>
@@ -89672,7 +90198,7 @@
         <v>72</v>
       </c>
       <c r="E4096" s="1">
-        <v>867838</v>
+        <v>867837</v>
       </c>
     </row>
     <row r="4097" spans="1:7" x14ac:dyDescent="0.25">
@@ -89680,16 +90206,16 @@
         <v>46183</v>
       </c>
       <c r="B4097" s="3" t="s">
-        <v>907</v>
+        <v>349</v>
       </c>
       <c r="C4097" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4097" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4097" s="1">
-        <v>867837</v>
+        <v>24</v>
+      </c>
+      <c r="E4097" s="2" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="4098" spans="1:7" x14ac:dyDescent="0.25">
@@ -89706,7 +90232,7 @@
         <v>24</v>
       </c>
       <c r="E4098" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4099" spans="1:7" x14ac:dyDescent="0.25">
@@ -89723,7 +90249,7 @@
         <v>24</v>
       </c>
       <c r="E4099" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4100" spans="1:7" x14ac:dyDescent="0.25">
@@ -89740,7 +90266,7 @@
         <v>24</v>
       </c>
       <c r="E4100" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="4101" spans="1:7" x14ac:dyDescent="0.25">
@@ -89757,7 +90283,7 @@
         <v>24</v>
       </c>
       <c r="E4101" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="4102" spans="1:7" x14ac:dyDescent="0.25">
@@ -89765,16 +90291,16 @@
         <v>46183</v>
       </c>
       <c r="B4102" s="3" t="s">
-        <v>349</v>
+        <v>1173</v>
       </c>
       <c r="C4102" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D4102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4102" s="2" t="s">
-        <v>994</v>
+        <v>2252</v>
+      </c>
+      <c r="E4102" s="1">
+        <v>136324</v>
       </c>
     </row>
     <row r="4103" spans="1:7" x14ac:dyDescent="0.25">
@@ -89782,16 +90308,16 @@
         <v>46183</v>
       </c>
       <c r="B4103" s="3" t="s">
-        <v>1173</v>
+        <v>275</v>
       </c>
       <c r="C4103" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4103" s="1" t="s">
-        <v>2252</v>
-      </c>
-      <c r="E4103" s="1">
-        <v>136324</v>
+        <v>26</v>
+      </c>
+      <c r="E4103" s="2" t="s">
+        <v>3010</v>
       </c>
     </row>
     <row r="4104" spans="1:7" x14ac:dyDescent="0.25">
@@ -89808,7 +90334,7 @@
         <v>26</v>
       </c>
       <c r="E4104" s="2" t="s">
-        <v>3010</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="4105" spans="1:7" x14ac:dyDescent="0.25">
@@ -89850,13 +90376,13 @@
         <v>46183</v>
       </c>
       <c r="B4107" s="3" t="s">
-        <v>275</v>
+        <v>878</v>
       </c>
       <c r="C4107" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4107" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4107" s="2" t="s">
         <v>3192</v>
@@ -89884,13 +90410,13 @@
         <v>46183</v>
       </c>
       <c r="B4109" s="3" t="s">
-        <v>878</v>
+        <v>2892</v>
       </c>
       <c r="C4109" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4109" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E4109" s="2" t="s">
         <v>3194</v>
@@ -89901,16 +90427,22 @@
         <v>46183</v>
       </c>
       <c r="B4110" s="3" t="s">
-        <v>2892</v>
+        <v>73</v>
       </c>
       <c r="C4110" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4110" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E4110" s="2" t="s">
         <v>3195</v>
+      </c>
+      <c r="F4110" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4110" s="7">
+        <v>46183</v>
       </c>
     </row>
     <row r="4111" spans="1:7" x14ac:dyDescent="0.25">
@@ -89933,7 +90465,7 @@
         <v>0</v>
       </c>
       <c r="G4111" s="7">
-        <v>46183</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="4112" spans="1:7" x14ac:dyDescent="0.25">
@@ -89952,6 +90484,12 @@
       <c r="E4112" s="2" t="s">
         <v>3197</v>
       </c>
+      <c r="F4112" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4112" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="4113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4113" s="7">
@@ -89969,22 +90507,34 @@
       <c r="E4113" s="2" t="s">
         <v>3198</v>
       </c>
+      <c r="F4113" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4113" s="7">
+        <v>46184</v>
+      </c>
     </row>
     <row r="4114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4114" s="7">
         <v>46183</v>
       </c>
       <c r="B4114" s="3" t="s">
-        <v>73</v>
+        <v>245</v>
       </c>
       <c r="C4114" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D4114" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4114" s="2" t="s">
         <v>3199</v>
+      </c>
+      <c r="F4114" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4114" s="7">
+        <v>46183</v>
       </c>
     </row>
     <row r="4115" spans="1:8" x14ac:dyDescent="0.25">
@@ -89992,13 +90542,13 @@
         <v>46183</v>
       </c>
       <c r="B4115" s="3" t="s">
-        <v>245</v>
+        <v>2212</v>
       </c>
       <c r="C4115" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D4115" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4115" s="2" t="s">
         <v>3200</v>
@@ -90008,6 +90558,9 @@
       </c>
       <c r="G4115" s="7">
         <v>46183</v>
+      </c>
+      <c r="H4115" s="1" t="s">
+        <v>3202</v>
       </c>
     </row>
     <row r="4116" spans="1:8" x14ac:dyDescent="0.25">
@@ -90041,25 +90594,16 @@
         <v>46183</v>
       </c>
       <c r="B4117" s="3" t="s">
-        <v>2212</v>
+        <v>1176</v>
       </c>
       <c r="C4117" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D4117" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4117" s="2" t="s">
-        <v>3202</v>
-      </c>
-      <c r="F4117" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4117" s="7">
-        <v>46183</v>
-      </c>
-      <c r="H4117" s="1" t="s">
-        <v>3204</v>
+        <v>36</v>
+      </c>
+      <c r="E4117" s="1">
+        <v>990351</v>
       </c>
     </row>
     <row r="4118" spans="1:8" x14ac:dyDescent="0.25">
@@ -90076,7 +90620,7 @@
         <v>36</v>
       </c>
       <c r="E4118" s="1">
-        <v>990351</v>
+        <v>990352</v>
       </c>
     </row>
     <row r="4119" spans="1:8" x14ac:dyDescent="0.25">
@@ -90093,7 +90637,7 @@
         <v>36</v>
       </c>
       <c r="E4119" s="1">
-        <v>990352</v>
+        <v>990353</v>
       </c>
     </row>
     <row r="4120" spans="1:8" x14ac:dyDescent="0.25">
@@ -90110,7 +90654,7 @@
         <v>36</v>
       </c>
       <c r="E4120" s="1">
-        <v>990353</v>
+        <v>990354</v>
       </c>
     </row>
     <row r="4121" spans="1:8" x14ac:dyDescent="0.25">
@@ -90127,7 +90671,7 @@
         <v>36</v>
       </c>
       <c r="E4121" s="1">
-        <v>990354</v>
+        <v>990355</v>
       </c>
     </row>
     <row r="4122" spans="1:8" x14ac:dyDescent="0.25">
@@ -90135,16 +90679,16 @@
         <v>46183</v>
       </c>
       <c r="B4122" s="3" t="s">
-        <v>1176</v>
+        <v>245</v>
       </c>
       <c r="C4122" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D4122" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4122" s="1">
-        <v>990355</v>
+        <v>20</v>
+      </c>
+      <c r="E4122" s="2" t="s">
+        <v>3204</v>
       </c>
     </row>
     <row r="4123" spans="1:8" x14ac:dyDescent="0.25">
@@ -90203,16 +90747,16 @@
         <v>46183</v>
       </c>
       <c r="B4126" s="3" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C4126" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D4126" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4126" s="2" t="s">
-        <v>3208</v>
+        <v>74</v>
+      </c>
+      <c r="E4126" s="1">
+        <v>450714</v>
       </c>
     </row>
     <row r="4127" spans="1:8" x14ac:dyDescent="0.25">
@@ -90229,7 +90773,7 @@
         <v>74</v>
       </c>
       <c r="E4127" s="1">
-        <v>450714</v>
+        <v>450715</v>
       </c>
     </row>
     <row r="4128" spans="1:8" x14ac:dyDescent="0.25">
@@ -90246,7 +90790,7 @@
         <v>74</v>
       </c>
       <c r="E4128" s="1">
-        <v>450715</v>
+        <v>450716</v>
       </c>
     </row>
     <row r="4129" spans="1:8" x14ac:dyDescent="0.25">
@@ -90263,7 +90807,7 @@
         <v>74</v>
       </c>
       <c r="E4129" s="1">
-        <v>450716</v>
+        <v>450717</v>
       </c>
     </row>
     <row r="4130" spans="1:8" x14ac:dyDescent="0.25">
@@ -90280,7 +90824,7 @@
         <v>74</v>
       </c>
       <c r="E4130" s="1">
-        <v>450717</v>
+        <v>450718</v>
       </c>
     </row>
     <row r="4131" spans="1:8" x14ac:dyDescent="0.25">
@@ -90297,7 +90841,7 @@
         <v>74</v>
       </c>
       <c r="E4131" s="1">
-        <v>450718</v>
+        <v>450719</v>
       </c>
     </row>
     <row r="4132" spans="1:8" x14ac:dyDescent="0.25">
@@ -90314,7 +90858,7 @@
         <v>74</v>
       </c>
       <c r="E4132" s="1">
-        <v>450719</v>
+        <v>450720</v>
       </c>
     </row>
     <row r="4133" spans="1:8" x14ac:dyDescent="0.25">
@@ -90331,7 +90875,7 @@
         <v>74</v>
       </c>
       <c r="E4133" s="1">
-        <v>450720</v>
+        <v>450721</v>
       </c>
     </row>
     <row r="4134" spans="1:8" x14ac:dyDescent="0.25">
@@ -90348,7 +90892,7 @@
         <v>74</v>
       </c>
       <c r="E4134" s="1">
-        <v>450721</v>
+        <v>450722</v>
       </c>
     </row>
     <row r="4135" spans="1:8" x14ac:dyDescent="0.25">
@@ -90365,7 +90909,7 @@
         <v>74</v>
       </c>
       <c r="E4135" s="1">
-        <v>450722</v>
+        <v>450723</v>
       </c>
     </row>
     <row r="4136" spans="1:8" x14ac:dyDescent="0.25">
@@ -90373,16 +90917,16 @@
         <v>46183</v>
       </c>
       <c r="B4136" s="3" t="s">
-        <v>135</v>
+        <v>3208</v>
       </c>
       <c r="C4136" s="1" t="s">
-        <v>3</v>
+        <v>3209</v>
       </c>
       <c r="D4136" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4136" s="1">
-        <v>450723</v>
+        <v>4</v>
+      </c>
+      <c r="E4136" s="2" t="s">
+        <v>2482</v>
       </c>
     </row>
     <row r="4137" spans="1:8" x14ac:dyDescent="0.25">
@@ -90390,16 +90934,16 @@
         <v>46183</v>
       </c>
       <c r="B4137" s="3" t="s">
+        <v>3208</v>
+      </c>
+      <c r="C4137" s="1" t="s">
         <v>3209</v>
-      </c>
-      <c r="C4137" s="1" t="s">
-        <v>3210</v>
       </c>
       <c r="D4137" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4137" s="2" t="s">
-        <v>2482</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="4138" spans="1:8" x14ac:dyDescent="0.25">
@@ -90407,10 +90951,10 @@
         <v>46183</v>
       </c>
       <c r="B4138" s="3" t="s">
+        <v>3208</v>
+      </c>
+      <c r="C4138" s="1" t="s">
         <v>3209</v>
-      </c>
-      <c r="C4138" s="1" t="s">
-        <v>3210</v>
       </c>
       <c r="D4138" s="1" t="s">
         <v>4</v>
@@ -90424,10 +90968,10 @@
         <v>46183</v>
       </c>
       <c r="B4139" s="3" t="s">
+        <v>3208</v>
+      </c>
+      <c r="C4139" s="1" t="s">
         <v>3209</v>
-      </c>
-      <c r="C4139" s="1" t="s">
-        <v>3210</v>
       </c>
       <c r="D4139" s="1" t="s">
         <v>4</v>
@@ -90441,16 +90985,16 @@
         <v>46183</v>
       </c>
       <c r="B4140" s="3" t="s">
+        <v>3208</v>
+      </c>
+      <c r="C4140" s="1" t="s">
         <v>3209</v>
-      </c>
-      <c r="C4140" s="1" t="s">
-        <v>3210</v>
       </c>
       <c r="D4140" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4140" s="2" t="s">
-        <v>3213</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4141" spans="1:8" x14ac:dyDescent="0.25">
@@ -90458,16 +91002,16 @@
         <v>46183</v>
       </c>
       <c r="B4141" s="3" t="s">
+        <v>3208</v>
+      </c>
+      <c r="C4141" s="1" t="s">
         <v>3209</v>
-      </c>
-      <c r="C4141" s="1" t="s">
-        <v>3210</v>
       </c>
       <c r="D4141" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4141" s="2" t="s">
-        <v>665</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="4142" spans="1:8" x14ac:dyDescent="0.25">
@@ -90475,16 +91019,25 @@
         <v>46183</v>
       </c>
       <c r="B4142" s="3" t="s">
-        <v>3209</v>
+        <v>3214</v>
       </c>
       <c r="C4142" s="1" t="s">
-        <v>3210</v>
+        <v>25</v>
       </c>
       <c r="D4142" s="1" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="E4142" s="2" t="s">
-        <v>3214</v>
+        <v>3215</v>
+      </c>
+      <c r="F4142" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4142" s="7">
+        <v>46183</v>
+      </c>
+      <c r="H4142" s="1" t="s">
+        <v>3217</v>
       </c>
     </row>
     <row r="4143" spans="1:8" x14ac:dyDescent="0.25">
@@ -90492,7 +91045,7 @@
         <v>46183</v>
       </c>
       <c r="B4143" s="3" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="C4143" s="1" t="s">
         <v>25</v>
@@ -90518,16 +91071,16 @@
         <v>46183</v>
       </c>
       <c r="B4144" s="3" t="s">
-        <v>3215</v>
+        <v>320</v>
       </c>
       <c r="C4144" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4144" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4144" s="2" t="s">
-        <v>3217</v>
+        <v>49</v>
+      </c>
+      <c r="E4144" s="1">
+        <v>115544</v>
       </c>
       <c r="F4144" s="1" t="s">
         <v>0</v>
@@ -90544,16 +91097,16 @@
         <v>46183</v>
       </c>
       <c r="B4145" s="3" t="s">
-        <v>320</v>
+        <v>2378</v>
       </c>
       <c r="C4145" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4145" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4145" s="1">
-        <v>115544</v>
+        <v>2380</v>
+      </c>
+      <c r="E4145" s="2" t="s">
+        <v>1164</v>
       </c>
       <c r="F4145" s="1" t="s">
         <v>0</v>
@@ -90567,50 +91120,1268 @@
     </row>
     <row r="4146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4146" s="7">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B4146" s="3" t="s">
-        <v>2378</v>
+        <v>2961</v>
       </c>
       <c r="C4146" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4146" s="1" t="s">
-        <v>2380</v>
-      </c>
-      <c r="E4146" s="2" t="s">
-        <v>1164</v>
+        <v>22</v>
+      </c>
+      <c r="E4146" s="1">
+        <v>932842</v>
       </c>
       <c r="F4146" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4146" s="7">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H4146" s="1" t="s">
         <v>3221</v>
       </c>
     </row>
-    <row r="1045525" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1045525" s="7"/>
-    </row>
-    <row r="1045535" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1045535" s="7"/>
-    </row>
-    <row r="1048538" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1048538" s="7"/>
+    <row r="4147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4147" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4147" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C4147" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4147" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4147" s="2" t="s">
+        <v>3222</v>
+      </c>
+      <c r="F4147" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4147" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4148" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4148" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C4148" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4148" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4148" s="2" t="s">
+        <v>3223</v>
+      </c>
+      <c r="F4148" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4148" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4149" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4149" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C4149" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4149" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4149" s="2" t="s">
+        <v>3224</v>
+      </c>
+      <c r="F4149" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4149" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4150" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4150" s="3" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C4150" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4150" s="1" t="s">
+        <v>3226</v>
+      </c>
+      <c r="E4150" s="2" t="s">
+        <v>3227</v>
+      </c>
+      <c r="F4150" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4150" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4151" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4151" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C4151" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4151" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4151" s="2" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4152" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4152" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C4152" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4152" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4152" s="2" t="s">
+        <v>3229</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4153" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4153" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C4153" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4153" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4153" s="2" t="s">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4154" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4154" s="3" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C4154" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4154" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4154" s="1">
+        <v>806529</v>
+      </c>
+      <c r="F4154" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4154" s="7">
+        <v>46184</v>
+      </c>
+      <c r="H4154" s="1" t="s">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4155" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4155" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4155" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4155" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4155" s="2" t="s">
+        <v>3232</v>
+      </c>
+      <c r="F4155" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4155" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4156" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4156" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C4156" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4156" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4156" s="2" t="s">
+        <v>3234</v>
+      </c>
+      <c r="F4156" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4156" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4157" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4157" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4157" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4157" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4157" s="2" t="s">
+        <v>3235</v>
+      </c>
+      <c r="F4157" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4157" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4158" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4158" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C4158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4158" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4158" s="2" t="s">
+        <v>3236</v>
+      </c>
+      <c r="F4158" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4158" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4159" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4159" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C4159" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4159" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4159" s="2" t="s">
+        <v>3238</v>
+      </c>
+      <c r="F4159" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4159" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4160" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4160" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C4160" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4160" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4160" s="2" t="s">
+        <v>3240</v>
+      </c>
+      <c r="F4160" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4160" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4161" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4161" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C4161" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4161" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4161" s="2" t="s">
+        <v>3241</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4162" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4162" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C4162" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4162" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4162" s="2" t="s">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4163" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4163" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C4163" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4163" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4163" s="2" t="s">
+        <v>3243</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4164" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4164" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C4164" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4164" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4164" s="2" t="s">
+        <v>3244</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4165" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4165" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C4165" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4165" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4165" s="2" t="s">
+        <v>3245</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4166" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4166" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C4166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4166" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4166" s="2" t="s">
+        <v>3246</v>
+      </c>
+    </row>
+    <row r="4167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4167" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4167" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C4167" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4167" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4167" s="2" t="s">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4168" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4168" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4168" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4168" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4168" s="2" t="s">
+        <v>3248</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4169" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4169" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4169" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4169" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4169" s="2" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4170" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4170" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4170" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4170" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4170" s="2" t="s">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4171" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4171" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4171" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4171" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4171" s="2" t="s">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4172" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4172" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4172" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4172" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4172" s="2" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4173" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4173" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4173" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4173" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4173" s="2" t="s">
+        <v>3253</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4174" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4174" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4174" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4174" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4174" s="2" t="s">
+        <v>3254</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4175" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4175" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4175" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4175" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4175" s="2" t="s">
+        <v>3255</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4176" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4176" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4176" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4176" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4176" s="2" t="s">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4177" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4177" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C4177" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4177" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4177" s="2" t="s">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4178" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4178" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C4178" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4178" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4178" s="2" t="s">
+        <v>3258</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4179" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4179" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C4179" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4179" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4179" s="2" t="s">
+        <v>3259</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4180" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4180" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C4180" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4180" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4180" s="2" t="s">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4181" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4181" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4181" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4181" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4181" s="2" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4182" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4182" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4182" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4182" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4182" s="2" t="s">
+        <v>3262</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4183" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4183" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4183" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4183" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4183" s="2" t="s">
+        <v>3263</v>
+      </c>
+    </row>
+    <row r="4184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4184" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4184" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4184" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4184" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4184" s="2" t="s">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="4185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4185" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4185" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4185" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4185" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4185" s="2" t="s">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="4186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4186" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4186" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4186" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4186" s="2">
+        <v>186171</v>
+      </c>
+    </row>
+    <row r="4187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4187" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4187" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4187" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4187" s="2">
+        <v>186172</v>
+      </c>
+    </row>
+    <row r="4188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4188" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4188" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4188" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4188" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4188" s="2">
+        <v>186173</v>
+      </c>
+    </row>
+    <row r="4189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4189" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4189" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4189" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4189" s="2">
+        <v>186174</v>
+      </c>
+    </row>
+    <row r="4190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4190" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4190" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4190" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4190" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4190" s="2">
+        <v>186175</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4191" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4191" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4191" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4191" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4191" s="2" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="4192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4192" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4192" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4192" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4192" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4192" s="2" t="s">
+        <v>3267</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4193" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4193" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4193" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4193" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4193" s="2" t="s">
+        <v>3268</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4194" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4194" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4194" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4194" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4194" s="2" t="s">
+        <v>3269</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4195" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4195" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4195" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4195" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4195" s="2" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4196" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4196" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4196" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4196" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4196" s="2" t="s">
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4197" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4197" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4197" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4197" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4197" s="2" t="s">
+        <v>3272</v>
+      </c>
+    </row>
+    <row r="4198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4198" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4198" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4198" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4198" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4198" s="2" t="s">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4199" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4199" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4199" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4199" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4199" s="2" t="s">
+        <v>3274</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4200" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4200" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C4200" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D4200" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4200" s="2" t="s">
+        <v>3275</v>
+      </c>
+      <c r="F4200" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4200" s="7">
+        <v>46184</v>
+      </c>
+      <c r="H4200" s="1" t="s">
+        <v>3278</v>
+      </c>
+    </row>
+    <row r="4201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4201" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4201" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C4201" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D4201" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4201" s="2" t="s">
+        <v>3276</v>
+      </c>
+      <c r="F4201" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4201" s="7">
+        <v>46184</v>
+      </c>
+      <c r="H4201" s="1" t="s">
+        <v>3279</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4202" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4202" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C4202" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D4202" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4202" s="2" t="s">
+        <v>3277</v>
+      </c>
+      <c r="F4202" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4202" s="7">
+        <v>46184</v>
+      </c>
+      <c r="H4202" s="1" t="s">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="4203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4203" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4203" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="C4203" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4203" s="1" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E4203" s="2" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4204" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4204" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="C4204" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4204" s="1" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E4204" s="2" t="s">
+        <v>3282</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4205" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4205" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C4205" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4205" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4205" s="2" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4206" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4206" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C4206" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4206" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4206" s="2" t="s">
+        <v>3284</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4207" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4207" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C4207" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4207" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4207" s="2" t="s">
+        <v>3285</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4208" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4208" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C4208" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4208" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4208" s="2" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4209" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B4209" s="3" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C4209" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4209" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4209" s="1">
+        <v>946307</v>
+      </c>
+      <c r="F4209" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4209" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="4210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4210" s="1" t="s">
+        <v>3288</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4211" s="1" t="s">
+        <v>3288</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4212" s="1" t="s">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="4213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4213" s="1" t="s">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="4214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4214" s="1" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C4217" s="1" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4230" s="23"/>
+      <c r="B4230" s="22"/>
+      <c r="C4230" s="23"/>
+      <c r="D4230" s="23"/>
+      <c r="E4230" s="23"/>
+    </row>
+    <row r="4231" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4231" s="21"/>
+      <c r="B4231" s="20"/>
+      <c r="C4231" s="21"/>
+      <c r="D4231" s="21"/>
+      <c r="E4231" s="21"/>
+    </row>
+    <row r="1045524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1045524" s="7"/>
+    </row>
+    <row r="1045534" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1045534" s="7"/>
+    </row>
+    <row r="1048537" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1048537" s="7"/>
+    </row>
+    <row r="1048553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1048553" s="7"/>
     </row>
     <row r="1048554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1048554" s="7"/>
       <c r="G1048554" s="7"/>
     </row>
-    <row r="1048555" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1048555" s="7"/>
-      <c r="G1048555" s="7"/>
-    </row>
-    <row r="1048558" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1048558" s="7"/>
+    <row r="1048557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1048557" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H4214" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H172">
     <sortCondition ref="B3:B172"/>
   </sortState>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD06BF4-245B-40C9-A625-A03D1D0F902D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F51579F-B361-470F-B4B4-11485A8C769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4243</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17063" uniqueCount="3295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17236" uniqueCount="3317">
   <si>
     <t>USE</t>
   </si>
@@ -8995,9 +8995,6 @@
     <t>MEGHA MEDICAL AGENCIES</t>
   </si>
   <si>
-    <t>U</t>
-  </si>
-  <si>
     <t>10586/-</t>
   </si>
   <si>
@@ -9899,6 +9896,75 @@
   </si>
   <si>
     <t xml:space="preserve">              </t>
+  </si>
+  <si>
+    <t>000275</t>
+  </si>
+  <si>
+    <t>74661/-</t>
+  </si>
+  <si>
+    <t>42552/-</t>
+  </si>
+  <si>
+    <t>002748</t>
+  </si>
+  <si>
+    <t>000531</t>
+  </si>
+  <si>
+    <t>000532</t>
+  </si>
+  <si>
+    <t>000533</t>
+  </si>
+  <si>
+    <t>000534</t>
+  </si>
+  <si>
+    <t>000535</t>
+  </si>
+  <si>
+    <t>033392</t>
+  </si>
+  <si>
+    <t>033391</t>
+  </si>
+  <si>
+    <t>033155</t>
+  </si>
+  <si>
+    <t>033156</t>
+  </si>
+  <si>
+    <t>086535</t>
+  </si>
+  <si>
+    <t>52645/-</t>
+  </si>
+  <si>
+    <t>000283</t>
+  </si>
+  <si>
+    <t>54406/-</t>
+  </si>
+  <si>
+    <t>008962</t>
+  </si>
+  <si>
+    <t>216/-</t>
+  </si>
+  <si>
+    <t>008961</t>
+  </si>
+  <si>
+    <t>20490/-</t>
+  </si>
+  <si>
+    <t>008960</t>
+  </si>
+  <si>
+    <t>2822/-</t>
   </si>
   <si>
     <t>Party Name</t>
@@ -9992,7 +10058,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -10015,41 +10081,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -10102,18 +10140,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -10460,7 +10486,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>3292</v>
+        <v>3314</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>365</v>
@@ -10469,10 +10495,10 @@
         <v>692</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3293</v>
+        <v>3315</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3294</v>
+        <v>3316</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>391</v>
@@ -18265,6 +18291,12 @@
       <c r="E411" s="2" t="s">
         <v>714</v>
       </c>
+      <c r="F411" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G411" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="412" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="7">
@@ -19883,6 +19915,12 @@
       <c r="E495" s="2" t="s">
         <v>1416</v>
       </c>
+      <c r="F495" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G495" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="496" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="7">
@@ -20831,6 +20869,12 @@
       <c r="E540" s="2" t="s">
         <v>1328</v>
       </c>
+      <c r="F540" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G540" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="541" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="7">
@@ -23176,6 +23220,12 @@
       <c r="E660" s="1">
         <v>450654</v>
       </c>
+      <c r="F660" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G660" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="661" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="7">
@@ -23193,6 +23243,12 @@
       <c r="E661" s="1">
         <v>450655</v>
       </c>
+      <c r="F661" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G661" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="662" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="7">
@@ -25657,6 +25713,12 @@
       <c r="E797" s="2" t="s">
         <v>403</v>
       </c>
+      <c r="F797" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G797" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="798" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="7">
@@ -25674,6 +25736,12 @@
       <c r="E798" s="2" t="s">
         <v>404</v>
       </c>
+      <c r="F798" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G798" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="799" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="7">
@@ -25691,6 +25759,12 @@
       <c r="E799" s="2" t="s">
         <v>1022</v>
       </c>
+      <c r="F799" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G799" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="800" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="7">
@@ -27296,6 +27370,12 @@
       <c r="E891" s="2" t="s">
         <v>1947</v>
       </c>
+      <c r="F891" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G891" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="892" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="7">
@@ -27313,6 +27393,12 @@
       <c r="E892" s="2" t="s">
         <v>1948</v>
       </c>
+      <c r="F892" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G892" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="893" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="7">
@@ -29223,6 +29309,12 @@
       <c r="E987" s="2" t="s">
         <v>869</v>
       </c>
+      <c r="F987" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G987" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="988" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="7">
@@ -34463,6 +34555,12 @@
       <c r="E1251" s="1">
         <v>958213</v>
       </c>
+      <c r="F1251" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1251" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1252" s="7">
@@ -35148,7 +35246,10 @@
         <v>1582</v>
       </c>
       <c r="F1285" s="1" t="s">
-        <v>2990</v>
+        <v>0</v>
+      </c>
+      <c r="G1285" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="1286" spans="1:7" x14ac:dyDescent="0.25">
@@ -38321,6 +38422,12 @@
       <c r="E1454" s="2" t="s">
         <v>1500</v>
       </c>
+      <c r="F1454" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1454" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1455" s="7">
@@ -38757,6 +38864,12 @@
       <c r="E1474" s="2" t="s">
         <v>978</v>
       </c>
+      <c r="F1474" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1474" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1475" s="7">
@@ -39737,6 +39850,12 @@
       <c r="E1527" s="14" t="s">
         <v>885</v>
       </c>
+      <c r="F1527" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1527" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1528" s="7">
@@ -41985,6 +42104,12 @@
       <c r="E1640" s="2" t="s">
         <v>1539</v>
       </c>
+      <c r="F1640" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1640" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1641" s="7">
@@ -44246,6 +44371,12 @@
       <c r="E1755" s="2" t="s">
         <v>1863</v>
       </c>
+      <c r="F1755" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1755" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1756" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1756" s="7">
@@ -44339,7 +44470,12 @@
       <c r="E1760" s="2" t="s">
         <v>1868</v>
       </c>
-      <c r="G1760" s="7"/>
+      <c r="F1760" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1760" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="1761" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1761" s="7">
@@ -49940,6 +50076,12 @@
       <c r="E2050" s="2" t="s">
         <v>1054</v>
       </c>
+      <c r="F2050" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2050" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2051" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2051" s="7">
@@ -51049,6 +51191,12 @@
       <c r="E2105" s="2" t="s">
         <v>457</v>
       </c>
+      <c r="F2105" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2105" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2106" s="7">
@@ -51066,6 +51214,12 @@
       <c r="E2106" s="2" t="s">
         <v>458</v>
       </c>
+      <c r="F2106" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2106" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2107" s="15" t="s">
@@ -53795,7 +53949,7 @@
         <v>54</v>
       </c>
       <c r="D2249" s="1" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="E2249" s="2" t="s">
         <v>1912</v>
@@ -54497,6 +54651,12 @@
       <c r="E2284" s="2" t="s">
         <v>1895</v>
       </c>
+      <c r="F2284" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2284" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2285" s="7">
@@ -54599,6 +54759,12 @@
       <c r="E2290" s="1">
         <v>332593</v>
       </c>
+      <c r="F2290" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2290" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2291" s="7">
@@ -56369,6 +56535,12 @@
       <c r="E2378" s="2" t="s">
         <v>1353</v>
       </c>
+      <c r="F2378" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2378" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2379" s="7">
@@ -56386,6 +56558,12 @@
       <c r="E2379" s="2" t="s">
         <v>1354</v>
       </c>
+      <c r="F2379" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2379" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2380" s="7">
@@ -56552,12 +56730,7 @@
       <c r="E2387" s="1">
         <v>733741</v>
       </c>
-      <c r="F2387" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2387" s="7">
-        <v>46165</v>
-      </c>
+      <c r="G2387" s="7"/>
     </row>
     <row r="2388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2388" s="7">
@@ -56643,6 +56816,12 @@
       </c>
       <c r="E2391" s="1">
         <v>733746</v>
+      </c>
+      <c r="F2391" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2391" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="2392" spans="1:7" x14ac:dyDescent="0.25">
@@ -61242,7 +61421,12 @@
       <c r="E2622" s="2" t="s">
         <v>2152</v>
       </c>
-      <c r="G2622" s="7"/>
+      <c r="F2622" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2622" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2623" s="7">
@@ -64370,6 +64554,12 @@
       <c r="E2770" s="1">
         <v>383193</v>
       </c>
+      <c r="F2770" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2770" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2771" s="7">
@@ -64387,6 +64577,12 @@
       <c r="E2771" s="1">
         <v>383194</v>
       </c>
+      <c r="F2771" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2771" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2772" s="7">
@@ -64404,6 +64600,12 @@
       <c r="E2772" s="1">
         <v>383195</v>
       </c>
+      <c r="F2772" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2772" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2773" s="7">
@@ -64736,6 +64938,12 @@
       <c r="E2788" s="2" t="s">
         <v>2267</v>
       </c>
+      <c r="F2788" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2788" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2789" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2789" s="7">
@@ -65175,6 +65383,12 @@
       <c r="E2811" s="2" t="s">
         <v>2290</v>
       </c>
+      <c r="F2811" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2811" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2812" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2812" s="7">
@@ -67561,7 +67775,7 @@
         <v>0</v>
       </c>
       <c r="G2923" s="7">
-        <v>46165</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="2924" spans="1:8" x14ac:dyDescent="0.25">
@@ -67603,12 +67817,7 @@
       <c r="E2925" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="F2925" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2925" s="7">
-        <v>46165</v>
-      </c>
+      <c r="G2925" s="7"/>
     </row>
     <row r="2926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2926" s="7">
@@ -67815,6 +68024,12 @@
       <c r="E2935" s="2" t="s">
         <v>2420</v>
       </c>
+      <c r="F2935" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2935" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="2936" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2936" s="7">
@@ -67969,7 +68184,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="2945" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2945" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2945" s="7">
         <v>46165</v>
       </c>
@@ -67986,7 +68201,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="2946" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2946" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2946" s="7">
         <v>46165</v>
       </c>
@@ -68003,7 +68218,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="2947" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2947" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2947" s="7">
         <v>46165</v>
       </c>
@@ -68019,8 +68234,9 @@
       <c r="E2947" s="2" t="s">
         <v>2432</v>
       </c>
-    </row>
-    <row r="2948" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G2947" s="7"/>
+    </row>
+    <row r="2948" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2948" s="7">
         <v>46165</v>
       </c>
@@ -68036,8 +68252,14 @@
       <c r="E2948" s="2" t="s">
         <v>2433</v>
       </c>
-    </row>
-    <row r="2949" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2948" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2948" s="7">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2949" s="7">
         <v>46165</v>
       </c>
@@ -68054,7 +68276,7 @@
         <v>2434</v>
       </c>
     </row>
-    <row r="2950" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2950" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2950" s="7">
         <v>46165</v>
       </c>
@@ -68071,7 +68293,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="2951" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2951" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2951" s="7">
         <v>46165</v>
       </c>
@@ -68088,7 +68310,7 @@
         <v>2436</v>
       </c>
     </row>
-    <row r="2952" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2952" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2952" s="7">
         <v>46165</v>
       </c>
@@ -68105,7 +68327,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="2953" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2953" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2953" s="7">
         <v>46165</v>
       </c>
@@ -68122,7 +68344,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="2954" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2954" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2954" s="7">
         <v>46165</v>
       </c>
@@ -68139,7 +68361,7 @@
         <v>2439</v>
       </c>
     </row>
-    <row r="2955" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2955" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2955" s="7">
         <v>46165</v>
       </c>
@@ -68156,7 +68378,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="2956" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2956" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2956" s="7">
         <v>46165</v>
       </c>
@@ -68173,7 +68395,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="2957" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2957" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2957" s="7">
         <v>46165</v>
       </c>
@@ -68190,7 +68412,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="2958" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2958" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2958" s="7">
         <v>46165</v>
       </c>
@@ -68207,7 +68429,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="2959" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2959" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2959" s="7">
         <v>46165</v>
       </c>
@@ -68224,7 +68446,7 @@
         <v>2434</v>
       </c>
     </row>
-    <row r="2960" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2960" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2960" s="7">
         <v>46165</v>
       </c>
@@ -69150,6 +69372,12 @@
       <c r="E3002" s="2" t="s">
         <v>2488</v>
       </c>
+      <c r="F3002" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3002" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3003" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3003" s="7">
@@ -70509,7 +70737,7 @@
         <v>46167</v>
       </c>
       <c r="B3069" s="3" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C3069" s="1" t="s">
         <v>2564</v>
@@ -70600,7 +70828,7 @@
         <v>46167</v>
       </c>
       <c r="B3074" s="3" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C3074" s="1" t="s">
         <v>2564</v>
@@ -70623,7 +70851,7 @@
         <v>46167</v>
       </c>
       <c r="B3075" s="3" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C3075" s="1" t="s">
         <v>2564</v>
@@ -70646,7 +70874,7 @@
         <v>46167</v>
       </c>
       <c r="B3076" s="3" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C3076" s="1" t="s">
         <v>2564</v>
@@ -70663,7 +70891,7 @@
         <v>46167</v>
       </c>
       <c r="B3077" s="3" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C3077" s="1" t="s">
         <v>2564</v>
@@ -71707,6 +71935,12 @@
       <c r="E3131" s="1">
         <v>122233</v>
       </c>
+      <c r="F3131" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3131" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3132" s="7">
@@ -72929,6 +73163,12 @@
       <c r="E3187" s="1">
         <v>868289</v>
       </c>
+      <c r="F3187" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3187" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3188" s="7">
@@ -73611,6 +73851,12 @@
       <c r="E3225" s="2" t="s">
         <v>2633</v>
       </c>
+      <c r="F3225" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3225" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3226" s="7">
@@ -73766,6 +74012,12 @@
       <c r="E3232" s="1">
         <v>514069</v>
       </c>
+      <c r="F3232" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3232" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3233" s="7">
@@ -73783,6 +74035,12 @@
       <c r="E3233" s="1">
         <v>514070</v>
       </c>
+      <c r="F3233" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3233" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3234" s="7">
@@ -73800,6 +74058,12 @@
       <c r="E3234" s="1">
         <v>514071</v>
       </c>
+      <c r="F3234" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3234" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3235" s="7">
@@ -73908,6 +74172,12 @@
       <c r="E3240" s="1">
         <v>668424</v>
       </c>
+      <c r="F3240" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3240" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3241" s="7">
@@ -74045,6 +74315,12 @@
       <c r="E3247" s="2" t="s">
         <v>2640</v>
       </c>
+      <c r="F3247" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3247" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3248" s="7">
@@ -75612,6 +75888,12 @@
       <c r="E3329" s="2" t="s">
         <v>2725</v>
       </c>
+      <c r="F3329" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3329" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3330" s="7">
@@ -79965,6 +80247,12 @@
       <c r="E3553" s="2">
         <v>278634</v>
       </c>
+      <c r="F3553" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3553" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3554" s="7">
@@ -79982,6 +80270,12 @@
       <c r="E3554" s="2">
         <v>278635</v>
       </c>
+      <c r="F3554" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3554" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3555" s="7">
@@ -81369,6 +81663,12 @@
       <c r="E3626" s="2" t="s">
         <v>2148</v>
       </c>
+      <c r="F3626" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3626" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3627" s="7">
@@ -81506,6 +81806,12 @@
       <c r="E3633" s="2" t="s">
         <v>2949</v>
       </c>
+      <c r="F3633" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3633" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3634" s="7">
@@ -81523,6 +81829,12 @@
       <c r="E3634" s="2" t="s">
         <v>2950</v>
       </c>
+      <c r="F3634" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3634" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3635" s="7">
@@ -82334,7 +82646,7 @@
         <v>46174</v>
       </c>
       <c r="H3674" s="1" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="3675" spans="1:8" x14ac:dyDescent="0.25">
@@ -82360,7 +82672,7 @@
         <v>46174</v>
       </c>
       <c r="H3675" s="1" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="3676" spans="1:8" x14ac:dyDescent="0.25">
@@ -82386,7 +82698,7 @@
         <v>46174</v>
       </c>
       <c r="H3676" s="1" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="3677" spans="1:8" x14ac:dyDescent="0.25">
@@ -82403,7 +82715,7 @@
         <v>13</v>
       </c>
       <c r="E3677" s="2" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F3677" s="1" t="s">
         <v>0</v>
@@ -82426,7 +82738,7 @@
         <v>15</v>
       </c>
       <c r="E3678" s="2" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F3678" s="1" t="s">
         <v>0</v>
@@ -82440,7 +82752,7 @@
         <v>46174</v>
       </c>
       <c r="B3679" s="3" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="C3679" s="1" t="s">
         <v>23</v>
@@ -82458,7 +82770,7 @@
         <v>46174</v>
       </c>
       <c r="H3679" s="1" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="3680" spans="1:8" x14ac:dyDescent="0.25">
@@ -82509,7 +82821,7 @@
         <v>15</v>
       </c>
       <c r="E3682" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="3683" spans="1:7" x14ac:dyDescent="0.25">
@@ -82526,7 +82838,7 @@
         <v>15</v>
       </c>
       <c r="E3683" s="2" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="3684" spans="1:7" x14ac:dyDescent="0.25">
@@ -82543,7 +82855,7 @@
         <v>15</v>
       </c>
       <c r="E3684" s="2" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="3685" spans="1:7" x14ac:dyDescent="0.25">
@@ -82560,7 +82872,7 @@
         <v>15</v>
       </c>
       <c r="E3685" s="2" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3686" spans="1:7" x14ac:dyDescent="0.25">
@@ -82577,7 +82889,7 @@
         <v>15</v>
       </c>
       <c r="E3686" s="2" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="3687" spans="1:7" x14ac:dyDescent="0.25">
@@ -82594,7 +82906,7 @@
         <v>15</v>
       </c>
       <c r="E3687" s="2" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="3688" spans="1:7" x14ac:dyDescent="0.25">
@@ -82611,7 +82923,7 @@
         <v>13</v>
       </c>
       <c r="E3688" s="2" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="3689" spans="1:7" x14ac:dyDescent="0.25">
@@ -82628,7 +82940,7 @@
         <v>13</v>
       </c>
       <c r="E3689" s="2" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="3690" spans="1:7" x14ac:dyDescent="0.25">
@@ -82645,7 +82957,7 @@
         <v>13</v>
       </c>
       <c r="E3690" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="3691" spans="1:7" x14ac:dyDescent="0.25">
@@ -82662,7 +82974,7 @@
         <v>13</v>
       </c>
       <c r="E3691" s="2" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="3692" spans="1:7" x14ac:dyDescent="0.25">
@@ -82679,7 +82991,7 @@
         <v>15</v>
       </c>
       <c r="E3692" s="2" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="F3692" s="1" t="s">
         <v>0</v>
@@ -82702,7 +83014,7 @@
         <v>15</v>
       </c>
       <c r="E3693" s="2" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="F3693" s="1" t="s">
         <v>0</v>
@@ -82725,7 +83037,7 @@
         <v>15</v>
       </c>
       <c r="E3694" s="2" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="F3694" s="1" t="s">
         <v>0</v>
@@ -82748,7 +83060,7 @@
         <v>26</v>
       </c>
       <c r="E3695" s="2" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="3696" spans="1:7" x14ac:dyDescent="0.25">
@@ -83220,7 +83532,7 @@
         <v>4</v>
       </c>
       <c r="E3721" s="2" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="F3721" s="1" t="s">
         <v>0</v>
@@ -83243,7 +83555,7 @@
         <v>4</v>
       </c>
       <c r="E3722" s="2" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="F3722" s="1" t="s">
         <v>0</v>
@@ -83266,7 +83578,7 @@
         <v>4</v>
       </c>
       <c r="E3723" s="2" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="3724" spans="1:7" x14ac:dyDescent="0.25">
@@ -83283,7 +83595,7 @@
         <v>4</v>
       </c>
       <c r="E3724" s="2" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="3725" spans="1:7" x14ac:dyDescent="0.25">
@@ -83300,7 +83612,7 @@
         <v>4</v>
       </c>
       <c r="E3725" s="2" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="3726" spans="1:7" x14ac:dyDescent="0.25">
@@ -83374,7 +83686,7 @@
         <v>15</v>
       </c>
       <c r="E3729" s="2" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="3730" spans="1:8" x14ac:dyDescent="0.25">
@@ -83391,7 +83703,7 @@
         <v>15</v>
       </c>
       <c r="E3730" s="2" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="3731" spans="1:8" x14ac:dyDescent="0.25">
@@ -83408,7 +83720,7 @@
         <v>15</v>
       </c>
       <c r="E3731" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="3732" spans="1:8" x14ac:dyDescent="0.25">
@@ -83425,7 +83737,7 @@
         <v>15</v>
       </c>
       <c r="E3732" s="2" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F3732" s="1" t="s">
         <v>0</v>
@@ -83448,7 +83760,7 @@
         <v>16</v>
       </c>
       <c r="E3733" s="2" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="3734" spans="1:8" x14ac:dyDescent="0.25">
@@ -83465,7 +83777,7 @@
         <v>16</v>
       </c>
       <c r="E3734" s="2" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="3735" spans="1:8" x14ac:dyDescent="0.25">
@@ -83482,7 +83794,7 @@
         <v>16</v>
       </c>
       <c r="E3735" s="2" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="3736" spans="1:8" x14ac:dyDescent="0.25">
@@ -83499,7 +83811,7 @@
         <v>16</v>
       </c>
       <c r="E3736" s="2" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="F3736" s="1" t="s">
         <v>0</v>
@@ -83522,7 +83834,7 @@
         <v>16</v>
       </c>
       <c r="E3737" s="2" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="G3737" s="7"/>
     </row>
@@ -83549,7 +83861,7 @@
         <v>46174</v>
       </c>
       <c r="H3738" s="1" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="3739" spans="1:8" x14ac:dyDescent="0.25">
@@ -83575,7 +83887,7 @@
         <v>46174</v>
       </c>
       <c r="H3739" s="1" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="3740" spans="1:8" x14ac:dyDescent="0.25">
@@ -83601,7 +83913,7 @@
         <v>46174</v>
       </c>
       <c r="H3740" s="1" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="3741" spans="1:8" x14ac:dyDescent="0.25">
@@ -83618,7 +83930,7 @@
         <v>2380</v>
       </c>
       <c r="E3741" s="2" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="F3741" s="1" t="s">
         <v>0</v>
@@ -83747,7 +84059,7 @@
         <v>46174</v>
       </c>
       <c r="B3747" s="3" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="C3747" s="1" t="s">
         <v>137</v>
@@ -83756,7 +84068,7 @@
         <v>41</v>
       </c>
       <c r="E3747" s="2" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="F3747" s="1" t="s">
         <v>0</v>
@@ -83932,7 +84244,7 @@
         <v>4</v>
       </c>
       <c r="E3757" s="2" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="3758" spans="1:7" x14ac:dyDescent="0.25">
@@ -83949,7 +84261,7 @@
         <v>4</v>
       </c>
       <c r="E3758" s="2" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="3759" spans="1:7" x14ac:dyDescent="0.25">
@@ -84082,6 +84394,12 @@
       <c r="E3765" s="1">
         <v>479853</v>
       </c>
+      <c r="F3765" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3765" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3766" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3766" s="7">
@@ -84099,6 +84417,12 @@
       <c r="E3766" s="1">
         <v>479854</v>
       </c>
+      <c r="F3766" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3766" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3767" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3767" s="7">
@@ -84896,7 +85220,7 @@
         <v>2253</v>
       </c>
       <c r="E3813" s="2" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="G3813" s="7"/>
     </row>
@@ -84931,7 +85255,7 @@
         <v>700</v>
       </c>
       <c r="E3815" s="2" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="F3815" s="1" t="s">
         <v>0</v>
@@ -84954,7 +85278,13 @@
         <v>41</v>
       </c>
       <c r="E3816" s="2" t="s">
-        <v>3037</v>
+        <v>3036</v>
+      </c>
+      <c r="F3816" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3816" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="3817" spans="1:8" x14ac:dyDescent="0.25">
@@ -84971,7 +85301,7 @@
         <v>15</v>
       </c>
       <c r="E3817" s="2" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="F3817" s="1" t="s">
         <v>0</v>
@@ -84980,7 +85310,7 @@
         <v>46177</v>
       </c>
       <c r="H3817" s="1" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="3818" spans="1:8" x14ac:dyDescent="0.25">
@@ -84997,7 +85327,7 @@
         <v>24</v>
       </c>
       <c r="E3818" s="2" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="F3818" s="1" t="s">
         <v>0</v>
@@ -85006,7 +85336,7 @@
         <v>46177</v>
       </c>
       <c r="H3818" s="1" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="3819" spans="1:8" x14ac:dyDescent="0.25">
@@ -85032,7 +85362,7 @@
         <v>46177</v>
       </c>
       <c r="H3819" s="1" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="3820" spans="1:8" x14ac:dyDescent="0.25">
@@ -85040,7 +85370,7 @@
         <v>46177</v>
       </c>
       <c r="B3820" s="3" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="C3820" s="1" t="s">
         <v>12</v>
@@ -85049,7 +85379,7 @@
         <v>24</v>
       </c>
       <c r="E3820" s="2" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="F3820" s="1" t="s">
         <v>0</v>
@@ -85058,7 +85388,7 @@
         <v>46177</v>
       </c>
       <c r="H3820" s="1" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="3821" spans="1:8" x14ac:dyDescent="0.25">
@@ -85075,7 +85405,7 @@
         <v>4</v>
       </c>
       <c r="E3821" s="2" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="F3821" s="1" t="s">
         <v>0</v>
@@ -85098,7 +85428,7 @@
         <v>4</v>
       </c>
       <c r="E3822" s="2" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="3823" spans="1:8" x14ac:dyDescent="0.25">
@@ -85212,7 +85542,7 @@
         <v>22</v>
       </c>
       <c r="E3828" s="2" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="3829" spans="1:7" x14ac:dyDescent="0.25">
@@ -85229,7 +85559,7 @@
         <v>22</v>
       </c>
       <c r="E3829" s="2" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="3830" spans="1:7" x14ac:dyDescent="0.25">
@@ -85294,6 +85624,12 @@
       <c r="E3832" s="1">
         <v>947354</v>
       </c>
+      <c r="F3832" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3832" s="7">
+        <v>46185</v>
+      </c>
     </row>
     <row r="3833" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3833" s="7">
@@ -85487,7 +85823,7 @@
         <v>46177</v>
       </c>
       <c r="B3844" s="3" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C3844" s="1" t="s">
         <v>38</v>
@@ -85510,7 +85846,7 @@
         <v>46177</v>
       </c>
       <c r="B3845" s="3" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C3845" s="1" t="s">
         <v>38</v>
@@ -85533,7 +85869,7 @@
         <v>46177</v>
       </c>
       <c r="B3846" s="3" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C3846" s="1" t="s">
         <v>38</v>
@@ -85556,7 +85892,7 @@
         <v>46177</v>
       </c>
       <c r="B3847" s="3" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C3847" s="1" t="s">
         <v>38</v>
@@ -85573,7 +85909,7 @@
         <v>46177</v>
       </c>
       <c r="B3848" s="3" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C3848" s="1" t="s">
         <v>38</v>
@@ -85599,7 +85935,7 @@
         <v>26</v>
       </c>
       <c r="E3849" s="2" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="3850" spans="1:7" x14ac:dyDescent="0.25">
@@ -85616,7 +85952,7 @@
         <v>26</v>
       </c>
       <c r="E3850" s="2" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="3851" spans="1:7" x14ac:dyDescent="0.25">
@@ -85633,7 +85969,7 @@
         <v>26</v>
       </c>
       <c r="E3851" s="2" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="3852" spans="1:7" x14ac:dyDescent="0.25">
@@ -85650,7 +85986,7 @@
         <v>26</v>
       </c>
       <c r="E3852" s="2" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="3853" spans="1:7" x14ac:dyDescent="0.25">
@@ -85667,7 +86003,7 @@
         <v>26</v>
       </c>
       <c r="E3853" s="2" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="3854" spans="1:7" x14ac:dyDescent="0.25">
@@ -85675,7 +86011,7 @@
         <v>46177</v>
       </c>
       <c r="B3854" s="3" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C3854" s="1" t="s">
         <v>44</v>
@@ -85684,7 +86020,7 @@
         <v>4</v>
       </c>
       <c r="E3854" s="2" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="F3854" s="1" t="s">
         <v>0</v>
@@ -85753,7 +86089,7 @@
         <v>4</v>
       </c>
       <c r="E3857" s="2" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="F3857" s="1" t="s">
         <v>0</v>
@@ -85762,7 +86098,7 @@
         <v>46178</v>
       </c>
       <c r="H3857" s="1" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="3858" spans="1:8" x14ac:dyDescent="0.25">
@@ -85857,7 +86193,7 @@
         <v>46178</v>
       </c>
       <c r="H3861" s="1" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="3862" spans="1:8" x14ac:dyDescent="0.25">
@@ -85883,7 +86219,7 @@
         <v>46178</v>
       </c>
       <c r="H3862" s="1" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="3863" spans="1:8" x14ac:dyDescent="0.25">
@@ -85909,7 +86245,7 @@
         <v>46178</v>
       </c>
       <c r="H3863" s="1" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="3864" spans="1:8" x14ac:dyDescent="0.25">
@@ -85926,7 +86262,7 @@
         <v>82</v>
       </c>
       <c r="E3864" s="2" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="F3864" s="1" t="s">
         <v>0</v>
@@ -85935,7 +86271,7 @@
         <v>46178</v>
       </c>
       <c r="H3864" s="1" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="3865" spans="1:8" x14ac:dyDescent="0.25">
@@ -86063,7 +86399,7 @@
         <v>46178</v>
       </c>
       <c r="B3871" s="3" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C3871" s="1" t="s">
         <v>17</v>
@@ -86152,7 +86488,7 @@
         <v>24</v>
       </c>
       <c r="E3875" s="2" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="3876" spans="1:7" x14ac:dyDescent="0.25">
@@ -86169,7 +86505,7 @@
         <v>24</v>
       </c>
       <c r="E3876" s="2" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="3877" spans="1:7" x14ac:dyDescent="0.25">
@@ -86328,7 +86664,7 @@
         <v>4</v>
       </c>
       <c r="E3885" s="2" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="3886" spans="1:7" x14ac:dyDescent="0.25">
@@ -86345,7 +86681,7 @@
         <v>4</v>
       </c>
       <c r="E3886" s="2" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="3887" spans="1:7" x14ac:dyDescent="0.25">
@@ -86540,7 +86876,7 @@
         <v>46178</v>
       </c>
       <c r="B3898" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3898" s="1" t="s">
         <v>27</v>
@@ -86563,7 +86899,7 @@
         <v>46178</v>
       </c>
       <c r="B3899" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3899" s="1" t="s">
         <v>27</v>
@@ -86580,7 +86916,7 @@
         <v>46178</v>
       </c>
       <c r="B3900" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3900" s="1" t="s">
         <v>27</v>
@@ -86597,7 +86933,7 @@
         <v>46178</v>
       </c>
       <c r="B3901" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3901" s="1" t="s">
         <v>27</v>
@@ -86606,7 +86942,7 @@
         <v>4</v>
       </c>
       <c r="E3901" s="2" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="3902" spans="1:7" x14ac:dyDescent="0.25">
@@ -86614,7 +86950,7 @@
         <v>46178</v>
       </c>
       <c r="B3902" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3902" s="1" t="s">
         <v>27</v>
@@ -86623,7 +86959,7 @@
         <v>4</v>
       </c>
       <c r="E3902" s="2" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="3903" spans="1:7" x14ac:dyDescent="0.25">
@@ -86631,7 +86967,7 @@
         <v>46178</v>
       </c>
       <c r="B3903" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3903" s="1" t="s">
         <v>27</v>
@@ -86640,7 +86976,7 @@
         <v>4</v>
       </c>
       <c r="E3903" s="2" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="3904" spans="1:7" x14ac:dyDescent="0.25">
@@ -86648,7 +86984,7 @@
         <v>46178</v>
       </c>
       <c r="B3904" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3904" s="1" t="s">
         <v>27</v>
@@ -86657,7 +86993,7 @@
         <v>4</v>
       </c>
       <c r="E3904" s="2" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="3905" spans="1:5" x14ac:dyDescent="0.25">
@@ -86665,7 +87001,7 @@
         <v>46178</v>
       </c>
       <c r="B3905" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3905" s="1" t="s">
         <v>27</v>
@@ -86674,7 +87010,7 @@
         <v>4</v>
       </c>
       <c r="E3905" s="2" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="3906" spans="1:5" x14ac:dyDescent="0.25">
@@ -86682,7 +87018,7 @@
         <v>46178</v>
       </c>
       <c r="B3906" s="3" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C3906" s="1" t="s">
         <v>27</v>
@@ -86691,7 +87027,7 @@
         <v>4</v>
       </c>
       <c r="E3906" s="2" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="3907" spans="1:5" x14ac:dyDescent="0.25">
@@ -86699,7 +87035,7 @@
         <v>46178</v>
       </c>
       <c r="B3907" s="3" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="C3907" s="1" t="s">
         <v>37</v>
@@ -86708,7 +87044,7 @@
         <v>49</v>
       </c>
       <c r="E3907" s="2" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="3908" spans="1:5" x14ac:dyDescent="0.25">
@@ -86716,7 +87052,7 @@
         <v>46178</v>
       </c>
       <c r="B3908" s="3" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="C3908" s="1" t="s">
         <v>37</v>
@@ -86725,7 +87061,7 @@
         <v>49</v>
       </c>
       <c r="E3908" s="2" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="3909" spans="1:5" x14ac:dyDescent="0.25">
@@ -86742,7 +87078,7 @@
         <v>120</v>
       </c>
       <c r="E3909" s="2" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="3910" spans="1:5" x14ac:dyDescent="0.25">
@@ -86759,7 +87095,7 @@
         <v>120</v>
       </c>
       <c r="E3910" s="2" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="3911" spans="1:5" x14ac:dyDescent="0.25">
@@ -86776,7 +87112,7 @@
         <v>120</v>
       </c>
       <c r="E3911" s="2" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="3912" spans="1:5" x14ac:dyDescent="0.25">
@@ -86793,7 +87129,7 @@
         <v>120</v>
       </c>
       <c r="E3912" s="2" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="3913" spans="1:5" x14ac:dyDescent="0.25">
@@ -86810,7 +87146,7 @@
         <v>120</v>
       </c>
       <c r="E3913" s="2" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="3914" spans="1:5" x14ac:dyDescent="0.25">
@@ -86827,7 +87163,7 @@
         <v>120</v>
       </c>
       <c r="E3914" s="2" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="3915" spans="1:5" x14ac:dyDescent="0.25">
@@ -86844,7 +87180,7 @@
         <v>120</v>
       </c>
       <c r="E3915" s="2" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="3916" spans="1:5" x14ac:dyDescent="0.25">
@@ -87005,7 +87341,7 @@
         <v>46178</v>
       </c>
       <c r="B3925" s="3" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C3925" s="1" t="s">
         <v>17</v>
@@ -87190,7 +87526,7 @@
         <v>13</v>
       </c>
       <c r="E3935" s="2" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="3936" spans="1:7" x14ac:dyDescent="0.25">
@@ -87207,7 +87543,7 @@
         <v>13</v>
       </c>
       <c r="E3936" s="2" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="3937" spans="1:8" x14ac:dyDescent="0.25">
@@ -87224,7 +87560,7 @@
         <v>13</v>
       </c>
       <c r="E3937" s="2" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="3938" spans="1:8" x14ac:dyDescent="0.25">
@@ -87241,7 +87577,7 @@
         <v>13</v>
       </c>
       <c r="E3938" s="2" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="3939" spans="1:8" x14ac:dyDescent="0.25">
@@ -87258,7 +87594,7 @@
         <v>13</v>
       </c>
       <c r="E3939" s="2" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="3940" spans="1:8" x14ac:dyDescent="0.25">
@@ -87275,7 +87611,7 @@
         <v>13</v>
       </c>
       <c r="E3940" s="2" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="3941" spans="1:8" x14ac:dyDescent="0.25">
@@ -87283,7 +87619,7 @@
         <v>46178</v>
       </c>
       <c r="B3941" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3941" s="1" t="s">
         <v>46</v>
@@ -87306,7 +87642,7 @@
         <v>46178</v>
       </c>
       <c r="B3942" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3942" s="1" t="s">
         <v>46</v>
@@ -87329,7 +87665,7 @@
         <v>46178</v>
       </c>
       <c r="B3943" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3943" s="1" t="s">
         <v>46</v>
@@ -87352,7 +87688,7 @@
         <v>46178</v>
       </c>
       <c r="B3944" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3944" s="1" t="s">
         <v>46</v>
@@ -87369,7 +87705,7 @@
         <v>46178</v>
       </c>
       <c r="B3945" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3945" s="1" t="s">
         <v>46</v>
@@ -87386,7 +87722,7 @@
         <v>46178</v>
       </c>
       <c r="B3946" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3946" s="1" t="s">
         <v>46</v>
@@ -87403,7 +87739,7 @@
         <v>46178</v>
       </c>
       <c r="B3947" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3947" s="1" t="s">
         <v>46</v>
@@ -87420,7 +87756,7 @@
         <v>46178</v>
       </c>
       <c r="B3948" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3948" s="1" t="s">
         <v>46</v>
@@ -87437,7 +87773,7 @@
         <v>46178</v>
       </c>
       <c r="B3949" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3949" s="1" t="s">
         <v>46</v>
@@ -87454,7 +87790,7 @@
         <v>46178</v>
       </c>
       <c r="B3950" s="3" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C3950" s="1" t="s">
         <v>46</v>
@@ -87471,7 +87807,7 @@
         <v>46178</v>
       </c>
       <c r="B3951" s="3" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C3951" s="1" t="s">
         <v>25</v>
@@ -87489,7 +87825,7 @@
         <v>46178</v>
       </c>
       <c r="H3951" s="1" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="3952" spans="1:8" x14ac:dyDescent="0.25">
@@ -87529,7 +87865,7 @@
         <v>24</v>
       </c>
       <c r="E3953" s="2" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F3953" s="1" t="s">
         <v>0</v>
@@ -87552,7 +87888,7 @@
         <v>24</v>
       </c>
       <c r="E3954" s="2" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="F3954" s="1" t="s">
         <v>0</v>
@@ -87575,7 +87911,13 @@
         <v>24</v>
       </c>
       <c r="E3955" s="2" t="s">
-        <v>3099</v>
+        <v>3098</v>
+      </c>
+      <c r="F3955" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3955" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="3956" spans="1:8" x14ac:dyDescent="0.25">
@@ -87592,7 +87934,7 @@
         <v>2061</v>
       </c>
       <c r="E3956" s="2" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="F3956" s="1" t="s">
         <v>0</v>
@@ -87615,7 +87957,7 @@
         <v>15</v>
       </c>
       <c r="E3957" s="2" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="F3957" s="1" t="s">
         <v>0</v>
@@ -87624,7 +87966,7 @@
         <v>46179</v>
       </c>
       <c r="H3957" s="1" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="3958" spans="1:8" x14ac:dyDescent="0.25">
@@ -87641,7 +87983,7 @@
         <v>26</v>
       </c>
       <c r="E3958" s="2" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="F3958" s="1" t="s">
         <v>0</v>
@@ -87733,7 +88075,7 @@
         <v>24</v>
       </c>
       <c r="E3962" s="2" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="F3962" s="1" t="s">
         <v>0</v>
@@ -87756,7 +88098,7 @@
         <v>24</v>
       </c>
       <c r="E3963" s="2" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="F3963" s="1" t="s">
         <v>0</v>
@@ -87779,7 +88121,7 @@
         <v>24</v>
       </c>
       <c r="E3964" s="2" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="F3964" s="1" t="s">
         <v>0</v>
@@ -87802,7 +88144,7 @@
         <v>24</v>
       </c>
       <c r="E3965" s="2" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="F3965" s="1" t="s">
         <v>0</v>
@@ -87825,7 +88167,7 @@
         <v>24</v>
       </c>
       <c r="E3966" s="2" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="F3966" s="1" t="s">
         <v>0</v>
@@ -87865,7 +88207,7 @@
         <v>41</v>
       </c>
       <c r="E3968" s="2" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="3969" spans="1:7" x14ac:dyDescent="0.25">
@@ -87882,7 +88224,7 @@
         <v>41</v>
       </c>
       <c r="E3969" s="2" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="3970" spans="1:7" x14ac:dyDescent="0.25">
@@ -87899,7 +88241,7 @@
         <v>41</v>
       </c>
       <c r="E3970" s="2" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="3971" spans="1:7" x14ac:dyDescent="0.25">
@@ -87916,7 +88258,7 @@
         <v>41</v>
       </c>
       <c r="E3971" s="2" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="3972" spans="1:7" x14ac:dyDescent="0.25">
@@ -87933,7 +88275,7 @@
         <v>41</v>
       </c>
       <c r="E3972" s="2" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="3973" spans="1:7" x14ac:dyDescent="0.25">
@@ -87950,7 +88292,7 @@
         <v>1192</v>
       </c>
       <c r="E3973" s="2" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="F3973" s="1" t="s">
         <v>0</v>
@@ -87973,7 +88315,7 @@
         <v>1192</v>
       </c>
       <c r="E3974" s="2" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="3975" spans="1:7" x14ac:dyDescent="0.25">
@@ -87990,7 +88332,7 @@
         <v>1192</v>
       </c>
       <c r="E3975" s="2" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="3976" spans="1:7" x14ac:dyDescent="0.25">
@@ -88007,7 +88349,7 @@
         <v>1192</v>
       </c>
       <c r="E3976" s="2" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="3977" spans="1:7" x14ac:dyDescent="0.25">
@@ -88024,7 +88366,7 @@
         <v>1192</v>
       </c>
       <c r="E3977" s="2" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="3978" spans="1:7" x14ac:dyDescent="0.25">
@@ -88041,7 +88383,7 @@
         <v>1192</v>
       </c>
       <c r="E3978" s="2" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="3979" spans="1:7" x14ac:dyDescent="0.25">
@@ -88058,7 +88400,7 @@
         <v>1192</v>
       </c>
       <c r="E3979" s="2" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="3980" spans="1:7" x14ac:dyDescent="0.25">
@@ -88075,7 +88417,7 @@
         <v>1192</v>
       </c>
       <c r="E3980" s="2" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="3981" spans="1:7" x14ac:dyDescent="0.25">
@@ -88092,7 +88434,7 @@
         <v>1192</v>
       </c>
       <c r="E3981" s="2" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="3982" spans="1:7" x14ac:dyDescent="0.25">
@@ -88109,7 +88451,7 @@
         <v>1192</v>
       </c>
       <c r="E3982" s="2" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="3983" spans="1:7" x14ac:dyDescent="0.25">
@@ -88126,7 +88468,7 @@
         <v>1192</v>
       </c>
       <c r="E3983" s="2" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="3984" spans="1:7" x14ac:dyDescent="0.25">
@@ -88143,7 +88485,13 @@
         <v>26</v>
       </c>
       <c r="E3984" s="2" t="s">
-        <v>3125</v>
+        <v>3124</v>
+      </c>
+      <c r="F3984" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3984" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="3985" spans="1:5" x14ac:dyDescent="0.25">
@@ -88160,7 +88508,7 @@
         <v>26</v>
       </c>
       <c r="E3985" s="2" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="3986" spans="1:5" x14ac:dyDescent="0.25">
@@ -88177,7 +88525,7 @@
         <v>26</v>
       </c>
       <c r="E3986" s="2" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="3987" spans="1:5" x14ac:dyDescent="0.25">
@@ -88194,7 +88542,7 @@
         <v>26</v>
       </c>
       <c r="E3987" s="2" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="3988" spans="1:5" x14ac:dyDescent="0.25">
@@ -88211,7 +88559,7 @@
         <v>26</v>
       </c>
       <c r="E3988" s="2" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="3989" spans="1:5" x14ac:dyDescent="0.25">
@@ -88228,7 +88576,7 @@
         <v>26</v>
       </c>
       <c r="E3989" s="2" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="3990" spans="1:5" x14ac:dyDescent="0.25">
@@ -88245,7 +88593,7 @@
         <v>24</v>
       </c>
       <c r="E3990" s="2" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="3991" spans="1:5" x14ac:dyDescent="0.25">
@@ -88262,7 +88610,7 @@
         <v>24</v>
       </c>
       <c r="E3991" s="2" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="3992" spans="1:5" x14ac:dyDescent="0.25">
@@ -88279,7 +88627,7 @@
         <v>24</v>
       </c>
       <c r="E3992" s="2" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="3993" spans="1:5" x14ac:dyDescent="0.25">
@@ -88296,7 +88644,7 @@
         <v>24</v>
       </c>
       <c r="E3993" s="2" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="3994" spans="1:5" x14ac:dyDescent="0.25">
@@ -88313,7 +88661,7 @@
         <v>24</v>
       </c>
       <c r="E3994" s="2" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="3995" spans="1:5" x14ac:dyDescent="0.25">
@@ -88330,7 +88678,7 @@
         <v>24</v>
       </c>
       <c r="E3995" s="2" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="3996" spans="1:5" x14ac:dyDescent="0.25">
@@ -88347,7 +88695,7 @@
         <v>24</v>
       </c>
       <c r="E3996" s="2" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="3997" spans="1:5" x14ac:dyDescent="0.25">
@@ -88364,7 +88712,7 @@
         <v>24</v>
       </c>
       <c r="E3997" s="2" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="3998" spans="1:5" x14ac:dyDescent="0.25">
@@ -88381,7 +88729,7 @@
         <v>24</v>
       </c>
       <c r="E3998" s="2" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="3999" spans="1:5" x14ac:dyDescent="0.25">
@@ -88398,7 +88746,7 @@
         <v>24</v>
       </c>
       <c r="E3999" s="2" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="4000" spans="1:5" x14ac:dyDescent="0.25">
@@ -88415,7 +88763,7 @@
         <v>24</v>
       </c>
       <c r="E4000" s="2" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="4001" spans="1:8" x14ac:dyDescent="0.25">
@@ -88432,7 +88780,7 @@
         <v>24</v>
       </c>
       <c r="E4001" s="2" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="4002" spans="1:8" x14ac:dyDescent="0.25">
@@ -88449,7 +88797,7 @@
         <v>24</v>
       </c>
       <c r="E4002" s="2" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="4003" spans="1:8" x14ac:dyDescent="0.25">
@@ -88466,7 +88814,7 @@
         <v>24</v>
       </c>
       <c r="E4003" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="4004" spans="1:8" x14ac:dyDescent="0.25">
@@ -88483,7 +88831,7 @@
         <v>24</v>
       </c>
       <c r="E4004" s="2" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="4005" spans="1:8" x14ac:dyDescent="0.25">
@@ -88523,7 +88871,7 @@
         <v>15</v>
       </c>
       <c r="E4006" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="F4006" s="1" t="s">
         <v>0</v>
@@ -88546,7 +88894,7 @@
         <v>15</v>
       </c>
       <c r="E4007" s="2" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="F4007" s="1" t="s">
         <v>0</v>
@@ -88569,7 +88917,7 @@
         <v>15</v>
       </c>
       <c r="E4008" s="2" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="4009" spans="1:8" x14ac:dyDescent="0.25">
@@ -88586,7 +88934,7 @@
         <v>15</v>
       </c>
       <c r="E4009" s="2" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="4010" spans="1:8" x14ac:dyDescent="0.25">
@@ -88603,7 +88951,7 @@
         <v>15</v>
       </c>
       <c r="E4010" s="2" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="4011" spans="1:8" x14ac:dyDescent="0.25">
@@ -88611,7 +88959,7 @@
         <v>46179</v>
       </c>
       <c r="B4011" s="3" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="C4011" s="1" t="s">
         <v>131</v>
@@ -88620,7 +88968,7 @@
         <v>4</v>
       </c>
       <c r="E4011" s="2" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="4012" spans="1:8" x14ac:dyDescent="0.25">
@@ -88628,7 +88976,7 @@
         <v>46179</v>
       </c>
       <c r="B4012" s="3" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="C4012" s="1" t="s">
         <v>131</v>
@@ -88637,7 +88985,7 @@
         <v>4</v>
       </c>
       <c r="E4012" s="2" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="4013" spans="1:8" x14ac:dyDescent="0.25">
@@ -88677,7 +89025,7 @@
         <v>24</v>
       </c>
       <c r="E4014" s="2" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="F4014" s="1" t="s">
         <v>0</v>
@@ -88686,7 +89034,7 @@
         <v>46179</v>
       </c>
       <c r="H4014" s="1" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="4015" spans="1:8" x14ac:dyDescent="0.25">
@@ -88726,13 +89074,13 @@
         <v>4</v>
       </c>
       <c r="E4016" s="2" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="F4016" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4016" s="7">
-        <v>46179</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="4017" spans="1:7" x14ac:dyDescent="0.25">
@@ -88749,7 +89097,7 @@
         <v>4</v>
       </c>
       <c r="E4017" s="2" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="4018" spans="1:7" x14ac:dyDescent="0.25">
@@ -88766,7 +89114,7 @@
         <v>4</v>
       </c>
       <c r="E4018" s="2" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="4019" spans="1:7" x14ac:dyDescent="0.25">
@@ -88783,7 +89131,7 @@
         <v>4</v>
       </c>
       <c r="E4019" s="2" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="4020" spans="1:7" x14ac:dyDescent="0.25">
@@ -88800,7 +89148,7 @@
         <v>4</v>
       </c>
       <c r="E4020" s="2" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="F4020" s="1" t="s">
         <v>0</v>
@@ -88823,7 +89171,7 @@
         <v>15</v>
       </c>
       <c r="E4021" s="2" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="4022" spans="1:7" x14ac:dyDescent="0.25">
@@ -88840,7 +89188,7 @@
         <v>15</v>
       </c>
       <c r="E4022" s="2" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="4023" spans="1:7" x14ac:dyDescent="0.25">
@@ -88857,7 +89205,7 @@
         <v>4</v>
       </c>
       <c r="E4023" s="2" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="F4023" s="1" t="s">
         <v>0</v>
@@ -88880,7 +89228,7 @@
         <v>4</v>
       </c>
       <c r="E4024" s="2" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="F4024" s="1" t="s">
         <v>0</v>
@@ -89107,7 +89455,7 @@
         <v>24</v>
       </c>
       <c r="E4037" s="2" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="F4037" s="1" t="s">
         <v>0</v>
@@ -89116,7 +89464,7 @@
         <v>46181</v>
       </c>
       <c r="H4037" s="1" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="4038" spans="1:8" x14ac:dyDescent="0.25">
@@ -89133,7 +89481,7 @@
         <v>15</v>
       </c>
       <c r="E4038" s="2" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="F4038" s="2" t="s">
         <v>0</v>
@@ -89142,7 +89490,7 @@
         <v>46181</v>
       </c>
       <c r="H4038" s="1" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="4039" spans="1:8" x14ac:dyDescent="0.25">
@@ -89159,7 +89507,7 @@
         <v>82</v>
       </c>
       <c r="E4039" s="2" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="4040" spans="1:8" x14ac:dyDescent="0.25">
@@ -89176,7 +89524,7 @@
         <v>82</v>
       </c>
       <c r="E4040" s="2" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="4041" spans="1:8" x14ac:dyDescent="0.25">
@@ -89193,7 +89541,7 @@
         <v>82</v>
       </c>
       <c r="E4041" s="2" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="4042" spans="1:8" x14ac:dyDescent="0.25">
@@ -89210,7 +89558,7 @@
         <v>82</v>
       </c>
       <c r="E4042" s="2" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="4043" spans="1:8" x14ac:dyDescent="0.25">
@@ -89218,7 +89566,7 @@
         <v>46181</v>
       </c>
       <c r="B4043" s="3" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="C4043" s="1" t="s">
         <v>12</v>
@@ -89227,7 +89575,7 @@
         <v>15</v>
       </c>
       <c r="E4043" s="2" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="F4043" s="1" t="s">
         <v>0</v>
@@ -89241,7 +89589,7 @@
         <v>46181</v>
       </c>
       <c r="B4044" s="3" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="C4044" s="1" t="s">
         <v>12</v>
@@ -89250,7 +89598,7 @@
         <v>15</v>
       </c>
       <c r="E4044" s="2" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="F4044" s="1" t="s">
         <v>0</v>
@@ -89264,7 +89612,7 @@
         <v>46181</v>
       </c>
       <c r="B4045" s="3" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="C4045" s="1" t="s">
         <v>21</v>
@@ -89287,7 +89635,7 @@
         <v>46181</v>
       </c>
       <c r="B4046" s="3" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="C4046" s="1" t="s">
         <v>21</v>
@@ -89310,7 +89658,7 @@
         <v>46181</v>
       </c>
       <c r="B4047" s="3" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="C4047" s="1" t="s">
         <v>21</v>
@@ -89336,7 +89684,7 @@
         <v>49</v>
       </c>
       <c r="E4048" s="2" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="4049" spans="1:7" x14ac:dyDescent="0.25">
@@ -89353,7 +89701,7 @@
         <v>49</v>
       </c>
       <c r="E4049" s="2" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="4050" spans="1:7" x14ac:dyDescent="0.25">
@@ -89370,7 +89718,7 @@
         <v>49</v>
       </c>
       <c r="E4050" s="2" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="4051" spans="1:7" x14ac:dyDescent="0.25">
@@ -89387,7 +89735,7 @@
         <v>49</v>
       </c>
       <c r="E4051" s="2" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="F4051" s="1" t="s">
         <v>0</v>
@@ -89410,7 +89758,7 @@
         <v>49</v>
       </c>
       <c r="E4052" s="2" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="F4052" s="1" t="s">
         <v>0</v>
@@ -89594,7 +89942,7 @@
         <v>46181</v>
       </c>
       <c r="B4063" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C4063" s="1" t="s">
         <v>118</v>
@@ -89617,7 +89965,7 @@
         <v>46181</v>
       </c>
       <c r="B4064" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C4064" s="1" t="s">
         <v>118</v>
@@ -89640,7 +89988,7 @@
         <v>46181</v>
       </c>
       <c r="B4065" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C4065" s="1" t="s">
         <v>118</v>
@@ -89658,7 +90006,7 @@
         <v>46181</v>
       </c>
       <c r="B4066" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C4066" s="1" t="s">
         <v>118</v>
@@ -89676,7 +90024,7 @@
         <v>46181</v>
       </c>
       <c r="B4067" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C4067" s="1" t="s">
         <v>118</v>
@@ -89694,7 +90042,7 @@
         <v>46181</v>
       </c>
       <c r="B4068" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C4068" s="1" t="s">
         <v>118</v>
@@ -89712,7 +90060,7 @@
         <v>46181</v>
       </c>
       <c r="B4069" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4069" s="1" t="s">
         <v>188</v>
@@ -89721,7 +90069,7 @@
         <v>26</v>
       </c>
       <c r="E4069" s="2" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="4070" spans="1:7" x14ac:dyDescent="0.25">
@@ -89729,7 +90077,7 @@
         <v>46181</v>
       </c>
       <c r="B4070" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C4070" s="1" t="s">
         <v>188</v>
@@ -89738,7 +90086,7 @@
         <v>26</v>
       </c>
       <c r="E4070" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="4071" spans="1:7" x14ac:dyDescent="0.25">
@@ -89755,7 +90103,7 @@
         <v>2380</v>
       </c>
       <c r="E4071" s="2" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="F4071" s="1" t="s">
         <v>0</v>
@@ -89778,7 +90126,7 @@
         <v>2380</v>
       </c>
       <c r="E4072" s="2" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="F4072" s="1" t="s">
         <v>0</v>
@@ -89801,7 +90149,7 @@
         <v>10</v>
       </c>
       <c r="E4073" s="2" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="4074" spans="1:7" x14ac:dyDescent="0.25">
@@ -90317,7 +90665,7 @@
         <v>26</v>
       </c>
       <c r="E4103" s="2" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="4104" spans="1:7" x14ac:dyDescent="0.25">
@@ -90334,7 +90682,7 @@
         <v>26</v>
       </c>
       <c r="E4104" s="2" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="4105" spans="1:7" x14ac:dyDescent="0.25">
@@ -90351,7 +90699,7 @@
         <v>26</v>
       </c>
       <c r="E4105" s="2" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="4106" spans="1:7" x14ac:dyDescent="0.25">
@@ -90368,7 +90716,7 @@
         <v>26</v>
       </c>
       <c r="E4106" s="2" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="4107" spans="1:7" x14ac:dyDescent="0.25">
@@ -90385,7 +90733,7 @@
         <v>24</v>
       </c>
       <c r="E4107" s="2" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="4108" spans="1:7" x14ac:dyDescent="0.25">
@@ -90402,7 +90750,7 @@
         <v>24</v>
       </c>
       <c r="E4108" s="2" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="4109" spans="1:7" x14ac:dyDescent="0.25">
@@ -90419,7 +90767,7 @@
         <v>4</v>
       </c>
       <c r="E4109" s="2" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="4110" spans="1:7" x14ac:dyDescent="0.25">
@@ -90436,7 +90784,7 @@
         <v>15</v>
       </c>
       <c r="E4110" s="2" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="F4110" s="1" t="s">
         <v>0</v>
@@ -90459,7 +90807,7 @@
         <v>15</v>
       </c>
       <c r="E4111" s="2" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="F4111" s="1" t="s">
         <v>0</v>
@@ -90482,7 +90830,7 @@
         <v>15</v>
       </c>
       <c r="E4112" s="2" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="F4112" s="1" t="s">
         <v>0</v>
@@ -90505,7 +90853,7 @@
         <v>15</v>
       </c>
       <c r="E4113" s="2" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="F4113" s="1" t="s">
         <v>0</v>
@@ -90528,7 +90876,7 @@
         <v>20</v>
       </c>
       <c r="E4114" s="2" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="F4114" s="1" t="s">
         <v>0</v>
@@ -90551,7 +90899,7 @@
         <v>15</v>
       </c>
       <c r="E4115" s="2" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="F4115" s="1" t="s">
         <v>0</v>
@@ -90560,7 +90908,7 @@
         <v>46183</v>
       </c>
       <c r="H4115" s="1" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="4116" spans="1:8" x14ac:dyDescent="0.25">
@@ -90577,7 +90925,7 @@
         <v>15</v>
       </c>
       <c r="E4116" s="2" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="F4116" s="1" t="s">
         <v>0</v>
@@ -90586,7 +90934,7 @@
         <v>46183</v>
       </c>
       <c r="H4116" s="1" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="4117" spans="1:8" x14ac:dyDescent="0.25">
@@ -90688,7 +91036,13 @@
         <v>20</v>
       </c>
       <c r="E4122" s="2" t="s">
-        <v>3204</v>
+        <v>3203</v>
+      </c>
+      <c r="F4122" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4122" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="4123" spans="1:8" x14ac:dyDescent="0.25">
@@ -90705,7 +91059,13 @@
         <v>20</v>
       </c>
       <c r="E4123" s="2" t="s">
-        <v>3205</v>
+        <v>3204</v>
+      </c>
+      <c r="F4123" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4123" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="4124" spans="1:8" x14ac:dyDescent="0.25">
@@ -90722,7 +91082,7 @@
         <v>20</v>
       </c>
       <c r="E4124" s="2" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="4125" spans="1:8" x14ac:dyDescent="0.25">
@@ -90739,7 +91099,7 @@
         <v>20</v>
       </c>
       <c r="E4125" s="2" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="4126" spans="1:8" x14ac:dyDescent="0.25">
@@ -90917,16 +91277,22 @@
         <v>46183</v>
       </c>
       <c r="B4136" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C4136" s="1" t="s">
         <v>3208</v>
-      </c>
-      <c r="C4136" s="1" t="s">
-        <v>3209</v>
       </c>
       <c r="D4136" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4136" s="2" t="s">
         <v>2482</v>
+      </c>
+      <c r="F4136" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4136" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="4137" spans="1:8" x14ac:dyDescent="0.25">
@@ -90934,16 +91300,16 @@
         <v>46183</v>
       </c>
       <c r="B4137" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C4137" s="1" t="s">
         <v>3208</v>
-      </c>
-      <c r="C4137" s="1" t="s">
-        <v>3209</v>
       </c>
       <c r="D4137" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4137" s="2" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="4138" spans="1:8" x14ac:dyDescent="0.25">
@@ -90951,16 +91317,16 @@
         <v>46183</v>
       </c>
       <c r="B4138" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C4138" s="1" t="s">
         <v>3208</v>
-      </c>
-      <c r="C4138" s="1" t="s">
-        <v>3209</v>
       </c>
       <c r="D4138" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4138" s="2" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="4139" spans="1:8" x14ac:dyDescent="0.25">
@@ -90968,16 +91334,16 @@
         <v>46183</v>
       </c>
       <c r="B4139" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C4139" s="1" t="s">
         <v>3208</v>
-      </c>
-      <c r="C4139" s="1" t="s">
-        <v>3209</v>
       </c>
       <c r="D4139" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4139" s="2" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="4140" spans="1:8" x14ac:dyDescent="0.25">
@@ -90985,10 +91351,10 @@
         <v>46183</v>
       </c>
       <c r="B4140" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C4140" s="1" t="s">
         <v>3208</v>
-      </c>
-      <c r="C4140" s="1" t="s">
-        <v>3209</v>
       </c>
       <c r="D4140" s="1" t="s">
         <v>4</v>
@@ -91002,16 +91368,16 @@
         <v>46183</v>
       </c>
       <c r="B4141" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C4141" s="1" t="s">
         <v>3208</v>
-      </c>
-      <c r="C4141" s="1" t="s">
-        <v>3209</v>
       </c>
       <c r="D4141" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E4141" s="2" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="4142" spans="1:8" x14ac:dyDescent="0.25">
@@ -91019,7 +91385,7 @@
         <v>46183</v>
       </c>
       <c r="B4142" s="3" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="C4142" s="1" t="s">
         <v>25</v>
@@ -91028,7 +91394,7 @@
         <v>82</v>
       </c>
       <c r="E4142" s="2" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="F4142" s="1" t="s">
         <v>0</v>
@@ -91037,7 +91403,7 @@
         <v>46183</v>
       </c>
       <c r="H4142" s="1" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="4143" spans="1:8" x14ac:dyDescent="0.25">
@@ -91045,7 +91411,7 @@
         <v>46183</v>
       </c>
       <c r="B4143" s="3" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="C4143" s="1" t="s">
         <v>25</v>
@@ -91054,7 +91420,7 @@
         <v>82</v>
       </c>
       <c r="E4143" s="2" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="F4143" s="1" t="s">
         <v>0</v>
@@ -91063,7 +91429,7 @@
         <v>46183</v>
       </c>
       <c r="H4143" s="1" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="4144" spans="1:8" x14ac:dyDescent="0.25">
@@ -91089,7 +91455,7 @@
         <v>46183</v>
       </c>
       <c r="H4144" s="1" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="4145" spans="1:8" x14ac:dyDescent="0.25">
@@ -91115,7 +91481,7 @@
         <v>46183</v>
       </c>
       <c r="H4145" s="1" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="4146" spans="1:8" x14ac:dyDescent="0.25">
@@ -91141,7 +91507,7 @@
         <v>46184</v>
       </c>
       <c r="H4146" s="1" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="4147" spans="1:8" x14ac:dyDescent="0.25">
@@ -91158,7 +91524,7 @@
         <v>24</v>
       </c>
       <c r="E4147" s="2" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="F4147" s="1" t="s">
         <v>0</v>
@@ -91181,7 +91547,7 @@
         <v>24</v>
       </c>
       <c r="E4148" s="2" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="F4148" s="1" t="s">
         <v>0</v>
@@ -91204,7 +91570,7 @@
         <v>24</v>
       </c>
       <c r="E4149" s="2" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="F4149" s="1" t="s">
         <v>0</v>
@@ -91218,16 +91584,16 @@
         <v>46184</v>
       </c>
       <c r="B4150" s="3" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="C4150" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4150" s="1" t="s">
+        <v>3225</v>
+      </c>
+      <c r="E4150" s="2" t="s">
         <v>3226</v>
-      </c>
-      <c r="E4150" s="2" t="s">
-        <v>3227</v>
       </c>
       <c r="F4150" s="1" t="s">
         <v>0</v>
@@ -91250,7 +91616,7 @@
         <v>24</v>
       </c>
       <c r="E4151" s="2" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="4152" spans="1:8" x14ac:dyDescent="0.25">
@@ -91267,7 +91633,7 @@
         <v>24</v>
       </c>
       <c r="E4152" s="2" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="4153" spans="1:8" x14ac:dyDescent="0.25">
@@ -91284,7 +91650,7 @@
         <v>24</v>
       </c>
       <c r="E4153" s="2" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="4154" spans="1:8" x14ac:dyDescent="0.25">
@@ -91310,7 +91676,7 @@
         <v>46184</v>
       </c>
       <c r="H4154" s="1" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="4155" spans="1:8" x14ac:dyDescent="0.25">
@@ -91327,7 +91693,7 @@
         <v>4</v>
       </c>
       <c r="E4155" s="2" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="F4155" s="1" t="s">
         <v>0</v>
@@ -91341,7 +91707,7 @@
         <v>46184</v>
       </c>
       <c r="B4156" s="3" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C4156" s="1" t="s">
         <v>17</v>
@@ -91350,7 +91716,7 @@
         <v>111</v>
       </c>
       <c r="E4156" s="2" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="F4156" s="1" t="s">
         <v>0</v>
@@ -91373,7 +91739,7 @@
         <v>4</v>
       </c>
       <c r="E4157" s="2" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="F4157" s="1" t="s">
         <v>0</v>
@@ -91396,7 +91762,7 @@
         <v>58</v>
       </c>
       <c r="E4158" s="2" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="F4158" s="1" t="s">
         <v>0</v>
@@ -91410,7 +91776,7 @@
         <v>46184</v>
       </c>
       <c r="B4159" s="3" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="C4159" s="1" t="s">
         <v>137</v>
@@ -91419,7 +91785,7 @@
         <v>4</v>
       </c>
       <c r="E4159" s="2" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="F4159" s="1" t="s">
         <v>0</v>
@@ -91433,7 +91799,7 @@
         <v>46184</v>
       </c>
       <c r="B4160" s="3" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C4160" s="1" t="s">
         <v>17</v>
@@ -91442,7 +91808,7 @@
         <v>111</v>
       </c>
       <c r="E4160" s="2" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="F4160" s="1" t="s">
         <v>0</v>
@@ -91456,7 +91822,7 @@
         <v>46184</v>
       </c>
       <c r="B4161" s="3" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C4161" s="1" t="s">
         <v>17</v>
@@ -91465,7 +91831,7 @@
         <v>111</v>
       </c>
       <c r="E4161" s="2" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="4162" spans="1:5" x14ac:dyDescent="0.25">
@@ -91473,7 +91839,7 @@
         <v>46184</v>
       </c>
       <c r="B4162" s="3" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C4162" s="1" t="s">
         <v>17</v>
@@ -91482,7 +91848,7 @@
         <v>111</v>
       </c>
       <c r="E4162" s="2" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="4163" spans="1:5" x14ac:dyDescent="0.25">
@@ -91490,7 +91856,7 @@
         <v>46184</v>
       </c>
       <c r="B4163" s="3" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C4163" s="1" t="s">
         <v>17</v>
@@ -91499,7 +91865,7 @@
         <v>111</v>
       </c>
       <c r="E4163" s="2" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="4164" spans="1:5" x14ac:dyDescent="0.25">
@@ -91507,7 +91873,7 @@
         <v>46184</v>
       </c>
       <c r="B4164" s="3" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C4164" s="1" t="s">
         <v>17</v>
@@ -91516,7 +91882,7 @@
         <v>111</v>
       </c>
       <c r="E4164" s="2" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="4165" spans="1:5" x14ac:dyDescent="0.25">
@@ -91533,7 +91899,7 @@
         <v>58</v>
       </c>
       <c r="E4165" s="2" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="4166" spans="1:5" x14ac:dyDescent="0.25">
@@ -91550,7 +91916,7 @@
         <v>58</v>
       </c>
       <c r="E4166" s="2" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="4167" spans="1:5" x14ac:dyDescent="0.25">
@@ -91567,7 +91933,7 @@
         <v>58</v>
       </c>
       <c r="E4167" s="2" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="4168" spans="1:5" x14ac:dyDescent="0.25">
@@ -91584,7 +91950,7 @@
         <v>4</v>
       </c>
       <c r="E4168" s="2" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="4169" spans="1:5" x14ac:dyDescent="0.25">
@@ -91601,7 +91967,7 @@
         <v>4</v>
       </c>
       <c r="E4169" s="2" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="4170" spans="1:5" x14ac:dyDescent="0.25">
@@ -91618,7 +91984,7 @@
         <v>4</v>
       </c>
       <c r="E4170" s="2" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="4171" spans="1:5" x14ac:dyDescent="0.25">
@@ -91635,7 +92001,7 @@
         <v>4</v>
       </c>
       <c r="E4171" s="2" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="4172" spans="1:5" x14ac:dyDescent="0.25">
@@ -91652,7 +92018,7 @@
         <v>4</v>
       </c>
       <c r="E4172" s="2" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="4173" spans="1:5" x14ac:dyDescent="0.25">
@@ -91669,7 +92035,7 @@
         <v>4</v>
       </c>
       <c r="E4173" s="2" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="4174" spans="1:5" x14ac:dyDescent="0.25">
@@ -91686,7 +92052,7 @@
         <v>4</v>
       </c>
       <c r="E4174" s="2" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="4175" spans="1:5" x14ac:dyDescent="0.25">
@@ -91703,7 +92069,7 @@
         <v>4</v>
       </c>
       <c r="E4175" s="2" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="4176" spans="1:5" x14ac:dyDescent="0.25">
@@ -91720,7 +92086,7 @@
         <v>4</v>
       </c>
       <c r="E4176" s="2" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="4177" spans="1:5" x14ac:dyDescent="0.25">
@@ -91728,7 +92094,7 @@
         <v>46184</v>
       </c>
       <c r="B4177" s="3" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C4177" s="1" t="s">
         <v>17</v>
@@ -91737,7 +92103,7 @@
         <v>111</v>
       </c>
       <c r="E4177" s="2" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="4178" spans="1:5" x14ac:dyDescent="0.25">
@@ -91745,7 +92111,7 @@
         <v>46184</v>
       </c>
       <c r="B4178" s="3" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C4178" s="1" t="s">
         <v>17</v>
@@ -91754,7 +92120,7 @@
         <v>111</v>
       </c>
       <c r="E4178" s="2" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="4179" spans="1:5" x14ac:dyDescent="0.25">
@@ -91762,7 +92128,7 @@
         <v>46184</v>
       </c>
       <c r="B4179" s="3" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C4179" s="1" t="s">
         <v>17</v>
@@ -91771,7 +92137,7 @@
         <v>111</v>
       </c>
       <c r="E4179" s="2" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="4180" spans="1:5" x14ac:dyDescent="0.25">
@@ -91779,7 +92145,7 @@
         <v>46184</v>
       </c>
       <c r="B4180" s="3" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C4180" s="1" t="s">
         <v>17</v>
@@ -91788,7 +92154,7 @@
         <v>111</v>
       </c>
       <c r="E4180" s="2" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="4181" spans="1:5" x14ac:dyDescent="0.25">
@@ -91805,7 +92171,7 @@
         <v>120</v>
       </c>
       <c r="E4181" s="2" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="4182" spans="1:5" x14ac:dyDescent="0.25">
@@ -91822,7 +92188,7 @@
         <v>120</v>
       </c>
       <c r="E4182" s="2" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="4183" spans="1:5" x14ac:dyDescent="0.25">
@@ -91839,7 +92205,7 @@
         <v>120</v>
       </c>
       <c r="E4183" s="2" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="4184" spans="1:5" x14ac:dyDescent="0.25">
@@ -91856,7 +92222,7 @@
         <v>120</v>
       </c>
       <c r="E4184" s="2" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="4185" spans="1:5" x14ac:dyDescent="0.25">
@@ -91873,7 +92239,7 @@
         <v>120</v>
       </c>
       <c r="E4185" s="2" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="4186" spans="1:5" x14ac:dyDescent="0.25">
@@ -91975,7 +92341,7 @@
         <v>4</v>
       </c>
       <c r="E4191" s="2" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="4192" spans="1:5" x14ac:dyDescent="0.25">
@@ -91992,7 +92358,7 @@
         <v>4</v>
       </c>
       <c r="E4192" s="2" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="4193" spans="1:8" x14ac:dyDescent="0.25">
@@ -92009,7 +92375,7 @@
         <v>4</v>
       </c>
       <c r="E4193" s="2" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="4194" spans="1:8" x14ac:dyDescent="0.25">
@@ -92026,7 +92392,7 @@
         <v>4</v>
       </c>
       <c r="E4194" s="2" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="4195" spans="1:8" x14ac:dyDescent="0.25">
@@ -92043,7 +92409,7 @@
         <v>4</v>
       </c>
       <c r="E4195" s="2" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="4196" spans="1:8" x14ac:dyDescent="0.25">
@@ -92060,7 +92426,7 @@
         <v>4</v>
       </c>
       <c r="E4196" s="2" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="4197" spans="1:8" x14ac:dyDescent="0.25">
@@ -92077,7 +92443,7 @@
         <v>4</v>
       </c>
       <c r="E4197" s="2" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="4198" spans="1:8" x14ac:dyDescent="0.25">
@@ -92094,7 +92460,7 @@
         <v>4</v>
       </c>
       <c r="E4198" s="2" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="4199" spans="1:8" x14ac:dyDescent="0.25">
@@ -92111,7 +92477,7 @@
         <v>4</v>
       </c>
       <c r="E4199" s="2" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="4200" spans="1:8" x14ac:dyDescent="0.25">
@@ -92128,7 +92494,7 @@
         <v>15</v>
       </c>
       <c r="E4200" s="2" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="F4200" s="1" t="s">
         <v>0</v>
@@ -92137,7 +92503,7 @@
         <v>46184</v>
       </c>
       <c r="H4200" s="1" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="4201" spans="1:8" x14ac:dyDescent="0.25">
@@ -92154,7 +92520,7 @@
         <v>15</v>
       </c>
       <c r="E4201" s="2" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="F4201" s="1" t="s">
         <v>0</v>
@@ -92163,7 +92529,7 @@
         <v>46184</v>
       </c>
       <c r="H4201" s="1" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="4202" spans="1:8" x14ac:dyDescent="0.25">
@@ -92180,7 +92546,7 @@
         <v>15</v>
       </c>
       <c r="E4202" s="2" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="F4202" s="1" t="s">
         <v>0</v>
@@ -92189,7 +92555,7 @@
         <v>46184</v>
       </c>
       <c r="H4202" s="1" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="4203" spans="1:8" x14ac:dyDescent="0.25">
@@ -92206,7 +92572,7 @@
         <v>2903</v>
       </c>
       <c r="E4203" s="2" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="4204" spans="1:8" x14ac:dyDescent="0.25">
@@ -92223,7 +92589,7 @@
         <v>2903</v>
       </c>
       <c r="E4204" s="2" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="4205" spans="1:8" x14ac:dyDescent="0.25">
@@ -92240,7 +92606,7 @@
         <v>10</v>
       </c>
       <c r="E4205" s="2" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="4206" spans="1:8" x14ac:dyDescent="0.25">
@@ -92257,7 +92623,7 @@
         <v>10</v>
       </c>
       <c r="E4206" s="2" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="4207" spans="1:8" x14ac:dyDescent="0.25">
@@ -92274,7 +92640,7 @@
         <v>10</v>
       </c>
       <c r="E4207" s="2" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="4208" spans="1:8" x14ac:dyDescent="0.25">
@@ -92294,12 +92660,12 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="4209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4209" s="7">
         <v>46184</v>
       </c>
       <c r="B4209" s="3" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="C4209" s="1" t="s">
         <v>25</v>
@@ -92317,49 +92683,586 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="4210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4210" s="1" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4211" s="1" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4212" s="1" t="s">
         <v>3288</v>
       </c>
     </row>
-    <row r="4211" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4211" s="1" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="4212" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4212" s="1" t="s">
+    <row r="4213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4213" s="1" t="s">
         <v>3289</v>
       </c>
     </row>
-    <row r="4213" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4213" s="1" t="s">
+    <row r="4214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4214" s="1" t="s">
         <v>3290</v>
       </c>
     </row>
-    <row r="4214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4214" s="1" t="s">
+    <row r="4215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4215" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4215" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C4215" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4215" s="2" t="s">
         <v>3291</v>
       </c>
-    </row>
-    <row r="4217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F4215" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4215" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4215" s="1" t="s">
+        <v>3292</v>
+      </c>
+    </row>
+    <row r="4216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4216" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4216" s="3" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C4216" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4216" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4216" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F4216" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4216" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4216" s="1" t="s">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4217" s="1" t="s">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="4230" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4230" s="23"/>
-      <c r="B4230" s="22"/>
-      <c r="C4230" s="23"/>
-      <c r="D4230" s="23"/>
-      <c r="E4230" s="23"/>
-    </row>
-    <row r="4231" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4231" s="21"/>
-      <c r="B4231" s="20"/>
-      <c r="C4231" s="21"/>
-      <c r="D4231" s="21"/>
-      <c r="E4231" s="21"/>
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="4218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4218" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4218" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C4218" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4218" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4218" s="2" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="4219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4219" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4219" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4219" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4219" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4219" s="2" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="4220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4220" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4220" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4220" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4220" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4220" s="2" t="s">
+        <v>3296</v>
+      </c>
+    </row>
+    <row r="4221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4221" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4221" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4221" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4221" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4221" s="2" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="4222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4222" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4222" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4222" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4222" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4222" s="2" t="s">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="4223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4223" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4223" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4223" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4223" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4223" s="2" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="4224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4224" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4224" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4224" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4224" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4224" s="1">
+        <v>823124</v>
+      </c>
+      <c r="F4224" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4224" s="7">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="4225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4225" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4225" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4225" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4225" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4225" s="1">
+        <v>823125</v>
+      </c>
+    </row>
+    <row r="4226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4226" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4226" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4226" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4226" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4226" s="1">
+        <v>823126</v>
+      </c>
+    </row>
+    <row r="4227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4227" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4227" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4227" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4227" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4227" s="1">
+        <v>823127</v>
+      </c>
+    </row>
+    <row r="4228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4228" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4228" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4228" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4228" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4228" s="1">
+        <v>823128</v>
+      </c>
+    </row>
+    <row r="4229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4229" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4229" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4229" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4229" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4229" s="1">
+        <v>823129</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4230" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4230" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4230" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4230" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4230" s="1">
+        <v>823130</v>
+      </c>
+    </row>
+    <row r="4231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4231" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4231" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4231" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4231" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4231" s="1">
+        <v>823131</v>
+      </c>
+    </row>
+    <row r="4232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4232" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4232" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4232" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4232" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4232" s="1">
+        <v>823132</v>
+      </c>
+    </row>
+    <row r="4233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4233" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4233" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4233" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4233" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4233" s="1">
+        <v>823133</v>
+      </c>
+    </row>
+    <row r="4234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4234" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4234" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4234" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4234" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4234" s="2" t="s">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="4235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4235" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4235" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4235" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4235" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4235" s="2" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="4236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4236" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4236" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4236" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4236" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4236" s="2" t="s">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="4237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4237" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4237" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4237" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4237" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4237" s="2" t="s">
+        <v>3303</v>
+      </c>
+    </row>
+    <row r="4238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4238" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4238" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4238" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4238" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4238" s="2" t="s">
+        <v>3304</v>
+      </c>
+      <c r="F4238" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4238" s="7">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="4239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4239" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4239" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C4239" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4239" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4239" s="1">
+        <v>105395</v>
+      </c>
+      <c r="F4239" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4239" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4239" s="1" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="4240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4240" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4240" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C4240" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4240" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4240" s="2" t="s">
+        <v>3306</v>
+      </c>
+      <c r="F4240" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4240" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4240" s="1" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="4241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4241" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4241" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C4241" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4241" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4241" s="2" t="s">
+        <v>3308</v>
+      </c>
+      <c r="F4241" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4241" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4241" s="1" t="s">
+        <v>3309</v>
+      </c>
+    </row>
+    <row r="4242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4242" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4242" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C4242" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4242" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4242" s="2" t="s">
+        <v>3310</v>
+      </c>
+      <c r="F4242" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4242" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4242" s="1" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="4243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4243" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4243" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C4243" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4243" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4243" s="2" t="s">
+        <v>3312</v>
+      </c>
+      <c r="F4243" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4243" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4243" s="1" t="s">
+        <v>3313</v>
+      </c>
     </row>
     <row r="1045524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1045524" s="7"/>
@@ -92381,7 +93284,6 @@
       <c r="G1048557" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4214" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H172">
     <sortCondition ref="B3:B172"/>
   </sortState>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F51579F-B361-470F-B4B4-11485A8C769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32089604-9B18-478D-BE04-84F7A2D4BE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="CHEQUES SHEET 2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHEQUES SHEET 2026'!$A$1:$H$4320</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17236" uniqueCount="3317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17588" uniqueCount="3372">
   <si>
     <t>USE</t>
   </si>
@@ -9883,21 +9883,6 @@
     <t>AKASH MEDICOS</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">              </t>
-  </si>
-  <si>
     <t>000275</t>
   </si>
   <si>
@@ -9965,6 +9950,186 @@
   </si>
   <si>
     <t>2822/-</t>
+  </si>
+  <si>
+    <t>KANSAL PHARMACEUTICALS</t>
+  </si>
+  <si>
+    <t>774011</t>
+  </si>
+  <si>
+    <t>774010</t>
+  </si>
+  <si>
+    <t>064144</t>
+  </si>
+  <si>
+    <t>064145</t>
+  </si>
+  <si>
+    <t>064146</t>
+  </si>
+  <si>
+    <t>115913/-</t>
+  </si>
+  <si>
+    <t>74572/-</t>
+  </si>
+  <si>
+    <t>181150/-</t>
+  </si>
+  <si>
+    <t>006225</t>
+  </si>
+  <si>
+    <t>006224</t>
+  </si>
+  <si>
+    <t>006223</t>
+  </si>
+  <si>
+    <t>002731</t>
+  </si>
+  <si>
+    <t>002732</t>
+  </si>
+  <si>
+    <t>002733</t>
+  </si>
+  <si>
+    <t>002734</t>
+  </si>
+  <si>
+    <t>002735</t>
+  </si>
+  <si>
+    <t>001655</t>
+  </si>
+  <si>
+    <t>017188</t>
+  </si>
+  <si>
+    <t>017189</t>
+  </si>
+  <si>
+    <t>017190</t>
+  </si>
+  <si>
+    <t>017191</t>
+  </si>
+  <si>
+    <t>017192</t>
+  </si>
+  <si>
+    <t>001656</t>
+  </si>
+  <si>
+    <t>003695</t>
+  </si>
+  <si>
+    <t>003696</t>
+  </si>
+  <si>
+    <t>003697</t>
+  </si>
+  <si>
+    <t>003698</t>
+  </si>
+  <si>
+    <t>001657</t>
+  </si>
+  <si>
+    <t>001658</t>
+  </si>
+  <si>
+    <t>001659</t>
+  </si>
+  <si>
+    <t>001660</t>
+  </si>
+  <si>
+    <t>001661</t>
+  </si>
+  <si>
+    <t>001662</t>
+  </si>
+  <si>
+    <t>001663</t>
+  </si>
+  <si>
+    <t>001664</t>
+  </si>
+  <si>
+    <t>001665</t>
+  </si>
+  <si>
+    <t>001666</t>
+  </si>
+  <si>
+    <t>001667</t>
+  </si>
+  <si>
+    <t>001668</t>
+  </si>
+  <si>
+    <t>025395</t>
+  </si>
+  <si>
+    <t>025396</t>
+  </si>
+  <si>
+    <t>025397</t>
+  </si>
+  <si>
+    <t>025398</t>
+  </si>
+  <si>
+    <t>025399</t>
+  </si>
+  <si>
+    <t>025400</t>
+  </si>
+  <si>
+    <t>006226</t>
+  </si>
+  <si>
+    <t>006227</t>
+  </si>
+  <si>
+    <t>006228</t>
+  </si>
+  <si>
+    <t>006229</t>
+  </si>
+  <si>
+    <t>006230</t>
+  </si>
+  <si>
+    <t>006231</t>
+  </si>
+  <si>
+    <t>006232</t>
+  </si>
+  <si>
+    <t>006233</t>
+  </si>
+  <si>
+    <t>006234</t>
+  </si>
+  <si>
+    <t>006235</t>
+  </si>
+  <si>
+    <t>006236</t>
+  </si>
+  <si>
+    <t>006237</t>
+  </si>
+  <si>
+    <t>005276</t>
+  </si>
+  <si>
+    <t>005277</t>
   </si>
   <si>
     <t>Party Name</t>
@@ -10468,11 +10633,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1048557"/>
+  <dimension ref="A1:O1048551"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="20.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
@@ -10486,7 +10651,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>3314</v>
+        <v>3369</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>365</v>
@@ -10495,10 +10660,10 @@
         <v>692</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3315</v>
+        <v>3370</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3316</v>
+        <v>3371</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>391</v>
@@ -17507,6 +17672,12 @@
       <c r="E370" s="2" t="s">
         <v>768</v>
       </c>
+      <c r="F370" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G370" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="371" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="7">
@@ -17862,6 +18033,7 @@
       <c r="E390" s="2" t="s">
         <v>1101</v>
       </c>
+      <c r="G390" s="7"/>
     </row>
     <row r="391" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="7">
@@ -20719,7 +20891,12 @@
       <c r="E533" s="2" t="s">
         <v>1512</v>
       </c>
-      <c r="G533" s="7"/>
+      <c r="F533" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G533" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="534" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="7">
@@ -20760,6 +20937,12 @@
       <c r="E535" s="2" t="s">
         <v>664</v>
       </c>
+      <c r="F535" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G535" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="536" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="7">
@@ -22440,6 +22623,12 @@
       <c r="E622" s="2" t="s">
         <v>1533</v>
       </c>
+      <c r="F622" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G622" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="623" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="7">
@@ -35363,6 +35552,12 @@
       <c r="E1291" s="2" t="s">
         <v>664</v>
       </c>
+      <c r="F1291" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1291" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="1292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1292" s="7">
@@ -42825,6 +43020,12 @@
       <c r="E1676" s="2" t="s">
         <v>1806</v>
       </c>
+      <c r="F1676" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1676" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1677" s="7">
@@ -43209,12 +43410,7 @@
       <c r="E1696" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F1696" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1696" s="7">
-        <v>46167</v>
-      </c>
+      <c r="G1696" s="7"/>
     </row>
     <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1697" s="7">
@@ -43575,6 +43771,12 @@
       <c r="E1714" s="1">
         <v>814185</v>
       </c>
+      <c r="F1714" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1714" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="1715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1715" s="7">
@@ -43592,6 +43794,12 @@
       <c r="E1715" s="1">
         <v>814187</v>
       </c>
+      <c r="F1715" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1715" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="1716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1716" s="7">
@@ -44215,6 +44423,12 @@
       <c r="E1747" s="1">
         <v>257921</v>
       </c>
+      <c r="F1747" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1747" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="1748" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1748" s="7">
@@ -44629,6 +44843,12 @@
       </c>
       <c r="E1768" s="1">
         <v>110546</v>
+      </c>
+      <c r="F1768" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1768" s="7">
+        <v>46186</v>
       </c>
     </row>
     <row r="1769" spans="1:7" x14ac:dyDescent="0.25">
@@ -46875,6 +47095,12 @@
       <c r="E1885" s="2" t="s">
         <v>1886</v>
       </c>
+      <c r="F1885" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1885" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="1886" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1886" s="7">
@@ -55387,6 +55613,12 @@
       <c r="E2322" s="2" t="s">
         <v>1270</v>
       </c>
+      <c r="F2322" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2322" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2323" s="7">
@@ -56730,7 +56962,12 @@
       <c r="E2387" s="1">
         <v>733741</v>
       </c>
-      <c r="G2387" s="7"/>
+      <c r="F2387" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2387" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2388" s="7">
@@ -58123,7 +58360,12 @@
       <c r="E2461" s="1">
         <v>152107</v>
       </c>
-      <c r="G2461" s="19"/>
+      <c r="F2461" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2461" s="19">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2462" s="7">
@@ -58312,6 +58554,12 @@
       <c r="E2472" s="1">
         <v>178122</v>
       </c>
+      <c r="F2472" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2472" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2473" s="7">
@@ -60801,7 +61049,12 @@
       <c r="E2593" s="1">
         <v>458706</v>
       </c>
-      <c r="G2593" s="7"/>
+      <c r="F2593" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2593" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2594" s="7">
@@ -60842,6 +61095,12 @@
       <c r="E2595" s="1">
         <v>458708</v>
       </c>
+      <c r="F2595" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2595" s="7">
+        <v>46183</v>
+      </c>
     </row>
     <row r="2596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2596" s="7">
@@ -63491,6 +63750,12 @@
       <c r="E2718" s="1">
         <v>458746</v>
       </c>
+      <c r="F2718" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2718" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2719" s="7">
@@ -67049,6 +67314,12 @@
       <c r="E2892" s="2" t="s">
         <v>2359</v>
       </c>
+      <c r="F2892" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2892" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="2893" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2893" s="7">
@@ -70870,38 +71141,10 @@
       </c>
     </row>
     <row r="3076" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3076" s="7">
-        <v>46167</v>
-      </c>
-      <c r="B3076" s="3" t="s">
-        <v>3047</v>
-      </c>
-      <c r="C3076" s="1" t="s">
-        <v>2564</v>
-      </c>
-      <c r="D3076" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3076" s="1">
-        <v>947153</v>
-      </c>
+      <c r="A3076" s="7"/>
     </row>
     <row r="3077" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3077" s="7">
-        <v>46167</v>
-      </c>
-      <c r="B3077" s="3" t="s">
-        <v>3047</v>
-      </c>
-      <c r="C3077" s="1" t="s">
-        <v>2564</v>
-      </c>
-      <c r="D3077" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3077" s="1">
-        <v>947154</v>
-      </c>
+      <c r="A3077" s="7"/>
     </row>
     <row r="3078" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3078" s="7">
@@ -71284,6 +71527,7 @@
       <c r="E3097" s="2" t="s">
         <v>2577</v>
       </c>
+      <c r="G3097" s="7"/>
     </row>
     <row r="3098" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3098" s="7">
@@ -73186,6 +73430,12 @@
       <c r="E3188" s="1">
         <v>868290</v>
       </c>
+      <c r="F3188" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3188" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3189" s="7">
@@ -75112,6 +75362,12 @@
       <c r="E3292" s="2" t="s">
         <v>2680</v>
       </c>
+      <c r="F3292" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3292" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3293" s="7">
@@ -75129,6 +75385,12 @@
       <c r="E3293" s="2" t="s">
         <v>2681</v>
       </c>
+      <c r="F3293" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3293" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3294" s="7">
@@ -76856,6 +77118,12 @@
       <c r="E3376" s="2" t="s">
         <v>2765</v>
       </c>
+      <c r="F3376" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3376" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3377" s="7">
@@ -79289,6 +79557,12 @@
       <c r="E3505" s="2" t="s">
         <v>2850</v>
       </c>
+      <c r="F3505" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3505" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3506" s="7">
@@ -79653,6 +79927,12 @@
       <c r="E3525" s="2" t="s">
         <v>2867</v>
       </c>
+      <c r="F3525" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3525" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3526" s="7">
@@ -81686,6 +81966,12 @@
       <c r="E3627" s="2" t="s">
         <v>2149</v>
       </c>
+      <c r="F3627" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3627" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="3628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3628" s="7">
@@ -88970,6 +89256,12 @@
       <c r="E4011" s="2" t="s">
         <v>3152</v>
       </c>
+      <c r="F4011" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4011" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="4012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4012" s="7">
@@ -92642,6 +92934,12 @@
       <c r="E4207" s="2" t="s">
         <v>3284</v>
       </c>
+      <c r="F4207" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4207" s="7">
+        <v>46186</v>
+      </c>
     </row>
     <row r="4208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4208" s="7">
@@ -92684,28 +92982,106 @@
       </c>
     </row>
     <row r="4210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4210" s="1" t="s">
+      <c r="A4210" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4210" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C4210" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4210" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4210" s="2" t="s">
+        <v>3286</v>
+      </c>
+      <c r="F4210" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4210" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4210" s="1" t="s">
         <v>3287</v>
       </c>
     </row>
     <row r="4211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4211" s="1" t="s">
-        <v>3287</v>
+      <c r="A4211" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4211" s="3" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C4211" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4211" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4211" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F4211" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4211" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4211" s="1" t="s">
+        <v>3288</v>
       </c>
     </row>
     <row r="4212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4212" s="1" t="s">
-        <v>3288</v>
+      <c r="A4212" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4212" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C4212" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4212" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4212" s="2" t="s">
+        <v>3289</v>
       </c>
     </row>
     <row r="4213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4213" s="1" t="s">
-        <v>3289</v>
+      <c r="A4213" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4213" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4213" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4213" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4213" s="2" t="s">
+        <v>3290</v>
       </c>
     </row>
     <row r="4214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4214" s="1" t="s">
-        <v>3290</v>
+      <c r="A4214" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B4214" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4214" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4214" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4214" s="2" t="s">
+        <v>3291</v>
       </c>
     </row>
     <row r="4215" spans="1:8" x14ac:dyDescent="0.25">
@@ -92713,7 +93089,7 @@
         <v>46185</v>
       </c>
       <c r="B4215" s="3" t="s">
-        <v>2109</v>
+        <v>230</v>
       </c>
       <c r="C4215" s="1" t="s">
         <v>25</v>
@@ -92722,15 +93098,6 @@
         <v>4</v>
       </c>
       <c r="E4215" s="2" t="s">
-        <v>3291</v>
-      </c>
-      <c r="F4215" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4215" s="7">
-        <v>46185</v>
-      </c>
-      <c r="H4215" s="1" t="s">
         <v>3292</v>
       </c>
     </row>
@@ -92739,30 +93106,33 @@
         <v>46185</v>
       </c>
       <c r="B4216" s="3" t="s">
-        <v>2785</v>
+        <v>230</v>
       </c>
       <c r="C4216" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4216" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E4216" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="F4216" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4216" s="7">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4217" s="7">
         <v>46185</v>
       </c>
-      <c r="H4216" s="1" t="s">
-        <v>3293</v>
-      </c>
-    </row>
-    <row r="4217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4217" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="C4217" s="1" t="s">
-        <v>3286</v>
+        <v>25</v>
+      </c>
+      <c r="D4217" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4217" s="2" t="s">
+        <v>3294</v>
       </c>
     </row>
     <row r="4218" spans="1:8" x14ac:dyDescent="0.25">
@@ -92770,16 +93140,22 @@
         <v>46185</v>
       </c>
       <c r="B4218" s="3" t="s">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="C4218" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4218" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4218" s="2" t="s">
-        <v>3294</v>
+        <v>26</v>
+      </c>
+      <c r="E4218" s="1">
+        <v>823124</v>
+      </c>
+      <c r="F4218" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4218" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="4219" spans="1:8" x14ac:dyDescent="0.25">
@@ -92787,16 +93163,22 @@
         <v>46185</v>
       </c>
       <c r="B4219" s="3" t="s">
-        <v>230</v>
+        <v>465</v>
       </c>
       <c r="C4219" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4219" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4219" s="2" t="s">
-        <v>3295</v>
+        <v>26</v>
+      </c>
+      <c r="E4219" s="1">
+        <v>823125</v>
+      </c>
+      <c r="F4219" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4219" s="7">
+        <v>46186</v>
       </c>
     </row>
     <row r="4220" spans="1:8" x14ac:dyDescent="0.25">
@@ -92804,16 +93186,16 @@
         <v>46185</v>
       </c>
       <c r="B4220" s="3" t="s">
-        <v>230</v>
+        <v>465</v>
       </c>
       <c r="C4220" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4220" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4220" s="2" t="s">
-        <v>3296</v>
+        <v>26</v>
+      </c>
+      <c r="E4220" s="1">
+        <v>823126</v>
       </c>
     </row>
     <row r="4221" spans="1:8" x14ac:dyDescent="0.25">
@@ -92821,16 +93203,16 @@
         <v>46185</v>
       </c>
       <c r="B4221" s="3" t="s">
-        <v>230</v>
+        <v>465</v>
       </c>
       <c r="C4221" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4221" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4221" s="2" t="s">
-        <v>3297</v>
+        <v>26</v>
+      </c>
+      <c r="E4221" s="1">
+        <v>823127</v>
       </c>
     </row>
     <row r="4222" spans="1:8" x14ac:dyDescent="0.25">
@@ -92838,16 +93220,16 @@
         <v>46185</v>
       </c>
       <c r="B4222" s="3" t="s">
-        <v>230</v>
+        <v>465</v>
       </c>
       <c r="C4222" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4222" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4222" s="2" t="s">
-        <v>3298</v>
+        <v>26</v>
+      </c>
+      <c r="E4222" s="1">
+        <v>823128</v>
       </c>
     </row>
     <row r="4223" spans="1:8" x14ac:dyDescent="0.25">
@@ -92855,16 +93237,16 @@
         <v>46185</v>
       </c>
       <c r="B4223" s="3" t="s">
-        <v>230</v>
+        <v>465</v>
       </c>
       <c r="C4223" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4223" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4223" s="2" t="s">
-        <v>3299</v>
+        <v>26</v>
+      </c>
+      <c r="E4223" s="1">
+        <v>823129</v>
       </c>
     </row>
     <row r="4224" spans="1:8" x14ac:dyDescent="0.25">
@@ -92881,13 +93263,7 @@
         <v>26</v>
       </c>
       <c r="E4224" s="1">
-        <v>823124</v>
-      </c>
-      <c r="F4224" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4224" s="7">
-        <v>46185</v>
+        <v>823130</v>
       </c>
     </row>
     <row r="4225" spans="1:8" x14ac:dyDescent="0.25">
@@ -92904,7 +93280,7 @@
         <v>26</v>
       </c>
       <c r="E4225" s="1">
-        <v>823125</v>
+        <v>823131</v>
       </c>
     </row>
     <row r="4226" spans="1:8" x14ac:dyDescent="0.25">
@@ -92921,7 +93297,7 @@
         <v>26</v>
       </c>
       <c r="E4226" s="1">
-        <v>823126</v>
+        <v>823132</v>
       </c>
     </row>
     <row r="4227" spans="1:8" x14ac:dyDescent="0.25">
@@ -92938,7 +93314,7 @@
         <v>26</v>
       </c>
       <c r="E4227" s="1">
-        <v>823127</v>
+        <v>823133</v>
       </c>
     </row>
     <row r="4228" spans="1:8" x14ac:dyDescent="0.25">
@@ -92946,16 +93322,16 @@
         <v>46185</v>
       </c>
       <c r="B4228" s="3" t="s">
-        <v>465</v>
+        <v>73</v>
       </c>
       <c r="C4228" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4228" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4228" s="1">
-        <v>823128</v>
+        <v>15</v>
+      </c>
+      <c r="E4228" s="2" t="s">
+        <v>3296</v>
       </c>
     </row>
     <row r="4229" spans="1:8" x14ac:dyDescent="0.25">
@@ -92963,16 +93339,16 @@
         <v>46185</v>
       </c>
       <c r="B4229" s="3" t="s">
-        <v>465</v>
+        <v>73</v>
       </c>
       <c r="C4229" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4229" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4229" s="1">
-        <v>823129</v>
+        <v>15</v>
+      </c>
+      <c r="E4229" s="2" t="s">
+        <v>3295</v>
       </c>
     </row>
     <row r="4230" spans="1:8" x14ac:dyDescent="0.25">
@@ -92980,16 +93356,16 @@
         <v>46185</v>
       </c>
       <c r="B4230" s="3" t="s">
-        <v>465</v>
+        <v>275</v>
       </c>
       <c r="C4230" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4230" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4230" s="1">
-        <v>823130</v>
+      <c r="E4230" s="2" t="s">
+        <v>3297</v>
       </c>
     </row>
     <row r="4231" spans="1:8" x14ac:dyDescent="0.25">
@@ -92997,16 +93373,16 @@
         <v>46185</v>
       </c>
       <c r="B4231" s="3" t="s">
-        <v>465</v>
+        <v>275</v>
       </c>
       <c r="C4231" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4231" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4231" s="1">
-        <v>823131</v>
+      <c r="E4231" s="2" t="s">
+        <v>3298</v>
       </c>
     </row>
     <row r="4232" spans="1:8" x14ac:dyDescent="0.25">
@@ -93014,16 +93390,22 @@
         <v>46185</v>
       </c>
       <c r="B4232" s="3" t="s">
-        <v>465</v>
+        <v>1176</v>
       </c>
       <c r="C4232" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D4232" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4232" s="1">
-        <v>823132</v>
+        <v>16</v>
+      </c>
+      <c r="E4232" s="2" t="s">
+        <v>3299</v>
+      </c>
+      <c r="F4232" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4232" s="7">
+        <v>46185</v>
       </c>
     </row>
     <row r="4233" spans="1:8" x14ac:dyDescent="0.25">
@@ -93031,16 +93413,25 @@
         <v>46185</v>
       </c>
       <c r="B4233" s="3" t="s">
-        <v>465</v>
+        <v>1566</v>
       </c>
       <c r="C4233" s="1" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D4233" s="1" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="E4233" s="1">
-        <v>823133</v>
+        <v>105395</v>
+      </c>
+      <c r="F4233" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4233" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4233" s="1" t="s">
+        <v>3300</v>
       </c>
     </row>
     <row r="4234" spans="1:8" x14ac:dyDescent="0.25">
@@ -93048,16 +93439,25 @@
         <v>46185</v>
       </c>
       <c r="B4234" s="3" t="s">
-        <v>73</v>
+        <v>2109</v>
       </c>
       <c r="C4234" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4234" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E4234" s="2" t="s">
         <v>3301</v>
+      </c>
+      <c r="F4234" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4234" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4234" s="1" t="s">
+        <v>3302</v>
       </c>
     </row>
     <row r="4235" spans="1:8" x14ac:dyDescent="0.25">
@@ -93065,16 +93465,25 @@
         <v>46185</v>
       </c>
       <c r="B4235" s="3" t="s">
-        <v>73</v>
+        <v>2699</v>
       </c>
       <c r="C4235" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4235" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E4235" s="2" t="s">
-        <v>3300</v>
+        <v>3303</v>
+      </c>
+      <c r="F4235" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4235" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4235" s="1" t="s">
+        <v>3304</v>
       </c>
     </row>
     <row r="4236" spans="1:8" x14ac:dyDescent="0.25">
@@ -93082,16 +93491,25 @@
         <v>46185</v>
       </c>
       <c r="B4236" s="3" t="s">
-        <v>275</v>
+        <v>2699</v>
       </c>
       <c r="C4236" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4236" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4236" s="2" t="s">
-        <v>3302</v>
+        <v>3305</v>
+      </c>
+      <c r="F4236" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4236" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4236" s="1" t="s">
+        <v>3306</v>
       </c>
     </row>
     <row r="4237" spans="1:8" x14ac:dyDescent="0.25">
@@ -93099,16 +93517,25 @@
         <v>46185</v>
       </c>
       <c r="B4237" s="3" t="s">
-        <v>275</v>
+        <v>2699</v>
       </c>
       <c r="C4237" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4237" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4237" s="2" t="s">
-        <v>3303</v>
+        <v>3307</v>
+      </c>
+      <c r="F4237" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4237" s="7">
+        <v>46185</v>
+      </c>
+      <c r="H4237" s="1" t="s">
+        <v>3308</v>
       </c>
     </row>
     <row r="4238" spans="1:8" x14ac:dyDescent="0.25">
@@ -93116,22 +93543,22 @@
         <v>46185</v>
       </c>
       <c r="B4238" s="3" t="s">
-        <v>1176</v>
+        <v>3309</v>
       </c>
       <c r="C4238" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D4238" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4238" s="2" t="s">
-        <v>3304</v>
+        <v>3311</v>
       </c>
       <c r="F4238" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4238" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="4239" spans="1:8" x14ac:dyDescent="0.25">
@@ -93139,149 +93566,1625 @@
         <v>46185</v>
       </c>
       <c r="B4239" s="3" t="s">
-        <v>1566</v>
+        <v>3309</v>
       </c>
       <c r="C4239" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D4239" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4239" s="1">
-        <v>105395</v>
-      </c>
-      <c r="F4239" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4239" s="7">
-        <v>46185</v>
-      </c>
-      <c r="H4239" s="1" t="s">
-        <v>3305</v>
+        <v>15</v>
+      </c>
+      <c r="E4239" s="2" t="s">
+        <v>3310</v>
       </c>
     </row>
     <row r="4240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4240" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B4240" s="3" t="s">
-        <v>2109</v>
+        <v>2212</v>
       </c>
       <c r="C4240" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4240" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E4240" s="2" t="s">
-        <v>3306</v>
+        <v>3312</v>
       </c>
       <c r="F4240" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4240" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="H4240" s="1" t="s">
-        <v>3307</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="4241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4241" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B4241" s="3" t="s">
-        <v>2699</v>
+        <v>2212</v>
       </c>
       <c r="C4241" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4241" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E4241" s="2" t="s">
-        <v>3308</v>
+        <v>3313</v>
       </c>
       <c r="F4241" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4241" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="H4241" s="1" t="s">
-        <v>3309</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="4242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4242" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B4242" s="3" t="s">
-        <v>2699</v>
+        <v>2212</v>
       </c>
       <c r="C4242" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4242" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E4242" s="2" t="s">
-        <v>3310</v>
+        <v>3314</v>
       </c>
       <c r="F4242" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4242" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="H4242" s="1" t="s">
-        <v>3311</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="4243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4243" s="7">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B4243" s="3" t="s">
-        <v>2699</v>
+        <v>2405</v>
       </c>
       <c r="C4243" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4243" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4243" s="2">
+        <v>781548</v>
+      </c>
+      <c r="F4243" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4243" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4244" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4244" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4244" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4244" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4244" s="2" t="s">
+        <v>3318</v>
+      </c>
+      <c r="F4244" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4244" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4245" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4245" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4245" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4245" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4245" s="2" t="s">
+        <v>3319</v>
+      </c>
+      <c r="F4245" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4245" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4246" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4246" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4246" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4246" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4246" s="2" t="s">
+        <v>3320</v>
+      </c>
+      <c r="F4246" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4246" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4247" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4247" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4247" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4247" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4247" s="2" t="s">
+        <v>3321</v>
+      </c>
+      <c r="F4247" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4247" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4248" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4248" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4248" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4248" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4248" s="2" t="s">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="4249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4249" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4249" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4249" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4249" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4249" s="2" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4250" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4250" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4250" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4250" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4250" s="2" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="4251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4251" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4251" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4251" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4251" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4251" s="2" t="s">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4252" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4252" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4252" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4252" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4252" s="2" t="s">
+        <v>3326</v>
+      </c>
+      <c r="F4252" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4252" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4253" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4253" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C4253" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4253" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4253" s="1">
+        <v>662363</v>
+      </c>
+      <c r="F4253" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4253" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4254" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4254" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4254" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4254" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4254" s="1">
+        <v>258407</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4255" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4255" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4255" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4255" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4255" s="1">
+        <v>258408</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4256" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4256" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4256" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4256" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4256" s="1">
+        <v>258406</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4257" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4257" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4257" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4257" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4257" s="2" t="s">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4258" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4258" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4258" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4258" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4258" s="2" t="s">
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4259" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4259" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4259" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4259" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4259" s="2" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4260" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4260" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4260" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4260" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4260" s="2" t="s">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4261" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4261" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4261" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4261" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4261" s="2" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="4262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4262" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4262" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4262" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4262" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4262" s="1">
+        <v>217926</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4263" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4263" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4263" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4263" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4263" s="1">
+        <v>217927</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4264" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4264" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4264" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4264" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4264" s="1">
+        <v>217928</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4265" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4265" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4265" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4265" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4265" s="1">
+        <v>217929</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4266" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4266" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4266" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4266" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4266" s="1">
+        <v>217930</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4267" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4267" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4267" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4267" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4267" s="1">
+        <v>217931</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4268" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4268" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C4268" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4268" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4268" s="1">
+        <v>217932</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4269" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4269" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C4269" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4269" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4269" s="1">
+        <v>671604</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4270" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4270" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C4270" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4270" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4270" s="1">
+        <v>671605</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4271" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4271" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C4271" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4271" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4271" s="1">
+        <v>671606</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4272" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4272" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C4272" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4272" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4272" s="1">
+        <v>671607</v>
+      </c>
+    </row>
+    <row r="4273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4273" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4273" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C4273" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4273" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4273" s="1">
+        <v>662364</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4274" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4274" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C4274" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4274" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4274" s="1">
+        <v>662365</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4275" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4275" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C4275" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4275" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4275" s="1">
+        <v>662366</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4276" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4276" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4276" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4276" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4276" s="1">
+        <v>997777</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4277" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4277" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4277" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4277" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4277" s="2" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F4277" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4277" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4278" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4278" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4278" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4278" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4278" s="1">
+        <v>997776</v>
+      </c>
+    </row>
+    <row r="4279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4279" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4279" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4279" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4279" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4279" s="1">
+        <v>997775</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4280" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4280" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4280" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4280" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4280" s="1">
+        <v>997774</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4281" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4281" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4281" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4281" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4281" s="1">
+        <v>997773</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4282" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4282" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4282" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4282" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4282" s="2" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4283" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4283" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4283" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4283" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4283" s="2" t="s">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4284" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4284" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4284" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4284" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4284" s="2" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4285" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4285" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4285" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4285" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4285" s="2" t="s">
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4286" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4286" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4286" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4286" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4286" s="2" t="s">
+        <v>3337</v>
+      </c>
+      <c r="F4286" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4286" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4287" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4287" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4287" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4287" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4287" s="2" t="s">
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4288" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4288" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4288" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4288" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4288" s="2" t="s">
+        <v>3339</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4289" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4289" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4289" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4289" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4289" s="2" t="s">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4290" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4290" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4290" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4290" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4290" s="2" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4291" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4291" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4291" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4291" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4291" s="2" t="s">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4292" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4292" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4292" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4292" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4292" s="2" t="s">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4293" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4293" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4293" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4293" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4293" s="2" t="s">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4294" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4294" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4294" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4294" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4294" s="2" t="s">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4295" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4295" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4295" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4295" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4295" s="2" t="s">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4296" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4296" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4296" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4296" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4296" s="2" t="s">
+        <v>3347</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4297" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4297" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C4297" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4297" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4297" s="2" t="s">
+        <v>3348</v>
+      </c>
+    </row>
+    <row r="4298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4298" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4298" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4298" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4298" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4298" s="2">
+        <v>114826</v>
+      </c>
+      <c r="F4298" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4298" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4299" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4299" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4299" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4299" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4299" s="2" t="s">
+        <v>3349</v>
+      </c>
+      <c r="F4299" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4299" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4300" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4300" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4300" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4300" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4300" s="2" t="s">
+        <v>3350</v>
+      </c>
+      <c r="F4300" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4300" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4301" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4301" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4301" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4301" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4301" s="2" t="s">
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4302" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4302" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4302" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4302" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4302" s="2" t="s">
+        <v>3352</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4303" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4303" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4303" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4303" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4303" s="2" t="s">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4304" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4304" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4304" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4304" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4304" s="2" t="s">
+        <v>3354</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4305" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4305" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4305" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4305" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4305" s="2">
+        <v>114827</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4306" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4306" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4306" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4306" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4306" s="2">
+        <v>114828</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4307" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4307" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4307" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4307" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4307" s="2">
+        <v>114829</v>
+      </c>
+    </row>
+    <row r="4308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4308" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4308" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4308" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4308" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4308" s="2">
+        <v>114830</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4309" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4309" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4309" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4309" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4309" s="2" t="s">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4310" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4310" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4310" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4310" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4310" s="2" t="s">
+        <v>3356</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4311" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4311" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4311" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4311" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4311" s="2" t="s">
+        <v>3357</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4312" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4312" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4312" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4312" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4312" s="2" t="s">
+        <v>3358</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4313" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4313" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4313" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4313" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4313" s="2" t="s">
+        <v>3359</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4314" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4314" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4314" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4314" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4314" s="2" t="s">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4315" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4315" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4315" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4315" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4315" s="2" t="s">
+        <v>3361</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4316" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4316" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4316" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4316" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4316" s="2" t="s">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4317" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4317" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4317" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4317" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4317" s="2" t="s">
+        <v>3363</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4318" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4318" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4318" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4318" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4318" s="2" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4319" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4319" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4319" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4319" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4319" s="2" t="s">
+        <v>3365</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4320" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4320" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4320" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4320" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4320" s="2" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4321" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4321" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C4321" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4243" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4243" s="2" t="s">
-        <v>3312</v>
-      </c>
-      <c r="F4243" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4243" s="7">
-        <v>46185</v>
-      </c>
-      <c r="H4243" s="1" t="s">
-        <v>3313</v>
-      </c>
-    </row>
-    <row r="1045524" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1045524" s="7"/>
-    </row>
-    <row r="1045534" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1045534" s="7"/>
-    </row>
-    <row r="1048537" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1048537" s="7"/>
-    </row>
-    <row r="1048553" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1048553" s="7"/>
-    </row>
-    <row r="1048554" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1048554" s="7"/>
-      <c r="G1048554" s="7"/>
-    </row>
-    <row r="1048557" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1048557" s="7"/>
+      <c r="D4321" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4321" s="2">
+        <v>742020</v>
+      </c>
+      <c r="F4321" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4321" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4322" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4322" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C4322" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4322" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4322" s="2" t="s">
+        <v>3367</v>
+      </c>
+      <c r="F4322" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4322" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4323" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B4323" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C4323" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4323" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4323" s="2" t="s">
+        <v>3368</v>
+      </c>
+      <c r="F4323" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4323" s="7">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4324" s="7"/>
+      <c r="E4324" s="2"/>
+    </row>
+    <row r="4325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4325" s="7"/>
+      <c r="E4325" s="2"/>
+    </row>
+    <row r="4326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4326" s="7"/>
+      <c r="E4326" s="2"/>
+    </row>
+    <row r="4327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4327" s="7"/>
+      <c r="E4327" s="2"/>
+    </row>
+    <row r="4328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4328" s="7"/>
+      <c r="E4328" s="2"/>
+    </row>
+    <row r="4329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4329" s="7"/>
+      <c r="E4329" s="2"/>
+    </row>
+    <row r="4330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4330" s="7"/>
+      <c r="E4330" s="2"/>
+    </row>
+    <row r="4331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4331" s="7"/>
+      <c r="E4331" s="2"/>
+    </row>
+    <row r="4332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4332" s="7"/>
+      <c r="E4332" s="2"/>
+    </row>
+    <row r="4333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4333" s="7"/>
+      <c r="E4333" s="2"/>
+    </row>
+    <row r="4334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4334" s="7"/>
+      <c r="E4334" s="2"/>
+    </row>
+    <row r="1045518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1045518" s="7"/>
+    </row>
+    <row r="1045528" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1045528" s="7"/>
+    </row>
+    <row r="1048531" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1048531" s="7"/>
+    </row>
+    <row r="1048547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1048547" s="7"/>
+    </row>
+    <row r="1048548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1048548" s="7"/>
+      <c r="G1048548" s="7"/>
+    </row>
+    <row r="1048551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1048551" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H172">
